--- a/DATA-ENS-2026-2027_surveillances.xlsx
+++ b/DATA-ENS-2026-2027_surveillances.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1867" uniqueCount="562">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1885" uniqueCount="559">
   <si>
     <t>Enseignements</t>
   </si>
@@ -104,7 +104,7 @@
     <t>RAIS ABDELMAJID</t>
   </si>
   <si>
-    <t>Retraité</t>
+    <t>Vacataire</t>
   </si>
   <si>
     <t>amrais@yahoo.com</t>
@@ -164,9 +164,6 @@
     <t>ABDELI MAMA</t>
   </si>
   <si>
-    <t>Vacataire</t>
-  </si>
-  <si>
     <t>abdelli.mama@gmail.com</t>
   </si>
   <si>
@@ -230,9 +227,6 @@
     <t>REGUIG ABDELDJALIL</t>
   </si>
   <si>
-    <t>Mise en disponibilité</t>
-  </si>
-  <si>
     <t>abdeldjalil.reguig@outlook.com</t>
   </si>
   <si>
@@ -600,9 +594,6 @@
   </si>
   <si>
     <t>KADA KLOUCHA OMAR</t>
-  </si>
-  <si>
-    <t>Permenant Associé</t>
   </si>
   <si>
     <t>klomar05@yahoo.fr</t>
@@ -2706,12 +2697,14 @@
   <dimension ref="A1:K190"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
+    <col min="1" max="1" width="42.4285714285714" customWidth="1"/>
     <col min="3" max="3" width="33.4285714285714" customWidth="1"/>
-    <col min="4" max="4" width="18.7142857142857" customWidth="1"/>
-    <col min="5" max="5" width="21.5714285714286" customWidth="1"/>
-    <col min="6" max="6" width="32.4285714285714" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="5.14285714285714" customWidth="1"/>
+    <col min="6" max="6" width="15.8571428571429" customWidth="1"/>
     <col min="7" max="7" width="15.7142857142857" customWidth="1"/>
     <col min="8" max="8" width="15.8571428571429" customWidth="1"/>
+    <col min="10" max="10" width="14.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -2891,13 +2884,13 @@
         <v>43</v>
       </c>
       <c r="D6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" t="s">
         <v>44</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>45</v>
-      </c>
-      <c r="G6" t="s">
-        <v>46</v>
       </c>
       <c r="H6" t="s">
         <v>26</v>
@@ -2914,68 +2907,74 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" t="s">
         <v>47</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>48</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" t="s">
         <v>49</v>
-      </c>
-      <c r="H7" t="s">
-        <v>50</v>
       </c>
       <c r="I7" t="s">
         <v>18</v>
       </c>
       <c r="J7" t="s">
+        <v>50</v>
+      </c>
+      <c r="K7" t="s">
         <v>51</v>
-      </c>
-      <c r="K7" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8" t="s">
         <v>53</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>54</v>
       </c>
-      <c r="C8" t="s">
-        <v>55</v>
+      <c r="D8" t="s">
+        <v>24</v>
       </c>
       <c r="H8" t="s">
         <v>26</v>
       </c>
       <c r="I8" t="s">
+        <v>55</v>
+      </c>
+      <c r="J8" t="s">
         <v>56</v>
       </c>
-      <c r="J8" t="s">
-        <v>57</v>
-      </c>
       <c r="K8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" t="s">
         <v>58</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>59</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
+        <v>24</v>
+      </c>
+      <c r="F9" t="s">
         <v>60</v>
       </c>
-      <c r="D9" t="s">
-        <v>44</v>
-      </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>61</v>
-      </c>
-      <c r="G9" t="s">
-        <v>62</v>
       </c>
       <c r="H9" t="s">
         <v>17</v>
@@ -2984,53 +2983,56 @@
         <v>27</v>
       </c>
       <c r="J9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" t="s">
         <v>63</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>64</v>
       </c>
-      <c r="C10" t="s">
-        <v>65</v>
-      </c>
       <c r="D10" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="E10" t="s">
         <v>31</v>
       </c>
       <c r="F10" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I10" t="s">
         <v>34</v>
       </c>
       <c r="J10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11" t="s">
         <v>68</v>
       </c>
-      <c r="B11" t="s">
-        <v>69</v>
-      </c>
-      <c r="C11" t="s">
-        <v>70</v>
+      <c r="D11" t="s">
+        <v>38</v>
       </c>
       <c r="H11" t="s">
         <v>17</v>
@@ -3039,21 +3041,24 @@
         <v>34</v>
       </c>
       <c r="J11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
+        <v>69</v>
+      </c>
+      <c r="B12" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" t="s">
         <v>71</v>
       </c>
-      <c r="B12" t="s">
-        <v>72</v>
-      </c>
-      <c r="C12" t="s">
-        <v>73</v>
+      <c r="D12" t="s">
+        <v>38</v>
       </c>
       <c r="H12" t="s">
         <v>26</v>
@@ -3062,122 +3067,134 @@
         <v>34</v>
       </c>
       <c r="J12" t="s">
+        <v>50</v>
+      </c>
+      <c r="K12" t="s">
         <v>51</v>
-      </c>
-      <c r="K12" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
+        <v>72</v>
+      </c>
+      <c r="B13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" t="s">
         <v>74</v>
       </c>
-      <c r="B13" t="s">
-        <v>75</v>
-      </c>
-      <c r="C13" t="s">
-        <v>76</v>
+      <c r="D13" t="s">
+        <v>24</v>
       </c>
       <c r="H13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I13" t="s">
         <v>40</v>
       </c>
       <c r="J13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
+        <v>75</v>
+      </c>
+      <c r="B14" t="s">
+        <v>76</v>
+      </c>
+      <c r="C14" t="s">
         <v>77</v>
       </c>
-      <c r="B14" t="s">
+      <c r="D14" t="s">
+        <v>38</v>
+      </c>
+      <c r="H14" t="s">
         <v>78</v>
-      </c>
-      <c r="C14" t="s">
-        <v>79</v>
-      </c>
-      <c r="H14" t="s">
-        <v>80</v>
       </c>
       <c r="I14" t="s">
         <v>40</v>
       </c>
       <c r="J14" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B15" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C15" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" t="s">
+        <v>38</v>
+      </c>
+      <c r="H15" t="s">
         <v>49</v>
-      </c>
-      <c r="H15" t="s">
-        <v>50</v>
       </c>
       <c r="I15" t="s">
         <v>18</v>
       </c>
       <c r="J15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K15" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B16" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C16" t="s">
-        <v>55</v>
+        <v>54</v>
+      </c>
+      <c r="D16" t="s">
+        <v>24</v>
       </c>
       <c r="H16" t="s">
         <v>26</v>
       </c>
       <c r="I16" t="s">
+        <v>55</v>
+      </c>
+      <c r="J16" t="s">
         <v>56</v>
       </c>
-      <c r="J16" t="s">
-        <v>57</v>
-      </c>
       <c r="K16" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C17" t="s">
+        <v>59</v>
+      </c>
+      <c r="D17" t="s">
+        <v>24</v>
+      </c>
+      <c r="F17" t="s">
         <v>60</v>
       </c>
-      <c r="D17" t="s">
-        <v>44</v>
-      </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>61</v>
-      </c>
-      <c r="G17" t="s">
-        <v>62</v>
       </c>
       <c r="H17" t="s">
         <v>17</v>
@@ -3186,53 +3203,56 @@
         <v>27</v>
       </c>
       <c r="J17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K17" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B18" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C18" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="E18" t="s">
         <v>31</v>
       </c>
       <c r="F18" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H18" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I18" t="s">
         <v>34</v>
       </c>
       <c r="J18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K18" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
+        <v>66</v>
+      </c>
+      <c r="B19" t="s">
+        <v>84</v>
+      </c>
+      <c r="C19" t="s">
         <v>68</v>
       </c>
-      <c r="B19" t="s">
-        <v>86</v>
-      </c>
-      <c r="C19" t="s">
-        <v>70</v>
+      <c r="D19" t="s">
+        <v>38</v>
       </c>
       <c r="H19" t="s">
         <v>17</v>
@@ -3241,21 +3261,24 @@
         <v>34</v>
       </c>
       <c r="J19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K19" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B20" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C20" t="s">
-        <v>88</v>
+        <v>86</v>
+      </c>
+      <c r="D20" t="s">
+        <v>38</v>
       </c>
       <c r="H20" t="s">
         <v>26</v>
@@ -3264,73 +3287,79 @@
         <v>34</v>
       </c>
       <c r="J20" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K20" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
+        <v>72</v>
+      </c>
+      <c r="B21" t="s">
+        <v>87</v>
+      </c>
+      <c r="C21" t="s">
         <v>74</v>
       </c>
-      <c r="B21" t="s">
-        <v>89</v>
-      </c>
-      <c r="C21" t="s">
-        <v>76</v>
+      <c r="D21" t="s">
+        <v>24</v>
       </c>
       <c r="H21" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I21" t="s">
         <v>40</v>
       </c>
       <c r="J21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K21" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
+        <v>75</v>
+      </c>
+      <c r="B22" t="s">
+        <v>88</v>
+      </c>
+      <c r="C22" t="s">
         <v>77</v>
       </c>
-      <c r="B22" t="s">
-        <v>90</v>
-      </c>
-      <c r="C22" t="s">
-        <v>79</v>
+      <c r="D22" t="s">
+        <v>38</v>
       </c>
       <c r="H22" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I22" t="s">
         <v>40</v>
       </c>
       <c r="J22" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K22" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
+        <v>89</v>
+      </c>
+      <c r="B23" t="s">
+        <v>90</v>
+      </c>
+      <c r="C23" t="s">
         <v>91</v>
       </c>
-      <c r="B23" t="s">
+      <c r="D23" t="s">
+        <v>24</v>
+      </c>
+      <c r="F23" t="s">
         <v>92</v>
-      </c>
-      <c r="C23" t="s">
-        <v>93</v>
-      </c>
-      <c r="D23" t="s">
-        <v>44</v>
-      </c>
-      <c r="F23" t="s">
-        <v>94</v>
       </c>
       <c r="H23" t="s">
         <v>26</v>
@@ -3339,56 +3368,56 @@
         <v>18</v>
       </c>
       <c r="J23" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K23" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" t="s">
+        <v>95</v>
+      </c>
+      <c r="B24" t="s">
+        <v>96</v>
+      </c>
+      <c r="C24" t="s">
         <v>97</v>
       </c>
-      <c r="B24" t="s">
+      <c r="D24" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24" t="s">
         <v>98</v>
       </c>
-      <c r="C24" t="s">
+      <c r="F24" t="s">
         <v>99</v>
       </c>
-      <c r="D24" t="s">
-        <v>44</v>
-      </c>
-      <c r="E24" t="s">
+      <c r="G24" t="s">
         <v>100</v>
-      </c>
-      <c r="F24" t="s">
-        <v>101</v>
-      </c>
-      <c r="G24" t="s">
-        <v>102</v>
       </c>
       <c r="H24" t="s">
         <v>26</v>
       </c>
       <c r="I24" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J24" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K24" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" t="s">
+        <v>101</v>
+      </c>
+      <c r="B25" t="s">
+        <v>102</v>
+      </c>
+      <c r="C25" t="s">
         <v>103</v>
-      </c>
-      <c r="B25" t="s">
-        <v>104</v>
-      </c>
-      <c r="C25" t="s">
-        <v>105</v>
       </c>
       <c r="D25" t="s">
         <v>38</v>
@@ -3397,71 +3426,71 @@
         <v>31</v>
       </c>
       <c r="F25" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H25" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I25" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J25" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K25" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" t="s">
+        <v>106</v>
+      </c>
+      <c r="B26" t="s">
+        <v>107</v>
+      </c>
+      <c r="C26" t="s">
         <v>108</v>
       </c>
-      <c r="B26" t="s">
+      <c r="D26" t="s">
+        <v>38</v>
+      </c>
+      <c r="E26" t="s">
+        <v>15</v>
+      </c>
+      <c r="F26" t="s">
         <v>109</v>
       </c>
-      <c r="C26" t="s">
+      <c r="H26" t="s">
         <v>110</v>
-      </c>
-      <c r="D26" t="s">
-        <v>38</v>
-      </c>
-      <c r="E26" t="s">
-        <v>15</v>
-      </c>
-      <c r="F26" t="s">
-        <v>111</v>
-      </c>
-      <c r="H26" t="s">
-        <v>112</v>
       </c>
       <c r="I26" t="s">
         <v>27</v>
       </c>
       <c r="J26" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="K26" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" t="s">
+        <v>112</v>
+      </c>
+      <c r="B27" t="s">
+        <v>113</v>
+      </c>
+      <c r="C27" t="s">
         <v>114</v>
       </c>
-      <c r="B27" t="s">
+      <c r="D27" t="s">
+        <v>38</v>
+      </c>
+      <c r="E27" t="s">
+        <v>15</v>
+      </c>
+      <c r="F27" t="s">
         <v>115</v>
-      </c>
-      <c r="C27" t="s">
-        <v>116</v>
-      </c>
-      <c r="D27" t="s">
-        <v>38</v>
-      </c>
-      <c r="E27" t="s">
-        <v>15</v>
-      </c>
-      <c r="F27" t="s">
-        <v>117</v>
       </c>
       <c r="H27" t="s">
         <v>26</v>
@@ -3470,18 +3499,18 @@
         <v>27</v>
       </c>
       <c r="J27" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K27" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B28" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C28" t="s">
         <v>13</v>
@@ -3496,36 +3525,36 @@
         <v>16</v>
       </c>
       <c r="H28" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I28" t="s">
         <v>34</v>
       </c>
       <c r="J28" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K28" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" t="s">
+        <v>118</v>
+      </c>
+      <c r="B29" t="s">
+        <v>119</v>
+      </c>
+      <c r="C29" t="s">
         <v>120</v>
       </c>
-      <c r="B29" t="s">
+      <c r="D29" t="s">
+        <v>38</v>
+      </c>
+      <c r="E29" t="s">
+        <v>15</v>
+      </c>
+      <c r="F29" t="s">
         <v>121</v>
-      </c>
-      <c r="C29" t="s">
-        <v>122</v>
-      </c>
-      <c r="D29" t="s">
-        <v>38</v>
-      </c>
-      <c r="E29" t="s">
-        <v>15</v>
-      </c>
-      <c r="F29" t="s">
-        <v>123</v>
       </c>
       <c r="H29" t="s">
         <v>26</v>
@@ -3534,225 +3563,225 @@
         <v>34</v>
       </c>
       <c r="J29" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K29" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" t="s">
+        <v>122</v>
+      </c>
+      <c r="B30" t="s">
+        <v>123</v>
+      </c>
+      <c r="C30" t="s">
         <v>124</v>
       </c>
-      <c r="B30" t="s">
+      <c r="D30" t="s">
+        <v>24</v>
+      </c>
+      <c r="F30" t="s">
         <v>125</v>
       </c>
-      <c r="C30" t="s">
+      <c r="G30" t="s">
         <v>126</v>
       </c>
-      <c r="D30" t="s">
-        <v>44</v>
-      </c>
-      <c r="F30" t="s">
-        <v>127</v>
-      </c>
-      <c r="G30" t="s">
-        <v>128</v>
-      </c>
       <c r="H30" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I30" t="s">
         <v>40</v>
       </c>
       <c r="J30" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K30" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" t="s">
+        <v>127</v>
+      </c>
+      <c r="B31" t="s">
+        <v>128</v>
+      </c>
+      <c r="C31" t="s">
         <v>129</v>
       </c>
-      <c r="B31" t="s">
+      <c r="D31" t="s">
+        <v>24</v>
+      </c>
+      <c r="E31" t="s">
         <v>130</v>
       </c>
-      <c r="C31" t="s">
+      <c r="F31" t="s">
         <v>131</v>
       </c>
-      <c r="D31" t="s">
-        <v>44</v>
-      </c>
-      <c r="E31" t="s">
+      <c r="G31" t="s">
         <v>132</v>
       </c>
-      <c r="F31" t="s">
+      <c r="H31" t="s">
+        <v>110</v>
+      </c>
+      <c r="I31" t="s">
+        <v>55</v>
+      </c>
+      <c r="J31" t="s">
         <v>133</v>
       </c>
-      <c r="G31" t="s">
+      <c r="K31" t="s">
         <v>134</v>
-      </c>
-      <c r="H31" t="s">
-        <v>112</v>
-      </c>
-      <c r="I31" t="s">
-        <v>56</v>
-      </c>
-      <c r="J31" t="s">
-        <v>135</v>
-      </c>
-      <c r="K31" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" t="s">
+        <v>135</v>
+      </c>
+      <c r="B32" t="s">
+        <v>136</v>
+      </c>
+      <c r="C32" t="s">
         <v>137</v>
       </c>
-      <c r="B32" t="s">
+      <c r="D32" t="s">
+        <v>24</v>
+      </c>
+      <c r="F32" t="s">
         <v>138</v>
-      </c>
-      <c r="C32" t="s">
-        <v>139</v>
-      </c>
-      <c r="D32" t="s">
-        <v>44</v>
-      </c>
-      <c r="F32" t="s">
-        <v>140</v>
       </c>
       <c r="H32" t="s">
         <v>26</v>
       </c>
       <c r="I32" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J32" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="K32" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B33" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C33" t="s">
+        <v>108</v>
+      </c>
+      <c r="D33" t="s">
+        <v>38</v>
+      </c>
+      <c r="E33" t="s">
+        <v>15</v>
+      </c>
+      <c r="F33" t="s">
+        <v>109</v>
+      </c>
+      <c r="H33" t="s">
         <v>110</v>
-      </c>
-      <c r="D33" t="s">
-        <v>38</v>
-      </c>
-      <c r="E33" t="s">
-        <v>15</v>
-      </c>
-      <c r="F33" t="s">
-        <v>111</v>
-      </c>
-      <c r="H33" t="s">
-        <v>112</v>
       </c>
       <c r="I33" t="s">
         <v>27</v>
       </c>
       <c r="J33" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="K33" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" t="s">
+        <v>142</v>
+      </c>
+      <c r="B34" t="s">
+        <v>143</v>
+      </c>
+      <c r="C34" t="s">
         <v>144</v>
       </c>
-      <c r="B34" t="s">
+      <c r="D34" t="s">
+        <v>38</v>
+      </c>
+      <c r="E34" t="s">
+        <v>15</v>
+      </c>
+      <c r="F34" t="s">
         <v>145</v>
       </c>
-      <c r="C34" t="s">
-        <v>146</v>
-      </c>
-      <c r="D34" t="s">
-        <v>38</v>
-      </c>
-      <c r="E34" t="s">
-        <v>15</v>
-      </c>
-      <c r="F34" t="s">
-        <v>147</v>
-      </c>
       <c r="H34" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I34" t="s">
         <v>27</v>
       </c>
       <c r="J34" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="K34" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" t="s">
+        <v>146</v>
+      </c>
+      <c r="B35" t="s">
+        <v>147</v>
+      </c>
+      <c r="C35" t="s">
         <v>148</v>
       </c>
-      <c r="B35" t="s">
+      <c r="D35" t="s">
+        <v>38</v>
+      </c>
+      <c r="E35" t="s">
+        <v>15</v>
+      </c>
+      <c r="F35" t="s">
         <v>149</v>
       </c>
-      <c r="C35" t="s">
-        <v>150</v>
-      </c>
-      <c r="D35" t="s">
-        <v>38</v>
-      </c>
-      <c r="E35" t="s">
-        <v>15</v>
-      </c>
-      <c r="F35" t="s">
-        <v>151</v>
-      </c>
       <c r="H35" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I35" t="s">
         <v>34</v>
       </c>
       <c r="J35" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K35" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" t="s">
+        <v>151</v>
+      </c>
+      <c r="B36" t="s">
+        <v>152</v>
+      </c>
+      <c r="C36" t="s">
         <v>153</v>
       </c>
-      <c r="B36" t="s">
+      <c r="D36" t="s">
+        <v>24</v>
+      </c>
+      <c r="E36" t="s">
         <v>154</v>
       </c>
-      <c r="C36" t="s">
+      <c r="F36" t="s">
         <v>155</v>
       </c>
-      <c r="D36" t="s">
-        <v>44</v>
-      </c>
-      <c r="E36" t="s">
+      <c r="G36" t="s">
         <v>156</v>
-      </c>
-      <c r="F36" t="s">
-        <v>157</v>
-      </c>
-      <c r="G36" t="s">
-        <v>158</v>
       </c>
       <c r="H36" t="s">
         <v>17</v>
@@ -3761,21 +3790,21 @@
         <v>40</v>
       </c>
       <c r="J36" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K36" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="37" spans="1:11">
       <c r="A37" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B37" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C37" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D37" t="s">
         <v>38</v>
@@ -3784,7 +3813,7 @@
         <v>15</v>
       </c>
       <c r="F37" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H37" t="s">
         <v>26</v>
@@ -3793,62 +3822,62 @@
         <v>40</v>
       </c>
       <c r="J37" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K37" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="38" spans="1:11">
       <c r="A38" t="s">
+        <v>160</v>
+      </c>
+      <c r="B38" t="s">
+        <v>161</v>
+      </c>
+      <c r="C38" t="s">
         <v>162</v>
-      </c>
-      <c r="B38" t="s">
-        <v>163</v>
-      </c>
-      <c r="C38" t="s">
-        <v>164</v>
       </c>
       <c r="D38" t="s">
         <v>14</v>
       </c>
       <c r="E38" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F38" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H38" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I38" t="s">
         <v>18</v>
       </c>
       <c r="J38" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="K38" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="39" spans="1:11">
       <c r="A39" t="s">
+        <v>167</v>
+      </c>
+      <c r="B39" t="s">
+        <v>168</v>
+      </c>
+      <c r="C39" t="s">
         <v>169</v>
       </c>
-      <c r="B39" t="s">
+      <c r="D39" t="s">
+        <v>38</v>
+      </c>
+      <c r="E39" t="s">
+        <v>15</v>
+      </c>
+      <c r="F39" t="s">
         <v>170</v>
-      </c>
-      <c r="C39" t="s">
-        <v>171</v>
-      </c>
-      <c r="D39" t="s">
-        <v>38</v>
-      </c>
-      <c r="E39" t="s">
-        <v>15</v>
-      </c>
-      <c r="F39" t="s">
-        <v>172</v>
       </c>
       <c r="H39" t="s">
         <v>17</v>
@@ -3857,21 +3886,21 @@
         <v>18</v>
       </c>
       <c r="J39" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="K39" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="40" spans="1:11">
       <c r="A40" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B40" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C40" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D40" t="s">
         <v>38</v>
@@ -3880,7 +3909,7 @@
         <v>15</v>
       </c>
       <c r="F40" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="H40" t="s">
         <v>26</v>
@@ -3889,21 +3918,21 @@
         <v>18</v>
       </c>
       <c r="J40" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="K40" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="41" spans="1:11">
       <c r="A41" t="s">
+        <v>173</v>
+      </c>
+      <c r="B41" t="s">
+        <v>174</v>
+      </c>
+      <c r="C41" t="s">
         <v>175</v>
-      </c>
-      <c r="B41" t="s">
-        <v>176</v>
-      </c>
-      <c r="C41" t="s">
-        <v>177</v>
       </c>
       <c r="D41" t="s">
         <v>38</v>
@@ -3912,39 +3941,39 @@
         <v>31</v>
       </c>
       <c r="F41" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H41" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I41" t="s">
         <v>27</v>
       </c>
       <c r="J41" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="K41" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="42" spans="1:11">
       <c r="A42" t="s">
+        <v>177</v>
+      </c>
+      <c r="B42" t="s">
+        <v>178</v>
+      </c>
+      <c r="C42" t="s">
         <v>179</v>
       </c>
-      <c r="B42" t="s">
+      <c r="D42" t="s">
+        <v>38</v>
+      </c>
+      <c r="E42" t="s">
+        <v>15</v>
+      </c>
+      <c r="F42" t="s">
         <v>180</v>
-      </c>
-      <c r="C42" t="s">
-        <v>181</v>
-      </c>
-      <c r="D42" t="s">
-        <v>38</v>
-      </c>
-      <c r="E42" t="s">
-        <v>15</v>
-      </c>
-      <c r="F42" t="s">
-        <v>182</v>
       </c>
       <c r="H42" t="s">
         <v>26</v>
@@ -3953,21 +3982,21 @@
         <v>27</v>
       </c>
       <c r="J42" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="K42" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="43" spans="1:11">
       <c r="A43" t="s">
+        <v>181</v>
+      </c>
+      <c r="B43" t="s">
+        <v>182</v>
+      </c>
+      <c r="C43" t="s">
         <v>183</v>
-      </c>
-      <c r="B43" t="s">
-        <v>184</v>
-      </c>
-      <c r="C43" t="s">
-        <v>185</v>
       </c>
       <c r="D43" t="s">
         <v>14</v>
@@ -3976,39 +4005,39 @@
         <v>31</v>
       </c>
       <c r="F43" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H43" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I43" t="s">
         <v>34</v>
       </c>
       <c r="J43" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="K43" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="44" spans="1:11">
       <c r="A44" t="s">
+        <v>185</v>
+      </c>
+      <c r="B44" t="s">
+        <v>186</v>
+      </c>
+      <c r="C44" t="s">
         <v>187</v>
       </c>
-      <c r="B44" t="s">
-        <v>188</v>
-      </c>
-      <c r="C44" t="s">
-        <v>189</v>
-      </c>
       <c r="D44" t="s">
-        <v>190</v>
+        <v>38</v>
       </c>
       <c r="E44" t="s">
         <v>31</v>
       </c>
       <c r="F44" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="H44" t="s">
         <v>26</v>
@@ -4017,56 +4046,59 @@
         <v>34</v>
       </c>
       <c r="J44" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="K44" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="45" spans="1:11">
       <c r="A45" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B45" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C45" t="s">
-        <v>76</v>
+        <v>74</v>
+      </c>
+      <c r="D45" t="s">
+        <v>24</v>
       </c>
       <c r="H45" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I45" t="s">
         <v>40</v>
       </c>
       <c r="J45" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="K45" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="46" spans="1:11">
       <c r="A46" t="s">
+        <v>192</v>
+      </c>
+      <c r="B46" t="s">
+        <v>193</v>
+      </c>
+      <c r="C46" t="s">
+        <v>194</v>
+      </c>
+      <c r="D46" t="s">
+        <v>24</v>
+      </c>
+      <c r="E46" t="s">
+        <v>130</v>
+      </c>
+      <c r="F46" t="s">
         <v>195</v>
       </c>
-      <c r="B46" t="s">
+      <c r="G46" t="s">
         <v>196</v>
-      </c>
-      <c r="C46" t="s">
-        <v>197</v>
-      </c>
-      <c r="D46" t="s">
-        <v>44</v>
-      </c>
-      <c r="E46" t="s">
-        <v>132</v>
-      </c>
-      <c r="F46" t="s">
-        <v>198</v>
-      </c>
-      <c r="G46" t="s">
-        <v>199</v>
       </c>
       <c r="H46" t="s">
         <v>17</v>
@@ -4075,30 +4107,30 @@
         <v>18</v>
       </c>
       <c r="J46" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="K46" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="47" spans="1:11">
       <c r="A47" t="s">
+        <v>199</v>
+      </c>
+      <c r="B47" t="s">
+        <v>200</v>
+      </c>
+      <c r="C47" t="s">
+        <v>201</v>
+      </c>
+      <c r="D47" t="s">
+        <v>38</v>
+      </c>
+      <c r="E47" t="s">
+        <v>15</v>
+      </c>
+      <c r="F47" t="s">
         <v>202</v>
-      </c>
-      <c r="B47" t="s">
-        <v>203</v>
-      </c>
-      <c r="C47" t="s">
-        <v>204</v>
-      </c>
-      <c r="D47" t="s">
-        <v>38</v>
-      </c>
-      <c r="E47" t="s">
-        <v>15</v>
-      </c>
-      <c r="F47" t="s">
-        <v>205</v>
       </c>
       <c r="H47" t="s">
         <v>26</v>
@@ -4107,132 +4139,132 @@
         <v>18</v>
       </c>
       <c r="J47" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="K47" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="48" spans="1:11">
       <c r="A48" t="s">
+        <v>203</v>
+      </c>
+      <c r="B48" t="s">
+        <v>204</v>
+      </c>
+      <c r="C48" t="s">
+        <v>205</v>
+      </c>
+      <c r="D48" t="s">
+        <v>38</v>
+      </c>
+      <c r="E48" t="s">
+        <v>15</v>
+      </c>
+      <c r="F48" t="s">
         <v>206</v>
       </c>
-      <c r="B48" t="s">
+      <c r="G48" t="s">
         <v>207</v>
       </c>
-      <c r="C48" t="s">
-        <v>208</v>
-      </c>
-      <c r="D48" t="s">
-        <v>190</v>
-      </c>
-      <c r="E48" t="s">
-        <v>15</v>
-      </c>
-      <c r="F48" t="s">
-        <v>209</v>
-      </c>
-      <c r="G48" t="s">
-        <v>210</v>
-      </c>
       <c r="H48" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I48" t="s">
         <v>18</v>
       </c>
       <c r="J48" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="K48" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="49" spans="1:11">
       <c r="A49" t="s">
+        <v>208</v>
+      </c>
+      <c r="B49" t="s">
+        <v>209</v>
+      </c>
+      <c r="C49" t="s">
+        <v>210</v>
+      </c>
+      <c r="D49" t="s">
+        <v>24</v>
+      </c>
+      <c r="E49" t="s">
+        <v>98</v>
+      </c>
+      <c r="F49" t="s">
         <v>211</v>
       </c>
-      <c r="B49" t="s">
+      <c r="G49" t="s">
         <v>212</v>
-      </c>
-      <c r="C49" t="s">
-        <v>213</v>
-      </c>
-      <c r="D49" t="s">
-        <v>44</v>
-      </c>
-      <c r="E49" t="s">
-        <v>100</v>
-      </c>
-      <c r="F49" t="s">
-        <v>214</v>
-      </c>
-      <c r="G49" t="s">
-        <v>215</v>
       </c>
       <c r="H49" t="s">
         <v>17</v>
       </c>
       <c r="I49" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J49" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="K49" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="50" spans="1:11">
       <c r="A50" t="s">
+        <v>214</v>
+      </c>
+      <c r="B50" t="s">
+        <v>215</v>
+      </c>
+      <c r="C50" t="s">
+        <v>216</v>
+      </c>
+      <c r="D50" t="s">
+        <v>38</v>
+      </c>
+      <c r="E50" t="s">
+        <v>15</v>
+      </c>
+      <c r="F50" t="s">
         <v>217</v>
       </c>
-      <c r="B50" t="s">
-        <v>218</v>
-      </c>
-      <c r="C50" t="s">
-        <v>219</v>
-      </c>
-      <c r="D50" t="s">
-        <v>38</v>
-      </c>
-      <c r="E50" t="s">
-        <v>15</v>
-      </c>
-      <c r="F50" t="s">
-        <v>220</v>
-      </c>
       <c r="H50" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I50" t="s">
         <v>27</v>
       </c>
       <c r="J50" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="K50" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="51" spans="1:11">
       <c r="A51" t="s">
+        <v>218</v>
+      </c>
+      <c r="B51" t="s">
+        <v>219</v>
+      </c>
+      <c r="C51" t="s">
+        <v>220</v>
+      </c>
+      <c r="D51" t="s">
+        <v>38</v>
+      </c>
+      <c r="E51" t="s">
+        <v>15</v>
+      </c>
+      <c r="F51" t="s">
         <v>221</v>
-      </c>
-      <c r="B51" t="s">
-        <v>222</v>
-      </c>
-      <c r="C51" t="s">
-        <v>223</v>
-      </c>
-      <c r="D51" t="s">
-        <v>38</v>
-      </c>
-      <c r="E51" t="s">
-        <v>15</v>
-      </c>
-      <c r="F51" t="s">
-        <v>224</v>
       </c>
       <c r="H51" t="s">
         <v>26</v>
@@ -4241,53 +4273,53 @@
         <v>34</v>
       </c>
       <c r="J51" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="K51" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="52" spans="1:11">
       <c r="A52" t="s">
+        <v>222</v>
+      </c>
+      <c r="B52" t="s">
+        <v>223</v>
+      </c>
+      <c r="C52" t="s">
+        <v>224</v>
+      </c>
+      <c r="D52" t="s">
+        <v>38</v>
+      </c>
+      <c r="E52" t="s">
+        <v>15</v>
+      </c>
+      <c r="F52" t="s">
         <v>225</v>
       </c>
-      <c r="B52" t="s">
-        <v>226</v>
-      </c>
-      <c r="C52" t="s">
-        <v>227</v>
-      </c>
-      <c r="D52" t="s">
-        <v>38</v>
-      </c>
-      <c r="E52" t="s">
-        <v>15</v>
-      </c>
-      <c r="F52" t="s">
-        <v>228</v>
-      </c>
       <c r="H52" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I52" t="s">
         <v>34</v>
       </c>
       <c r="J52" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="K52" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="53" spans="1:11">
       <c r="A53" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B53" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C53" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D53" t="s">
         <v>38</v>
@@ -4296,7 +4328,7 @@
         <v>15</v>
       </c>
       <c r="F53" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H53" t="s">
         <v>26</v>
@@ -4305,85 +4337,88 @@
         <v>40</v>
       </c>
       <c r="J53" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="K53" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="1:11">
       <c r="A54" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B54" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C54" t="s">
-        <v>233</v>
+        <v>230</v>
+      </c>
+      <c r="D54" t="s">
+        <v>24</v>
       </c>
       <c r="H54" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I54" t="s">
         <v>18</v>
       </c>
       <c r="J54" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="K54" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="55" spans="1:11">
       <c r="A55" t="s">
+        <v>233</v>
+      </c>
+      <c r="B55" t="s">
+        <v>234</v>
+      </c>
+      <c r="C55" t="s">
+        <v>235</v>
+      </c>
+      <c r="D55" t="s">
+        <v>38</v>
+      </c>
+      <c r="E55" t="s">
+        <v>15</v>
+      </c>
+      <c r="F55" t="s">
         <v>236</v>
       </c>
-      <c r="B55" t="s">
-        <v>237</v>
-      </c>
-      <c r="C55" t="s">
-        <v>238</v>
-      </c>
-      <c r="D55" t="s">
-        <v>38</v>
-      </c>
-      <c r="E55" t="s">
-        <v>15</v>
-      </c>
-      <c r="F55" t="s">
-        <v>239</v>
-      </c>
       <c r="H55" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I55" t="s">
         <v>18</v>
       </c>
       <c r="J55" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="K55" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="56" spans="1:11">
       <c r="A56" t="s">
+        <v>237</v>
+      </c>
+      <c r="B56" t="s">
+        <v>238</v>
+      </c>
+      <c r="C56" t="s">
+        <v>239</v>
+      </c>
+      <c r="D56" t="s">
+        <v>38</v>
+      </c>
+      <c r="E56" t="s">
+        <v>15</v>
+      </c>
+      <c r="F56" t="s">
         <v>240</v>
-      </c>
-      <c r="B56" t="s">
-        <v>241</v>
-      </c>
-      <c r="C56" t="s">
-        <v>242</v>
-      </c>
-      <c r="D56" t="s">
-        <v>38</v>
-      </c>
-      <c r="E56" t="s">
-        <v>15</v>
-      </c>
-      <c r="F56" t="s">
-        <v>243</v>
       </c>
       <c r="H56" t="s">
         <v>26</v>
@@ -4392,21 +4427,21 @@
         <v>18</v>
       </c>
       <c r="J56" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="K56" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="57" spans="1:11">
       <c r="A57" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B57" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C57" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="D57" t="s">
         <v>38</v>
@@ -4415,30 +4450,30 @@
         <v>15</v>
       </c>
       <c r="F57" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="H57" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I57" t="s">
         <v>27</v>
       </c>
       <c r="J57" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="K57" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="58" spans="1:11">
       <c r="A58" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B58" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C58" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D58" t="s">
         <v>38</v>
@@ -4447,7 +4482,7 @@
         <v>31</v>
       </c>
       <c r="F58" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="H58" t="s">
         <v>26</v>
@@ -4456,53 +4491,53 @@
         <v>27</v>
       </c>
       <c r="J58" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="K58" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="59" spans="1:11">
       <c r="A59" t="s">
+        <v>247</v>
+      </c>
+      <c r="B59" t="s">
+        <v>248</v>
+      </c>
+      <c r="C59" t="s">
+        <v>249</v>
+      </c>
+      <c r="D59" t="s">
+        <v>38</v>
+      </c>
+      <c r="E59" t="s">
+        <v>15</v>
+      </c>
+      <c r="F59" t="s">
         <v>250</v>
       </c>
-      <c r="B59" t="s">
-        <v>251</v>
-      </c>
-      <c r="C59" t="s">
-        <v>252</v>
-      </c>
-      <c r="D59" t="s">
-        <v>38</v>
-      </c>
-      <c r="E59" t="s">
-        <v>15</v>
-      </c>
-      <c r="F59" t="s">
-        <v>253</v>
-      </c>
       <c r="H59" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I59" t="s">
         <v>34</v>
       </c>
       <c r="J59" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="K59" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="60" spans="1:11">
       <c r="A60" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B60" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C60" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D60" t="s">
         <v>38</v>
@@ -4511,7 +4546,7 @@
         <v>15</v>
       </c>
       <c r="F60" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="H60" t="s">
         <v>26</v>
@@ -4520,44 +4555,47 @@
         <v>34</v>
       </c>
       <c r="J60" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="K60" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="61" spans="1:11">
       <c r="A61" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B61" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C61" t="s">
-        <v>76</v>
+        <v>74</v>
+      </c>
+      <c r="D61" t="s">
+        <v>24</v>
       </c>
       <c r="H61" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I61" t="s">
         <v>40</v>
       </c>
       <c r="J61" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="K61" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="62" spans="1:11">
       <c r="A62" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B62" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C62" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D62" t="s">
         <v>38</v>
@@ -4566,7 +4604,7 @@
         <v>31</v>
       </c>
       <c r="F62" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H62" t="s">
         <v>26</v>
@@ -4575,71 +4613,71 @@
         <v>40</v>
       </c>
       <c r="J62" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="K62" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="63" spans="1:11">
       <c r="A63" t="s">
+        <v>257</v>
+      </c>
+      <c r="B63" t="s">
+        <v>258</v>
+      </c>
+      <c r="C63" t="s">
+        <v>259</v>
+      </c>
+      <c r="D63" t="s">
+        <v>24</v>
+      </c>
+      <c r="F63" t="s">
         <v>260</v>
       </c>
-      <c r="B63" t="s">
+      <c r="H63" t="s">
         <v>261</v>
-      </c>
-      <c r="C63" t="s">
-        <v>262</v>
-      </c>
-      <c r="D63" t="s">
-        <v>44</v>
-      </c>
-      <c r="F63" t="s">
-        <v>263</v>
-      </c>
-      <c r="H63" t="s">
-        <v>264</v>
       </c>
       <c r="I63" t="s">
         <v>40</v>
       </c>
       <c r="J63" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="K63" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="64" spans="1:11">
       <c r="A64" t="s">
+        <v>262</v>
+      </c>
+      <c r="B64" t="s">
+        <v>263</v>
+      </c>
+      <c r="C64" t="s">
+        <v>264</v>
+      </c>
+      <c r="D64" t="s">
+        <v>24</v>
+      </c>
+      <c r="F64" t="s">
         <v>265</v>
       </c>
-      <c r="B64" t="s">
+      <c r="G64" t="s">
         <v>266</v>
       </c>
-      <c r="C64" t="s">
+      <c r="H64" t="s">
         <v>267</v>
-      </c>
-      <c r="D64" t="s">
-        <v>44</v>
-      </c>
-      <c r="F64" t="s">
-        <v>268</v>
-      </c>
-      <c r="G64" t="s">
-        <v>269</v>
-      </c>
-      <c r="H64" t="s">
-        <v>270</v>
       </c>
       <c r="I64" t="s">
         <v>18</v>
       </c>
       <c r="J64" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="K64" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="65" spans="1:11">
@@ -4647,45 +4685,45 @@
         <v>41</v>
       </c>
       <c r="B65" t="s">
+        <v>270</v>
+      </c>
+      <c r="C65" t="s">
+        <v>271</v>
+      </c>
+      <c r="D65" t="s">
+        <v>38</v>
+      </c>
+      <c r="E65" t="s">
+        <v>15</v>
+      </c>
+      <c r="F65" t="s">
+        <v>272</v>
+      </c>
+      <c r="G65" t="s">
         <v>273</v>
       </c>
-      <c r="C65" t="s">
+      <c r="H65" t="s">
         <v>274</v>
-      </c>
-      <c r="D65" t="s">
-        <v>38</v>
-      </c>
-      <c r="E65" t="s">
-        <v>15</v>
-      </c>
-      <c r="F65" t="s">
-        <v>275</v>
-      </c>
-      <c r="G65" t="s">
-        <v>276</v>
-      </c>
-      <c r="H65" t="s">
-        <v>277</v>
       </c>
       <c r="I65" t="s">
         <v>18</v>
       </c>
       <c r="J65" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="K65" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="66" spans="1:11">
       <c r="A66" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B66" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C66" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D66" t="s">
         <v>38</v>
@@ -4694,65 +4732,65 @@
         <v>15</v>
       </c>
       <c r="F66" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="G66" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="H66" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="I66" t="s">
         <v>18</v>
       </c>
       <c r="J66" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="K66" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="67" spans="1:11">
       <c r="A67" t="s">
+        <v>262</v>
+      </c>
+      <c r="B67" t="s">
+        <v>263</v>
+      </c>
+      <c r="C67" t="s">
+        <v>264</v>
+      </c>
+      <c r="D67" t="s">
+        <v>24</v>
+      </c>
+      <c r="F67" t="s">
         <v>265</v>
       </c>
-      <c r="B67" t="s">
+      <c r="G67" t="s">
         <v>266</v>
       </c>
-      <c r="C67" t="s">
-        <v>267</v>
-      </c>
-      <c r="D67" t="s">
-        <v>44</v>
-      </c>
-      <c r="F67" t="s">
-        <v>268</v>
-      </c>
-      <c r="G67" t="s">
+      <c r="H67" t="s">
+        <v>274</v>
+      </c>
+      <c r="I67" t="s">
+        <v>55</v>
+      </c>
+      <c r="J67" t="s">
+        <v>279</v>
+      </c>
+      <c r="K67" t="s">
         <v>269</v>
-      </c>
-      <c r="H67" t="s">
-        <v>277</v>
-      </c>
-      <c r="I67" t="s">
-        <v>56</v>
-      </c>
-      <c r="J67" t="s">
-        <v>282</v>
-      </c>
-      <c r="K67" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="68" spans="1:11">
       <c r="A68" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B68" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C68" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D68" t="s">
         <v>38</v>
@@ -4761,30 +4799,30 @@
         <v>15</v>
       </c>
       <c r="F68" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H68" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="I68" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J68" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="K68" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="69" spans="1:11">
       <c r="A69" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B69" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C69" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="D69" t="s">
         <v>38</v>
@@ -4793,33 +4831,33 @@
         <v>31</v>
       </c>
       <c r="F69" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="G69" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="H69" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="I69" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J69" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="K69" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="70" spans="1:11">
       <c r="A70" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B70" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C70" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D70" t="s">
         <v>38</v>
@@ -4828,54 +4866,54 @@
         <v>15</v>
       </c>
       <c r="F70" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H70" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="I70" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J70" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="K70" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="71" spans="1:11">
       <c r="A71" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B71" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C71" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D71" t="s">
         <v>14</v>
       </c>
       <c r="E71" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="F71" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="G71" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="H71" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="I71" t="s">
         <v>34</v>
       </c>
       <c r="J71" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="K71" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="72" spans="1:11">
@@ -4883,45 +4921,45 @@
         <v>41</v>
       </c>
       <c r="B72" t="s">
+        <v>270</v>
+      </c>
+      <c r="C72" t="s">
+        <v>271</v>
+      </c>
+      <c r="D72" t="s">
+        <v>38</v>
+      </c>
+      <c r="E72" t="s">
+        <v>15</v>
+      </c>
+      <c r="F72" t="s">
+        <v>272</v>
+      </c>
+      <c r="G72" t="s">
         <v>273</v>
       </c>
-      <c r="C72" t="s">
+      <c r="H72" t="s">
         <v>274</v>
-      </c>
-      <c r="D72" t="s">
-        <v>38</v>
-      </c>
-      <c r="E72" t="s">
-        <v>15</v>
-      </c>
-      <c r="F72" t="s">
-        <v>275</v>
-      </c>
-      <c r="G72" t="s">
-        <v>276</v>
-      </c>
-      <c r="H72" t="s">
-        <v>277</v>
       </c>
       <c r="I72" t="s">
         <v>34</v>
       </c>
       <c r="J72" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="K72" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="73" spans="1:11">
       <c r="A73" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B73" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C73" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D73" t="s">
         <v>38</v>
@@ -4930,33 +4968,33 @@
         <v>15</v>
       </c>
       <c r="F73" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="G73" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="H73" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="I73" t="s">
         <v>34</v>
       </c>
       <c r="J73" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="K73" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="74" spans="1:11">
       <c r="A74" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B74" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C74" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="D74" t="s">
         <v>38</v>
@@ -4965,88 +5003,91 @@
         <v>31</v>
       </c>
       <c r="F74" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="G74" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="H74" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="I74" t="s">
         <v>34</v>
       </c>
       <c r="J74" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="K74" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="75" spans="1:11">
       <c r="A75" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B75" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C75" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D75" t="s">
         <v>14</v>
       </c>
       <c r="E75" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="F75" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="G75" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="H75" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="I75" t="s">
         <v>40</v>
       </c>
       <c r="J75" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="K75" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="76" spans="1:11">
       <c r="A76" t="s">
+        <v>296</v>
+      </c>
+      <c r="B76" t="s">
+        <v>297</v>
+      </c>
+      <c r="C76" t="s">
+        <v>298</v>
+      </c>
+      <c r="D76" t="s">
+        <v>38</v>
+      </c>
+      <c r="H76" t="s">
         <v>299</v>
-      </c>
-      <c r="B76" t="s">
-        <v>300</v>
-      </c>
-      <c r="C76" t="s">
-        <v>301</v>
-      </c>
-      <c r="H76" t="s">
-        <v>302</v>
       </c>
       <c r="I76" t="s">
         <v>40</v>
       </c>
       <c r="J76" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="K76" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="77" spans="1:11">
       <c r="A77" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B77" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C77" t="s">
         <v>30</v>
@@ -5070,82 +5111,85 @@
         <v>18</v>
       </c>
       <c r="J77" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="K77" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="78" spans="1:11">
       <c r="A78" t="s">
+        <v>304</v>
+      </c>
+      <c r="B78" t="s">
+        <v>305</v>
+      </c>
+      <c r="C78" t="s">
+        <v>306</v>
+      </c>
+      <c r="D78" t="s">
+        <v>38</v>
+      </c>
+      <c r="E78" t="s">
+        <v>15</v>
+      </c>
+      <c r="F78" t="s">
         <v>307</v>
       </c>
-      <c r="B78" t="s">
-        <v>308</v>
-      </c>
-      <c r="C78" t="s">
-        <v>309</v>
-      </c>
-      <c r="D78" t="s">
-        <v>38</v>
-      </c>
-      <c r="E78" t="s">
-        <v>15</v>
-      </c>
-      <c r="F78" t="s">
-        <v>310</v>
-      </c>
       <c r="H78" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I78" t="s">
         <v>18</v>
       </c>
       <c r="J78" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="K78" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="79" spans="1:11">
       <c r="A79" t="s">
+        <v>308</v>
+      </c>
+      <c r="B79" t="s">
+        <v>309</v>
+      </c>
+      <c r="C79" t="s">
+        <v>310</v>
+      </c>
+      <c r="D79" t="s">
+        <v>24</v>
+      </c>
+      <c r="F79" t="s">
         <v>311</v>
       </c>
-      <c r="B79" t="s">
+      <c r="H79" t="s">
+        <v>110</v>
+      </c>
+      <c r="I79" t="s">
+        <v>55</v>
+      </c>
+      <c r="J79" t="s">
         <v>312</v>
       </c>
-      <c r="C79" t="s">
-        <v>313</v>
-      </c>
-      <c r="D79" t="s">
-        <v>44</v>
-      </c>
-      <c r="F79" t="s">
-        <v>314</v>
-      </c>
-      <c r="H79" t="s">
-        <v>112</v>
-      </c>
-      <c r="I79" t="s">
-        <v>56</v>
-      </c>
-      <c r="J79" t="s">
-        <v>315</v>
-      </c>
       <c r="K79" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="80" spans="1:11">
       <c r="A80" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="B80" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C80" t="s">
-        <v>76</v>
+        <v>74</v>
+      </c>
+      <c r="D80" t="s">
+        <v>24</v>
       </c>
       <c r="H80" t="s">
         <v>17</v>
@@ -5154,30 +5198,30 @@
         <v>27</v>
       </c>
       <c r="J80" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="K80" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="81" spans="1:11">
       <c r="A81" t="s">
+        <v>315</v>
+      </c>
+      <c r="B81" t="s">
+        <v>316</v>
+      </c>
+      <c r="C81" t="s">
+        <v>317</v>
+      </c>
+      <c r="D81" t="s">
+        <v>24</v>
+      </c>
+      <c r="F81" t="s">
         <v>318</v>
       </c>
-      <c r="B81" t="s">
+      <c r="G81" t="s">
         <v>319</v>
-      </c>
-      <c r="C81" t="s">
-        <v>320</v>
-      </c>
-      <c r="D81" t="s">
-        <v>44</v>
-      </c>
-      <c r="F81" t="s">
-        <v>321</v>
-      </c>
-      <c r="G81" t="s">
-        <v>322</v>
       </c>
       <c r="H81" t="s">
         <v>26</v>
@@ -5186,56 +5230,56 @@
         <v>27</v>
       </c>
       <c r="J81" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="K81" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="82" spans="1:11">
       <c r="A82" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B82" t="s">
+        <v>320</v>
+      </c>
+      <c r="C82" t="s">
+        <v>321</v>
+      </c>
+      <c r="D82" t="s">
+        <v>24</v>
+      </c>
+      <c r="E82" t="s">
+        <v>98</v>
+      </c>
+      <c r="F82" t="s">
+        <v>322</v>
+      </c>
+      <c r="G82" t="s">
         <v>323</v>
       </c>
-      <c r="C82" t="s">
-        <v>324</v>
-      </c>
-      <c r="D82" t="s">
-        <v>44</v>
-      </c>
-      <c r="E82" t="s">
-        <v>100</v>
-      </c>
-      <c r="F82" t="s">
-        <v>325</v>
-      </c>
-      <c r="G82" t="s">
-        <v>326</v>
-      </c>
       <c r="H82" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I82" t="s">
         <v>34</v>
       </c>
       <c r="J82" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="K82" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="83" spans="1:11">
       <c r="A83" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="B83" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C83" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="D83" t="s">
         <v>14</v>
@@ -5244,7 +5288,7 @@
         <v>15</v>
       </c>
       <c r="F83" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="H83" t="s">
         <v>26</v>
@@ -5253,21 +5297,21 @@
         <v>40</v>
       </c>
       <c r="J83" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="K83" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="84" spans="1:11">
       <c r="A84" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B84" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C84" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D84" t="s">
         <v>38</v>
@@ -5276,7 +5320,7 @@
         <v>15</v>
       </c>
       <c r="F84" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H84" t="s">
         <v>26</v>
@@ -5285,85 +5329,85 @@
         <v>18</v>
       </c>
       <c r="J84" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="K84" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
     </row>
     <row r="85" spans="1:11">
       <c r="A85" t="s">
+        <v>332</v>
+      </c>
+      <c r="B85" t="s">
+        <v>333</v>
+      </c>
+      <c r="C85" t="s">
+        <v>334</v>
+      </c>
+      <c r="D85" t="s">
+        <v>38</v>
+      </c>
+      <c r="E85" t="s">
+        <v>15</v>
+      </c>
+      <c r="F85" t="s">
         <v>335</v>
       </c>
-      <c r="B85" t="s">
-        <v>336</v>
-      </c>
-      <c r="C85" t="s">
-        <v>337</v>
-      </c>
-      <c r="D85" t="s">
-        <v>38</v>
-      </c>
-      <c r="E85" t="s">
-        <v>15</v>
-      </c>
-      <c r="F85" t="s">
-        <v>338</v>
-      </c>
       <c r="H85" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I85" t="s">
         <v>18</v>
       </c>
       <c r="J85" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="K85" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
     </row>
     <row r="86" spans="1:11">
       <c r="A86" t="s">
+        <v>336</v>
+      </c>
+      <c r="B86" t="s">
+        <v>337</v>
+      </c>
+      <c r="C86" t="s">
+        <v>338</v>
+      </c>
+      <c r="D86" t="s">
+        <v>38</v>
+      </c>
+      <c r="E86" t="s">
+        <v>15</v>
+      </c>
+      <c r="F86" t="s">
         <v>339</v>
-      </c>
-      <c r="B86" t="s">
-        <v>340</v>
-      </c>
-      <c r="C86" t="s">
-        <v>341</v>
-      </c>
-      <c r="D86" t="s">
-        <v>38</v>
-      </c>
-      <c r="E86" t="s">
-        <v>15</v>
-      </c>
-      <c r="F86" t="s">
-        <v>342</v>
       </c>
       <c r="H86" t="s">
         <v>26</v>
       </c>
       <c r="I86" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J86" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="K86" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
     </row>
     <row r="87" spans="1:11">
       <c r="A87" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B87" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="C87" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D87" t="s">
         <v>38</v>
@@ -5372,7 +5416,7 @@
         <v>15</v>
       </c>
       <c r="F87" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H87" t="s">
         <v>26</v>
@@ -5381,21 +5425,21 @@
         <v>27</v>
       </c>
       <c r="J87" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="K87" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
     </row>
     <row r="88" spans="1:11">
       <c r="A88" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="B88" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C88" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="D88" t="s">
         <v>14</v>
@@ -5404,30 +5448,30 @@
         <v>15</v>
       </c>
       <c r="F88" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="H88" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I88" t="s">
         <v>34</v>
       </c>
       <c r="J88" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="K88" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
     </row>
     <row r="89" spans="1:11">
       <c r="A89" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="B89" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="C89" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D89" t="s">
         <v>38</v>
@@ -5436,7 +5480,7 @@
         <v>15</v>
       </c>
       <c r="F89" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H89" t="s">
         <v>26</v>
@@ -5445,21 +5489,21 @@
         <v>34</v>
       </c>
       <c r="J89" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="K89" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
     </row>
     <row r="90" spans="1:11">
       <c r="A90" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="B90" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C90" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D90" t="s">
         <v>38</v>
@@ -5468,30 +5512,30 @@
         <v>15</v>
       </c>
       <c r="F90" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H90" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I90" t="s">
         <v>34</v>
       </c>
       <c r="J90" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="K90" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
     </row>
     <row r="91" spans="1:11">
       <c r="A91" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B91" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C91" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D91" t="s">
         <v>38</v>
@@ -5500,30 +5544,30 @@
         <v>15</v>
       </c>
       <c r="F91" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H91" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I91" t="s">
         <v>40</v>
       </c>
       <c r="J91" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="K91" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
     </row>
     <row r="92" spans="1:11">
       <c r="A92" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B92" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C92" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="D92" t="s">
         <v>38</v>
@@ -5532,7 +5576,7 @@
         <v>15</v>
       </c>
       <c r="F92" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="H92" t="s">
         <v>26</v>
@@ -5541,21 +5585,21 @@
         <v>40</v>
       </c>
       <c r="J92" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="K92" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
     </row>
     <row r="93" spans="1:11">
       <c r="A93" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B93" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C93" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D93" t="s">
         <v>38</v>
@@ -5564,7 +5608,7 @@
         <v>15</v>
       </c>
       <c r="F93" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H93" t="s">
         <v>17</v>
@@ -5573,53 +5617,53 @@
         <v>18</v>
       </c>
       <c r="J93" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="K93" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
     <row r="94" spans="1:11">
       <c r="A94" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B94" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="C94" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D94" t="s">
         <v>14</v>
       </c>
       <c r="E94" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F94" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H94" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I94" t="s">
         <v>18</v>
       </c>
       <c r="J94" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="K94" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
     <row r="95" spans="1:11">
       <c r="A95" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B95" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C95" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D95" t="s">
         <v>14</v>
@@ -5628,30 +5672,30 @@
         <v>31</v>
       </c>
       <c r="F95" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H95" t="s">
         <v>26</v>
       </c>
       <c r="I95" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J95" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="K95" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
     <row r="96" spans="1:11">
       <c r="A96" t="s">
+        <v>173</v>
+      </c>
+      <c r="B96" t="s">
+        <v>362</v>
+      </c>
+      <c r="C96" t="s">
         <v>175</v>
-      </c>
-      <c r="B96" t="s">
-        <v>365</v>
-      </c>
-      <c r="C96" t="s">
-        <v>177</v>
       </c>
       <c r="D96" t="s">
         <v>38</v>
@@ -5660,7 +5704,7 @@
         <v>31</v>
       </c>
       <c r="F96" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H96" t="s">
         <v>26</v>
@@ -5669,21 +5713,21 @@
         <v>27</v>
       </c>
       <c r="J96" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="K96" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
     <row r="97" spans="1:11">
       <c r="A97" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="B97" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="C97" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D97" t="s">
         <v>38</v>
@@ -5692,42 +5736,42 @@
         <v>15</v>
       </c>
       <c r="F97" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="H97" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I97" t="s">
         <v>34</v>
       </c>
       <c r="J97" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="K97" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
     <row r="98" spans="1:11">
       <c r="A98" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B98" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C98" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D98" t="s">
-        <v>190</v>
+        <v>38</v>
       </c>
       <c r="E98" t="s">
         <v>15</v>
       </c>
       <c r="F98" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="G98" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H98" t="s">
         <v>26</v>
@@ -5736,18 +5780,18 @@
         <v>34</v>
       </c>
       <c r="J98" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="K98" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
     <row r="99" spans="1:11">
       <c r="A99" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="B99" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C99" t="s">
         <v>13</v>
@@ -5768,21 +5812,21 @@
         <v>40</v>
       </c>
       <c r="J99" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="K99" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
     <row r="100" spans="1:11">
       <c r="A100" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B100" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C100" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D100" t="s">
         <v>14</v>
@@ -5791,30 +5835,30 @@
         <v>31</v>
       </c>
       <c r="F100" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H100" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I100" t="s">
         <v>18</v>
       </c>
       <c r="J100" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="K100" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
     </row>
     <row r="101" spans="1:11">
       <c r="A101" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B101" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C101" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D101" t="s">
         <v>38</v>
@@ -5823,7 +5867,7 @@
         <v>15</v>
       </c>
       <c r="F101" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H101" t="s">
         <v>17</v>
@@ -5832,53 +5876,53 @@
         <v>18</v>
       </c>
       <c r="J101" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="K101" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
     </row>
     <row r="102" spans="1:11">
       <c r="A102" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B102" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C102" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D102" t="s">
         <v>14</v>
       </c>
       <c r="E102" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F102" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H102" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I102" t="s">
         <v>18</v>
       </c>
       <c r="J102" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="K102" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
     </row>
     <row r="103" spans="1:11">
       <c r="A103" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="B103" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C103" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D103" t="s">
         <v>38</v>
@@ -5887,7 +5931,7 @@
         <v>31</v>
       </c>
       <c r="F103" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H103" t="s">
         <v>26</v>
@@ -5896,21 +5940,21 @@
         <v>27</v>
       </c>
       <c r="J103" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="K103" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
     </row>
     <row r="104" spans="1:11">
       <c r="A104" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="B104" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="C104" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D104" t="s">
         <v>38</v>
@@ -5919,42 +5963,42 @@
         <v>15</v>
       </c>
       <c r="F104" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="H104" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I104" t="s">
         <v>34</v>
       </c>
       <c r="J104" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="K104" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
     </row>
     <row r="105" spans="1:11">
       <c r="A105" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B105" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C105" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D105" t="s">
-        <v>190</v>
+        <v>38</v>
       </c>
       <c r="E105" t="s">
         <v>15</v>
       </c>
       <c r="F105" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="G105" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H105" t="s">
         <v>26</v>
@@ -5963,18 +6007,18 @@
         <v>34</v>
       </c>
       <c r="J105" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="K105" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
     </row>
     <row r="106" spans="1:11">
       <c r="A106" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="B106" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="C106" t="s">
         <v>13</v>
@@ -5995,18 +6039,18 @@
         <v>40</v>
       </c>
       <c r="J106" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="K106" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
     </row>
     <row r="107" spans="1:11">
       <c r="A107" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="B107" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C107" t="s">
         <v>13</v>
@@ -6021,39 +6065,39 @@
         <v>16</v>
       </c>
       <c r="H107" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I107" t="s">
         <v>18</v>
       </c>
       <c r="J107" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="K107" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="108" spans="1:11">
       <c r="A108" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B108" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C108" t="s">
+        <v>129</v>
+      </c>
+      <c r="D108" t="s">
+        <v>24</v>
+      </c>
+      <c r="E108" t="s">
+        <v>130</v>
+      </c>
+      <c r="F108" t="s">
         <v>131</v>
       </c>
-      <c r="D108" t="s">
-        <v>44</v>
-      </c>
-      <c r="E108" t="s">
+      <c r="G108" t="s">
         <v>132</v>
-      </c>
-      <c r="F108" t="s">
-        <v>133</v>
-      </c>
-      <c r="G108" t="s">
-        <v>134</v>
       </c>
       <c r="H108" t="s">
         <v>26</v>
@@ -6062,21 +6106,21 @@
         <v>18</v>
       </c>
       <c r="J108" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="K108" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="109" spans="1:11">
       <c r="A109" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="B109" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C109" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D109" t="s">
         <v>38</v>
@@ -6085,30 +6129,30 @@
         <v>15</v>
       </c>
       <c r="F109" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="H109" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I109" t="s">
         <v>18</v>
       </c>
       <c r="J109" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="K109" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="110" spans="1:11">
       <c r="A110" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="B110" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="C110" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D110" t="s">
         <v>38</v>
@@ -6117,65 +6161,65 @@
         <v>15</v>
       </c>
       <c r="F110" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H110" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I110" t="s">
         <v>27</v>
       </c>
       <c r="J110" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="K110" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="111" spans="1:11">
       <c r="A111" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B111" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C111" t="s">
+        <v>129</v>
+      </c>
+      <c r="D111" t="s">
+        <v>24</v>
+      </c>
+      <c r="E111" t="s">
+        <v>130</v>
+      </c>
+      <c r="F111" t="s">
         <v>131</v>
       </c>
-      <c r="D111" t="s">
-        <v>44</v>
-      </c>
-      <c r="E111" t="s">
+      <c r="G111" t="s">
         <v>132</v>
       </c>
-      <c r="F111" t="s">
-        <v>133</v>
-      </c>
-      <c r="G111" t="s">
-        <v>134</v>
-      </c>
       <c r="H111" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I111" t="s">
         <v>34</v>
       </c>
       <c r="J111" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="K111" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="112" spans="1:11">
       <c r="A112" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B112" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="C112" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D112" t="s">
         <v>38</v>
@@ -6184,94 +6228,94 @@
         <v>15</v>
       </c>
       <c r="F112" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H112" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I112" t="s">
         <v>34</v>
       </c>
       <c r="J112" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="K112" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="113" spans="1:11">
       <c r="A113" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B113" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="C113" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="D113" t="s">
         <v>14</v>
       </c>
       <c r="E113" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F113" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="H113" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I113" t="s">
         <v>40</v>
       </c>
       <c r="J113" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="K113" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="114" spans="1:11">
       <c r="A114" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="B114" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C114" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D114" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="F114" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="G114" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H114" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I114" t="s">
         <v>40</v>
       </c>
       <c r="J114" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="K114" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="115" spans="1:11">
       <c r="A115" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B115" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="C115" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D115" t="s">
         <v>14</v>
@@ -6280,30 +6324,30 @@
         <v>31</v>
       </c>
       <c r="F115" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H115" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I115" t="s">
         <v>18</v>
       </c>
       <c r="J115" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="K115" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
     </row>
     <row r="116" spans="1:11">
       <c r="A116" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B116" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="C116" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D116" t="s">
         <v>38</v>
@@ -6312,7 +6356,7 @@
         <v>15</v>
       </c>
       <c r="F116" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H116" t="s">
         <v>17</v>
@@ -6321,30 +6365,30 @@
         <v>18</v>
       </c>
       <c r="J116" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="K116" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
     </row>
     <row r="117" spans="1:11">
       <c r="A117" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B117" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C117" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="D117" t="s">
         <v>14</v>
       </c>
       <c r="E117" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F117" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="H117" t="s">
         <v>26</v>
@@ -6353,21 +6397,21 @@
         <v>18</v>
       </c>
       <c r="J117" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="K117" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
     </row>
     <row r="118" spans="1:11">
       <c r="A118" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="B118" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="C118" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="D118" t="s">
         <v>38</v>
@@ -6376,42 +6420,42 @@
         <v>15</v>
       </c>
       <c r="F118" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="H118" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I118" t="s">
         <v>27</v>
       </c>
       <c r="J118" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="K118" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
     </row>
     <row r="119" spans="1:11">
       <c r="A119" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B119" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="C119" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D119" t="s">
-        <v>190</v>
+        <v>38</v>
       </c>
       <c r="E119" t="s">
         <v>15</v>
       </c>
       <c r="F119" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="G119" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H119" t="s">
         <v>26</v>
@@ -6420,21 +6464,21 @@
         <v>34</v>
       </c>
       <c r="J119" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="K119" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
     </row>
     <row r="120" spans="1:11">
       <c r="A120" t="s">
+        <v>173</v>
+      </c>
+      <c r="B120" t="s">
+        <v>401</v>
+      </c>
+      <c r="C120" t="s">
         <v>175</v>
-      </c>
-      <c r="B120" t="s">
-        <v>404</v>
-      </c>
-      <c r="C120" t="s">
-        <v>177</v>
       </c>
       <c r="D120" t="s">
         <v>38</v>
@@ -6443,30 +6487,30 @@
         <v>31</v>
       </c>
       <c r="F120" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H120" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I120" t="s">
         <v>40</v>
       </c>
       <c r="J120" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="K120" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
     </row>
     <row r="121" spans="1:11">
       <c r="A121" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="B121" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C121" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="D121" t="s">
         <v>38</v>
@@ -6475,7 +6519,7 @@
         <v>15</v>
       </c>
       <c r="F121" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H121" t="s">
         <v>26</v>
@@ -6484,30 +6528,30 @@
         <v>40</v>
       </c>
       <c r="J121" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="K121" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
     </row>
     <row r="122" spans="1:11">
       <c r="A122" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="B122" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C122" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="D122" t="s">
         <v>14</v>
       </c>
       <c r="E122" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F122" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="H122" t="s">
         <v>26</v>
@@ -6516,21 +6560,21 @@
         <v>18</v>
       </c>
       <c r="J122" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="K122" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
     </row>
     <row r="123" spans="1:11">
       <c r="A123" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B123" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="C123" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D123" t="s">
         <v>38</v>
@@ -6539,10 +6583,10 @@
         <v>15</v>
       </c>
       <c r="F123" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H123" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I123" t="s">
         <v>18</v>
@@ -6551,18 +6595,18 @@
         <v>19</v>
       </c>
       <c r="K123" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
     </row>
     <row r="124" spans="1:11">
       <c r="A124" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="B124" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="C124" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D124" t="s">
         <v>14</v>
@@ -6571,30 +6615,30 @@
         <v>31</v>
       </c>
       <c r="F124" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H124" t="s">
         <v>26</v>
       </c>
       <c r="I124" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J124" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="K124" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
     </row>
     <row r="125" spans="1:11">
       <c r="A125" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="B125" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C125" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="D125" t="s">
         <v>38</v>
@@ -6603,42 +6647,42 @@
         <v>15</v>
       </c>
       <c r="F125" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="H125" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I125" t="s">
         <v>27</v>
       </c>
       <c r="J125" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="K125" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
     </row>
     <row r="126" spans="1:11">
       <c r="A126" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B126" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C126" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D126" t="s">
-        <v>190</v>
+        <v>38</v>
       </c>
       <c r="E126" t="s">
         <v>15</v>
       </c>
       <c r="F126" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="G126" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H126" t="s">
         <v>26</v>
@@ -6647,53 +6691,53 @@
         <v>34</v>
       </c>
       <c r="J126" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="K126" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
     </row>
     <row r="127" spans="1:11">
       <c r="A127" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="B127" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C127" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="D127" t="s">
         <v>14</v>
       </c>
       <c r="E127" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F127" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="H127" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I127" t="s">
         <v>34</v>
       </c>
       <c r="J127" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="K127" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
     </row>
     <row r="128" spans="1:11">
       <c r="A128" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="B128" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="C128" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="D128" t="s">
         <v>38</v>
@@ -6702,7 +6746,7 @@
         <v>15</v>
       </c>
       <c r="F128" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H128" t="s">
         <v>26</v>
@@ -6711,21 +6755,21 @@
         <v>40</v>
       </c>
       <c r="J128" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="K128" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
     </row>
     <row r="129" spans="1:11">
       <c r="A129" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="B129" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C129" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="D129" t="s">
         <v>38</v>
@@ -6734,39 +6778,39 @@
         <v>31</v>
       </c>
       <c r="F129" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="H129" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I129" t="s">
         <v>18</v>
       </c>
       <c r="J129" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="K129" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
     </row>
     <row r="130" spans="1:11">
       <c r="A130" t="s">
+        <v>421</v>
+      </c>
+      <c r="B130" t="s">
+        <v>422</v>
+      </c>
+      <c r="C130" t="s">
+        <v>423</v>
+      </c>
+      <c r="D130" t="s">
+        <v>38</v>
+      </c>
+      <c r="E130" t="s">
+        <v>15</v>
+      </c>
+      <c r="F130" t="s">
         <v>424</v>
-      </c>
-      <c r="B130" t="s">
-        <v>425</v>
-      </c>
-      <c r="C130" t="s">
-        <v>426</v>
-      </c>
-      <c r="D130" t="s">
-        <v>38</v>
-      </c>
-      <c r="E130" t="s">
-        <v>15</v>
-      </c>
-      <c r="F130" t="s">
-        <v>427</v>
       </c>
       <c r="H130" t="s">
         <v>26</v>
@@ -6775,53 +6819,53 @@
         <v>18</v>
       </c>
       <c r="J130" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="K130" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
     </row>
     <row r="131" spans="1:11">
       <c r="A131" t="s">
+        <v>426</v>
+      </c>
+      <c r="B131" t="s">
+        <v>427</v>
+      </c>
+      <c r="C131" t="s">
+        <v>428</v>
+      </c>
+      <c r="D131" t="s">
+        <v>38</v>
+      </c>
+      <c r="E131" t="s">
+        <v>15</v>
+      </c>
+      <c r="F131" t="s">
         <v>429</v>
       </c>
-      <c r="B131" t="s">
-        <v>430</v>
-      </c>
-      <c r="C131" t="s">
-        <v>431</v>
-      </c>
-      <c r="D131" t="s">
-        <v>38</v>
-      </c>
-      <c r="E131" t="s">
-        <v>15</v>
-      </c>
-      <c r="F131" t="s">
-        <v>432</v>
-      </c>
       <c r="H131" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I131" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J131" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K131" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
     </row>
     <row r="132" spans="1:11">
       <c r="A132" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="B132" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C132" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D132" t="s">
         <v>38</v>
@@ -6830,7 +6874,7 @@
         <v>15</v>
       </c>
       <c r="F132" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="H132" t="s">
         <v>26</v>
@@ -6839,21 +6883,21 @@
         <v>27</v>
       </c>
       <c r="J132" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="K132" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
     </row>
     <row r="133" spans="1:11">
       <c r="A133" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="B133" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C133" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D133" t="s">
         <v>38</v>
@@ -6862,39 +6906,39 @@
         <v>31</v>
       </c>
       <c r="F133" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="H133" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I133" t="s">
         <v>34</v>
       </c>
       <c r="J133" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="K133" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
     </row>
     <row r="134" spans="1:11">
       <c r="A134" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="B134" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="C134" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="D134" t="s">
-        <v>190</v>
+        <v>38</v>
       </c>
       <c r="E134" t="s">
         <v>31</v>
       </c>
       <c r="F134" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="H134" t="s">
         <v>17</v>
@@ -6903,30 +6947,30 @@
         <v>34</v>
       </c>
       <c r="J134" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="K134" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
     </row>
     <row r="135" spans="1:11">
       <c r="A135" t="s">
+        <v>421</v>
+      </c>
+      <c r="B135" t="s">
+        <v>422</v>
+      </c>
+      <c r="C135" t="s">
+        <v>423</v>
+      </c>
+      <c r="D135" t="s">
+        <v>38</v>
+      </c>
+      <c r="E135" t="s">
+        <v>15</v>
+      </c>
+      <c r="F135" t="s">
         <v>424</v>
-      </c>
-      <c r="B135" t="s">
-        <v>425</v>
-      </c>
-      <c r="C135" t="s">
-        <v>426</v>
-      </c>
-      <c r="D135" t="s">
-        <v>38</v>
-      </c>
-      <c r="E135" t="s">
-        <v>15</v>
-      </c>
-      <c r="F135" t="s">
-        <v>427</v>
       </c>
       <c r="H135" t="s">
         <v>26</v>
@@ -6935,27 +6979,27 @@
         <v>34</v>
       </c>
       <c r="J135" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="K135" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
     </row>
     <row r="136" spans="1:11">
       <c r="A136" t="s">
+        <v>438</v>
+      </c>
+      <c r="B136" t="s">
+        <v>439</v>
+      </c>
+      <c r="C136" t="s">
+        <v>440</v>
+      </c>
+      <c r="D136" t="s">
+        <v>24</v>
+      </c>
+      <c r="F136" t="s">
         <v>441</v>
-      </c>
-      <c r="B136" t="s">
-        <v>442</v>
-      </c>
-      <c r="C136" t="s">
-        <v>443</v>
-      </c>
-      <c r="D136" t="s">
-        <v>44</v>
-      </c>
-      <c r="F136" t="s">
-        <v>444</v>
       </c>
       <c r="H136" t="s">
         <v>17</v>
@@ -6964,30 +7008,30 @@
         <v>40</v>
       </c>
       <c r="J136" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="K136" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
     </row>
     <row r="137" spans="1:11">
       <c r="A137" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="B137" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C137" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D137" t="s">
-        <v>190</v>
+        <v>38</v>
       </c>
       <c r="E137" t="s">
         <v>31</v>
       </c>
       <c r="F137" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="H137" t="s">
         <v>26</v>
@@ -6996,21 +7040,21 @@
         <v>40</v>
       </c>
       <c r="J137" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="K137" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
     </row>
     <row r="138" spans="1:11">
       <c r="A138" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="B138" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="C138" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D138" t="s">
         <v>14</v>
@@ -7019,7 +7063,7 @@
         <v>31</v>
       </c>
       <c r="F138" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H138" t="s">
         <v>26</v>
@@ -7028,21 +7072,21 @@
         <v>18</v>
       </c>
       <c r="J138" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="K138" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="139" spans="1:11">
       <c r="A139" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="B139" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C139" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D139" t="s">
         <v>38</v>
@@ -7051,62 +7095,62 @@
         <v>31</v>
       </c>
       <c r="F139" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="H139" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I139" t="s">
         <v>18</v>
       </c>
       <c r="J139" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="K139" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="140" spans="1:11">
       <c r="A140" t="s">
+        <v>426</v>
+      </c>
+      <c r="B140" t="s">
+        <v>449</v>
+      </c>
+      <c r="C140" t="s">
+        <v>428</v>
+      </c>
+      <c r="D140" t="s">
+        <v>38</v>
+      </c>
+      <c r="E140" t="s">
+        <v>15</v>
+      </c>
+      <c r="F140" t="s">
         <v>429</v>
       </c>
-      <c r="B140" t="s">
-        <v>452</v>
-      </c>
-      <c r="C140" t="s">
-        <v>431</v>
-      </c>
-      <c r="D140" t="s">
-        <v>38</v>
-      </c>
-      <c r="E140" t="s">
-        <v>15</v>
-      </c>
-      <c r="F140" t="s">
-        <v>432</v>
-      </c>
       <c r="H140" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I140" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J140" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K140" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="141" spans="1:11">
       <c r="A141" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="B141" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="C141" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="D141" t="s">
         <v>38</v>
@@ -7115,7 +7159,7 @@
         <v>15</v>
       </c>
       <c r="F141" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="H141" t="s">
         <v>26</v>
@@ -7124,21 +7168,21 @@
         <v>27</v>
       </c>
       <c r="J141" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="K141" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="142" spans="1:11">
       <c r="A142" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B142" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="C142" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D142" t="s">
         <v>38</v>
@@ -7147,68 +7191,68 @@
         <v>15</v>
       </c>
       <c r="F142" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="H142" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I142" t="s">
         <v>27</v>
       </c>
       <c r="J142" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="K142" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="143" spans="1:11">
       <c r="A143" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="B143" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="C143" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="F143" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="H143" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I143" t="s">
         <v>34</v>
       </c>
       <c r="J143" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="K143" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="144" spans="1:11">
       <c r="A144" t="s">
+        <v>455</v>
+      </c>
+      <c r="B144" t="s">
+        <v>456</v>
+      </c>
+      <c r="C144" t="s">
+        <v>457</v>
+      </c>
+      <c r="D144" t="s">
+        <v>38</v>
+      </c>
+      <c r="E144" t="s">
+        <v>15</v>
+      </c>
+      <c r="F144" t="s">
         <v>458</v>
-      </c>
-      <c r="B144" t="s">
-        <v>459</v>
-      </c>
-      <c r="C144" t="s">
-        <v>460</v>
-      </c>
-      <c r="D144" t="s">
-        <v>38</v>
-      </c>
-      <c r="E144" t="s">
-        <v>15</v>
-      </c>
-      <c r="F144" t="s">
-        <v>461</v>
       </c>
       <c r="H144" t="s">
         <v>26</v>
@@ -7217,21 +7261,21 @@
         <v>34</v>
       </c>
       <c r="J144" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="K144" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="145" spans="1:11">
       <c r="A145" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="B145" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="C145" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="D145" t="s">
         <v>38</v>
@@ -7240,7 +7284,7 @@
         <v>31</v>
       </c>
       <c r="F145" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="H145" t="s">
         <v>26</v>
@@ -7249,56 +7293,56 @@
         <v>40</v>
       </c>
       <c r="J145" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="K145" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="146" spans="1:11">
       <c r="A146" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="B146" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="C146" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D146" t="s">
-        <v>190</v>
+        <v>38</v>
       </c>
       <c r="E146" t="s">
         <v>15</v>
       </c>
       <c r="F146" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="G146" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H146" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I146" t="s">
         <v>40</v>
       </c>
       <c r="J146" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="K146" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="147" spans="1:11">
       <c r="A147" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B147" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="C147" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D147" t="s">
         <v>38</v>
@@ -7307,30 +7351,30 @@
         <v>15</v>
       </c>
       <c r="F147" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H147" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I147" t="s">
         <v>18</v>
       </c>
       <c r="J147" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="K147" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
     </row>
     <row r="148" spans="1:11">
       <c r="A148" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="B148" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="C148" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D148" t="s">
         <v>38</v>
@@ -7339,7 +7383,7 @@
         <v>15</v>
       </c>
       <c r="F148" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="H148" t="s">
         <v>17</v>
@@ -7348,21 +7392,21 @@
         <v>18</v>
       </c>
       <c r="J148" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="K148" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
     </row>
     <row r="149" spans="1:11">
       <c r="A149" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="B149" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="C149" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D149" t="s">
         <v>14</v>
@@ -7371,62 +7415,62 @@
         <v>31</v>
       </c>
       <c r="F149" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H149" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I149" t="s">
         <v>18</v>
       </c>
       <c r="J149" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="K149" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
     </row>
     <row r="150" spans="1:11">
       <c r="A150" t="s">
+        <v>426</v>
+      </c>
+      <c r="B150" t="s">
+        <v>470</v>
+      </c>
+      <c r="C150" t="s">
+        <v>428</v>
+      </c>
+      <c r="D150" t="s">
+        <v>38</v>
+      </c>
+      <c r="E150" t="s">
+        <v>15</v>
+      </c>
+      <c r="F150" t="s">
         <v>429</v>
       </c>
-      <c r="B150" t="s">
-        <v>473</v>
-      </c>
-      <c r="C150" t="s">
-        <v>431</v>
-      </c>
-      <c r="D150" t="s">
-        <v>38</v>
-      </c>
-      <c r="E150" t="s">
-        <v>15</v>
-      </c>
-      <c r="F150" t="s">
-        <v>432</v>
-      </c>
       <c r="H150" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I150" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J150" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K150" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
     </row>
     <row r="151" spans="1:11">
       <c r="A151" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="B151" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="C151" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="D151" t="s">
         <v>38</v>
@@ -7435,7 +7479,7 @@
         <v>15</v>
       </c>
       <c r="F151" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="H151" t="s">
         <v>17</v>
@@ -7444,21 +7488,21 @@
         <v>27</v>
       </c>
       <c r="J151" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="K151" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
     </row>
     <row r="152" spans="1:11">
       <c r="A152" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="B152" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="C152" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="D152" t="s">
         <v>38</v>
@@ -7467,7 +7511,7 @@
         <v>31</v>
       </c>
       <c r="F152" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="H152" t="s">
         <v>26</v>
@@ -7476,21 +7520,21 @@
         <v>27</v>
       </c>
       <c r="J152" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="K152" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
     </row>
     <row r="153" spans="1:11">
       <c r="A153" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="B153" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="C153" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="D153" t="s">
         <v>38</v>
@@ -7499,30 +7543,30 @@
         <v>15</v>
       </c>
       <c r="F153" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H153" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I153" t="s">
         <v>27</v>
       </c>
       <c r="J153" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="K153" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
     </row>
     <row r="154" spans="1:11">
       <c r="A154" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="B154" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="C154" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D154" t="s">
         <v>38</v>
@@ -7531,7 +7575,7 @@
         <v>15</v>
       </c>
       <c r="F154" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="H154" t="s">
         <v>17</v>
@@ -7540,21 +7584,21 @@
         <v>34</v>
       </c>
       <c r="J154" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="K154" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
     </row>
     <row r="155" spans="1:11">
       <c r="A155" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="B155" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="C155" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D155" t="s">
         <v>38</v>
@@ -7563,62 +7607,62 @@
         <v>15</v>
       </c>
       <c r="F155" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H155" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I155" t="s">
         <v>34</v>
       </c>
       <c r="J155" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="K155" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
     </row>
     <row r="156" spans="1:11">
       <c r="A156" t="s">
+        <v>480</v>
+      </c>
+      <c r="B156" t="s">
+        <v>481</v>
+      </c>
+      <c r="C156" t="s">
+        <v>482</v>
+      </c>
+      <c r="D156" t="s">
+        <v>38</v>
+      </c>
+      <c r="E156" t="s">
+        <v>15</v>
+      </c>
+      <c r="F156" t="s">
         <v>483</v>
       </c>
-      <c r="B156" t="s">
-        <v>484</v>
-      </c>
-      <c r="C156" t="s">
-        <v>485</v>
-      </c>
-      <c r="D156" t="s">
-        <v>38</v>
-      </c>
-      <c r="E156" t="s">
-        <v>15</v>
-      </c>
-      <c r="F156" t="s">
-        <v>486</v>
-      </c>
       <c r="H156" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I156" t="s">
         <v>18</v>
       </c>
       <c r="J156" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="K156" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
     </row>
     <row r="157" spans="1:11">
       <c r="A157" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="B157" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="C157" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="D157" t="s">
         <v>38</v>
@@ -7627,7 +7671,7 @@
         <v>15</v>
       </c>
       <c r="F157" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="H157" t="s">
         <v>26</v>
@@ -7636,21 +7680,21 @@
         <v>18</v>
       </c>
       <c r="J157" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="K157" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
     </row>
     <row r="158" spans="1:11">
       <c r="A158" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="B158" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C158" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="D158" t="s">
         <v>38</v>
@@ -7659,39 +7703,39 @@
         <v>15</v>
       </c>
       <c r="F158" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H158" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I158" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J158" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="K158" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
     </row>
     <row r="159" spans="1:11">
       <c r="A159" t="s">
+        <v>490</v>
+      </c>
+      <c r="B159" t="s">
+        <v>491</v>
+      </c>
+      <c r="C159" t="s">
+        <v>492</v>
+      </c>
+      <c r="D159" t="s">
+        <v>24</v>
+      </c>
+      <c r="F159" t="s">
         <v>493</v>
       </c>
-      <c r="B159" t="s">
+      <c r="G159" t="s">
         <v>494</v>
-      </c>
-      <c r="C159" t="s">
-        <v>495</v>
-      </c>
-      <c r="D159" t="s">
-        <v>44</v>
-      </c>
-      <c r="F159" t="s">
-        <v>496</v>
-      </c>
-      <c r="G159" t="s">
-        <v>497</v>
       </c>
       <c r="H159" t="s">
         <v>17</v>
@@ -7700,21 +7744,21 @@
         <v>27</v>
       </c>
       <c r="J159" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="K159" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
     </row>
     <row r="160" spans="1:11">
       <c r="A160" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="B160" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="C160" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="D160" t="s">
         <v>38</v>
@@ -7723,7 +7767,7 @@
         <v>15</v>
       </c>
       <c r="F160" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H160" t="s">
         <v>26</v>
@@ -7732,21 +7776,21 @@
         <v>27</v>
       </c>
       <c r="J160" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="K160" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
     </row>
     <row r="161" spans="1:11">
       <c r="A161" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="B161" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="C161" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D161" t="s">
         <v>38</v>
@@ -7755,39 +7799,39 @@
         <v>31</v>
       </c>
       <c r="F161" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="H161" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I161" t="s">
         <v>34</v>
       </c>
       <c r="J161" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="K161" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
     </row>
     <row r="162" spans="1:11">
       <c r="A162" t="s">
+        <v>499</v>
+      </c>
+      <c r="B162" t="s">
+        <v>500</v>
+      </c>
+      <c r="C162" t="s">
+        <v>501</v>
+      </c>
+      <c r="D162" t="s">
+        <v>38</v>
+      </c>
+      <c r="E162" t="s">
+        <v>15</v>
+      </c>
+      <c r="F162" t="s">
         <v>502</v>
-      </c>
-      <c r="B162" t="s">
-        <v>503</v>
-      </c>
-      <c r="C162" t="s">
-        <v>504</v>
-      </c>
-      <c r="D162" t="s">
-        <v>38</v>
-      </c>
-      <c r="E162" t="s">
-        <v>15</v>
-      </c>
-      <c r="F162" t="s">
-        <v>505</v>
       </c>
       <c r="H162" t="s">
         <v>26</v>
@@ -7796,21 +7840,21 @@
         <v>34</v>
       </c>
       <c r="J162" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="K162" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
     </row>
     <row r="163" spans="1:11">
       <c r="A163" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="B163" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="C163" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="D163" t="s">
         <v>38</v>
@@ -7819,7 +7863,7 @@
         <v>31</v>
       </c>
       <c r="F163" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="H163" t="s">
         <v>26</v>
@@ -7828,21 +7872,21 @@
         <v>40</v>
       </c>
       <c r="J163" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="K163" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
     </row>
     <row r="164" spans="1:11">
       <c r="A164" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="B164" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="C164" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="D164" t="s">
         <v>38</v>
@@ -7851,30 +7895,30 @@
         <v>15</v>
       </c>
       <c r="F164" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="H164" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I164" t="s">
         <v>40</v>
       </c>
       <c r="J164" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="K164" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
     </row>
     <row r="165" spans="1:11">
       <c r="A165" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="B165" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="C165" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="D165" t="s">
         <v>38</v>
@@ -7883,30 +7927,30 @@
         <v>31</v>
       </c>
       <c r="F165" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="H165" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I165" t="s">
         <v>18</v>
       </c>
       <c r="J165" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="K165" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
     </row>
     <row r="166" spans="1:11">
       <c r="A166" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B166" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="C166" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D166" t="s">
         <v>38</v>
@@ -7915,7 +7959,7 @@
         <v>15</v>
       </c>
       <c r="F166" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H166" t="s">
         <v>26</v>
@@ -7924,53 +7968,53 @@
         <v>18</v>
       </c>
       <c r="J166" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="K166" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
     </row>
     <row r="167" spans="1:11">
       <c r="A167" t="s">
+        <v>426</v>
+      </c>
+      <c r="B167" t="s">
+        <v>509</v>
+      </c>
+      <c r="C167" t="s">
+        <v>428</v>
+      </c>
+      <c r="D167" t="s">
+        <v>38</v>
+      </c>
+      <c r="E167" t="s">
+        <v>15</v>
+      </c>
+      <c r="F167" t="s">
         <v>429</v>
       </c>
-      <c r="B167" t="s">
-        <v>512</v>
-      </c>
-      <c r="C167" t="s">
-        <v>431</v>
-      </c>
-      <c r="D167" t="s">
-        <v>38</v>
-      </c>
-      <c r="E167" t="s">
-        <v>15</v>
-      </c>
-      <c r="F167" t="s">
-        <v>432</v>
-      </c>
       <c r="H167" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I167" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J167" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K167" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
     </row>
     <row r="168" spans="1:11">
       <c r="A168" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="B168" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="C168" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="D168" t="s">
         <v>38</v>
@@ -7979,30 +8023,30 @@
         <v>15</v>
       </c>
       <c r="F168" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H168" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I168" t="s">
         <v>27</v>
       </c>
       <c r="J168" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="K168" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
     </row>
     <row r="169" spans="1:11">
       <c r="A169" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="B169" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="C169" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D169" t="s">
         <v>38</v>
@@ -8011,7 +8055,7 @@
         <v>15</v>
       </c>
       <c r="F169" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H169" t="s">
         <v>17</v>
@@ -8020,21 +8064,21 @@
         <v>27</v>
       </c>
       <c r="J169" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="K169" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
     </row>
     <row r="170" spans="1:11">
       <c r="A170" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="B170" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="C170" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D170" t="s">
         <v>38</v>
@@ -8043,7 +8087,7 @@
         <v>15</v>
       </c>
       <c r="F170" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H170" t="s">
         <v>17</v>
@@ -8052,21 +8096,21 @@
         <v>34</v>
       </c>
       <c r="J170" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="K170" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
     </row>
     <row r="171" spans="1:11">
       <c r="A171" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B171" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="C171" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="D171" t="s">
         <v>38</v>
@@ -8075,30 +8119,30 @@
         <v>15</v>
       </c>
       <c r="F171" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="H171" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I171" t="s">
         <v>34</v>
       </c>
       <c r="J171" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="K171" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
     </row>
     <row r="172" spans="1:11">
       <c r="A172" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B172" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="C172" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D172" t="s">
         <v>38</v>
@@ -8107,30 +8151,30 @@
         <v>31</v>
       </c>
       <c r="F172" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H172" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I172" t="s">
         <v>40</v>
       </c>
       <c r="J172" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="K172" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
     </row>
     <row r="173" spans="1:11">
       <c r="A173" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="B173" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="C173" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D173" t="s">
         <v>38</v>
@@ -8139,7 +8183,7 @@
         <v>15</v>
       </c>
       <c r="F173" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H173" t="s">
         <v>26</v>
@@ -8148,41 +8192,44 @@
         <v>40</v>
       </c>
       <c r="J173" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="K173" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
     </row>
     <row r="174" spans="1:11">
       <c r="A174" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="B174" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="C174" t="s">
-        <v>233</v>
+        <v>230</v>
+      </c>
+      <c r="D174" t="s">
+        <v>24</v>
       </c>
       <c r="H174" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I174" t="s">
         <v>18</v>
       </c>
       <c r="J174" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="K174" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
     </row>
     <row r="175" spans="1:11">
       <c r="A175" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B175" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="C175" t="s">
         <v>37</v>
@@ -8203,21 +8250,21 @@
         <v>18</v>
       </c>
       <c r="J175" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="K175" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
     </row>
     <row r="176" spans="1:11">
       <c r="A176" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="B176" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="C176" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="D176" t="s">
         <v>38</v>
@@ -8226,30 +8273,30 @@
         <v>15</v>
       </c>
       <c r="F176" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="H176" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I176" t="s">
         <v>27</v>
       </c>
       <c r="J176" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="K176" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
     </row>
     <row r="177" spans="1:11">
       <c r="A177" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B177" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="C177" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D177" t="s">
         <v>38</v>
@@ -8258,7 +8305,7 @@
         <v>15</v>
       </c>
       <c r="F177" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="H177" t="s">
         <v>26</v>
@@ -8267,62 +8314,62 @@
         <v>27</v>
       </c>
       <c r="J177" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="K177" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
     </row>
     <row r="178" spans="1:11">
       <c r="A178" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="B178" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="C178" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D178" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="F178" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="G178" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H178" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I178" t="s">
         <v>34</v>
       </c>
       <c r="J178" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="K178" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
     </row>
     <row r="179" spans="1:11">
       <c r="A179" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="B179" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="C179" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="D179" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="E179" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F179" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="H179" t="s">
         <v>26</v>
@@ -8331,18 +8378,18 @@
         <v>34</v>
       </c>
       <c r="J179" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="K179" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
     </row>
     <row r="180" spans="1:11">
       <c r="A180" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B180" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="C180" t="s">
         <v>30</v>
@@ -8360,27 +8407,27 @@
         <v>33</v>
       </c>
       <c r="H180" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I180" t="s">
         <v>34</v>
       </c>
       <c r="J180" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="K180" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
     </row>
     <row r="181" spans="1:11">
       <c r="A181" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="B181" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="C181" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="D181" t="s">
         <v>14</v>
@@ -8389,74 +8436,74 @@
         <v>15</v>
       </c>
       <c r="F181" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="H181" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I181" t="s">
         <v>40</v>
       </c>
       <c r="J181" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="K181" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
     </row>
     <row r="182" spans="1:11">
       <c r="A182" t="s">
+        <v>538</v>
+      </c>
+      <c r="B182" t="s">
+        <v>539</v>
+      </c>
+      <c r="C182" t="s">
+        <v>540</v>
+      </c>
+      <c r="D182" t="s">
+        <v>24</v>
+      </c>
+      <c r="F182" t="s">
         <v>541</v>
       </c>
-      <c r="B182" t="s">
+      <c r="G182" t="s">
         <v>542</v>
       </c>
-      <c r="C182" t="s">
-        <v>543</v>
-      </c>
-      <c r="D182" t="s">
-        <v>44</v>
-      </c>
-      <c r="F182" t="s">
-        <v>544</v>
-      </c>
-      <c r="G182" t="s">
-        <v>545</v>
-      </c>
       <c r="H182" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I182" t="s">
         <v>18</v>
       </c>
       <c r="J182" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="K182" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
     </row>
     <row r="183" spans="1:11">
       <c r="A183" t="s">
+        <v>544</v>
+      </c>
+      <c r="B183" t="s">
+        <v>545</v>
+      </c>
+      <c r="C183" t="s">
+        <v>546</v>
+      </c>
+      <c r="D183" t="s">
+        <v>24</v>
+      </c>
+      <c r="E183" t="s">
+        <v>98</v>
+      </c>
+      <c r="F183" t="s">
         <v>547</v>
       </c>
-      <c r="B183" t="s">
+      <c r="G183" t="s">
         <v>548</v>
-      </c>
-      <c r="C183" t="s">
-        <v>549</v>
-      </c>
-      <c r="D183" t="s">
-        <v>44</v>
-      </c>
-      <c r="E183" t="s">
-        <v>100</v>
-      </c>
-      <c r="F183" t="s">
-        <v>550</v>
-      </c>
-      <c r="G183" t="s">
-        <v>551</v>
       </c>
       <c r="H183" t="s">
         <v>17</v>
@@ -8465,21 +8512,21 @@
         <v>18</v>
       </c>
       <c r="J183" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="K183" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
     </row>
     <row r="184" spans="1:11">
       <c r="A184" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B184" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="C184" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D184" t="s">
         <v>38</v>
@@ -8488,7 +8535,7 @@
         <v>15</v>
       </c>
       <c r="F184" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H184" t="s">
         <v>26</v>
@@ -8497,21 +8544,21 @@
         <v>18</v>
       </c>
       <c r="J184" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="K184" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
     </row>
     <row r="185" spans="1:11">
       <c r="A185" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="B185" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="C185" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="D185" t="s">
         <v>38</v>
@@ -8520,62 +8567,62 @@
         <v>15</v>
       </c>
       <c r="F185" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="H185" t="s">
         <v>26</v>
       </c>
       <c r="I185" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J185" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="K185" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
     </row>
     <row r="186" spans="1:11">
       <c r="A186" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="B186" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="C186" t="s">
+        <v>108</v>
+      </c>
+      <c r="D186" t="s">
+        <v>38</v>
+      </c>
+      <c r="E186" t="s">
+        <v>15</v>
+      </c>
+      <c r="F186" t="s">
+        <v>109</v>
+      </c>
+      <c r="H186" t="s">
         <v>110</v>
-      </c>
-      <c r="D186" t="s">
-        <v>38</v>
-      </c>
-      <c r="E186" t="s">
-        <v>15</v>
-      </c>
-      <c r="F186" t="s">
-        <v>111</v>
-      </c>
-      <c r="H186" t="s">
-        <v>112</v>
       </c>
       <c r="I186" t="s">
         <v>27</v>
       </c>
       <c r="J186" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="K186" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
     </row>
     <row r="187" spans="1:11">
       <c r="A187" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="B187" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="C187" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D187" t="s">
         <v>38</v>
@@ -8584,7 +8631,7 @@
         <v>15</v>
       </c>
       <c r="F187" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H187" t="s">
         <v>26</v>
@@ -8593,21 +8640,21 @@
         <v>27</v>
       </c>
       <c r="J187" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="K187" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
     </row>
     <row r="188" spans="1:11">
       <c r="A188" t="s">
+        <v>101</v>
+      </c>
+      <c r="B188" t="s">
+        <v>556</v>
+      </c>
+      <c r="C188" t="s">
         <v>103</v>
-      </c>
-      <c r="B188" t="s">
-        <v>559</v>
-      </c>
-      <c r="C188" t="s">
-        <v>105</v>
       </c>
       <c r="D188" t="s">
         <v>38</v>
@@ -8616,30 +8663,30 @@
         <v>31</v>
       </c>
       <c r="F188" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H188" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I188" t="s">
         <v>27</v>
       </c>
       <c r="J188" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="K188" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
     </row>
     <row r="189" spans="1:11">
       <c r="A189" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="B189" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="C189" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D189" t="s">
         <v>38</v>
@@ -8648,30 +8695,30 @@
         <v>15</v>
       </c>
       <c r="F189" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="H189" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I189" t="s">
         <v>34</v>
       </c>
       <c r="J189" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="K189" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
     </row>
     <row r="190" spans="1:11">
       <c r="A190" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="B190" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="C190" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D190" t="s">
         <v>38</v>
@@ -8680,7 +8727,7 @@
         <v>15</v>
       </c>
       <c r="F190" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="H190" t="s">
         <v>26</v>
@@ -8689,10 +8736,10 @@
         <v>40</v>
       </c>
       <c r="J190" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="K190" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
     </row>
   </sheetData>

--- a/DATA-ENS-2026-2027_surveillances.xlsx
+++ b/DATA-ENS-2026-2027_surveillances.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1885" uniqueCount="559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1885" uniqueCount="558">
   <si>
     <t>Enseignements</t>
   </si>
@@ -74,7 +74,7 @@
     <t>OUKLI MIMOUNA</t>
   </si>
   <si>
-    <t>Permanente</t>
+    <t>Permanent</t>
   </si>
   <si>
     <t>Pr</t>
@@ -144,9 +144,6 @@
   </si>
   <si>
     <t>LALEDJ NADJET</t>
-  </si>
-  <si>
-    <t>Permanent</t>
   </si>
   <si>
     <t>nadjet_69@hotmail.fr</t>
@@ -2852,19 +2849,19 @@
         <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="E5" t="s">
         <v>31</v>
       </c>
       <c r="F5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H5" t="s">
         <v>17</v>
       </c>
       <c r="I5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J5" t="s">
         <v>19</v>
@@ -2875,28 +2872,28 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" t="s">
         <v>41</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>42</v>
-      </c>
-      <c r="C6" t="s">
-        <v>43</v>
       </c>
       <c r="D6" t="s">
         <v>24</v>
       </c>
       <c r="F6" t="s">
+        <v>43</v>
+      </c>
+      <c r="G6" t="s">
         <v>44</v>
-      </c>
-      <c r="G6" t="s">
-        <v>45</v>
       </c>
       <c r="H6" t="s">
         <v>26</v>
       </c>
       <c r="I6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J6" t="s">
         <v>19</v>
@@ -2907,39 +2904,39 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" t="s">
         <v>46</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>47</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" t="s">
         <v>48</v>
-      </c>
-      <c r="D7" t="s">
-        <v>38</v>
-      </c>
-      <c r="H7" t="s">
-        <v>49</v>
       </c>
       <c r="I7" t="s">
         <v>18</v>
       </c>
       <c r="J7" t="s">
+        <v>49</v>
+      </c>
+      <c r="K7" t="s">
         <v>50</v>
-      </c>
-      <c r="K7" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" t="s">
         <v>52</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>53</v>
-      </c>
-      <c r="C8" t="s">
-        <v>54</v>
       </c>
       <c r="D8" t="s">
         <v>24</v>
@@ -2948,33 +2945,33 @@
         <v>26</v>
       </c>
       <c r="I8" t="s">
+        <v>54</v>
+      </c>
+      <c r="J8" t="s">
         <v>55</v>
       </c>
-      <c r="J8" t="s">
-        <v>56</v>
-      </c>
       <c r="K8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9" t="s">
         <v>57</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>58</v>
-      </c>
-      <c r="C9" t="s">
-        <v>59</v>
       </c>
       <c r="D9" t="s">
         <v>24</v>
       </c>
       <c r="F9" t="s">
+        <v>59</v>
+      </c>
+      <c r="G9" t="s">
         <v>60</v>
-      </c>
-      <c r="G9" t="s">
-        <v>61</v>
       </c>
       <c r="H9" t="s">
         <v>17</v>
@@ -2983,21 +2980,21 @@
         <v>27</v>
       </c>
       <c r="J9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10" t="s">
         <v>62</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>63</v>
-      </c>
-      <c r="C10" t="s">
-        <v>64</v>
       </c>
       <c r="D10" t="s">
         <v>24</v>
@@ -3006,33 +3003,33 @@
         <v>31</v>
       </c>
       <c r="F10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I10" t="s">
         <v>34</v>
       </c>
       <c r="J10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" t="s">
         <v>66</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>67</v>
       </c>
-      <c r="C11" t="s">
-        <v>68</v>
-      </c>
       <c r="D11" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="H11" t="s">
         <v>17</v>
@@ -3041,24 +3038,24 @@
         <v>34</v>
       </c>
       <c r="J11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B12" t="s">
         <v>69</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>70</v>
       </c>
-      <c r="C12" t="s">
-        <v>71</v>
-      </c>
       <c r="D12" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="H12" t="s">
         <v>26</v>
@@ -3067,99 +3064,99 @@
         <v>34</v>
       </c>
       <c r="J12" t="s">
+        <v>49</v>
+      </c>
+      <c r="K12" t="s">
         <v>50</v>
-      </c>
-      <c r="K12" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
+        <v>71</v>
+      </c>
+      <c r="B13" t="s">
         <v>72</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>73</v>
-      </c>
-      <c r="C13" t="s">
-        <v>74</v>
       </c>
       <c r="D13" t="s">
         <v>24</v>
       </c>
       <c r="H13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
+        <v>74</v>
+      </c>
+      <c r="B14" t="s">
         <v>75</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>76</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
+        <v>14</v>
+      </c>
+      <c r="H14" t="s">
         <v>77</v>
       </c>
-      <c r="D14" t="s">
-        <v>38</v>
-      </c>
-      <c r="H14" t="s">
-        <v>78</v>
-      </c>
       <c r="I14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C15" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H15" t="s">
         <v>48</v>
-      </c>
-      <c r="D15" t="s">
-        <v>38</v>
-      </c>
-      <c r="H15" t="s">
-        <v>49</v>
       </c>
       <c r="I15" t="s">
         <v>18</v>
       </c>
       <c r="J15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D16" t="s">
         <v>24</v>
@@ -3168,33 +3165,33 @@
         <v>26</v>
       </c>
       <c r="I16" t="s">
+        <v>54</v>
+      </c>
+      <c r="J16" t="s">
         <v>55</v>
       </c>
-      <c r="J16" t="s">
-        <v>56</v>
-      </c>
       <c r="K16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D17" t="s">
         <v>24</v>
       </c>
       <c r="F17" t="s">
+        <v>59</v>
+      </c>
+      <c r="G17" t="s">
         <v>60</v>
-      </c>
-      <c r="G17" t="s">
-        <v>61</v>
       </c>
       <c r="H17" t="s">
         <v>17</v>
@@ -3203,21 +3200,21 @@
         <v>27</v>
       </c>
       <c r="J17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B18" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C18" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D18" t="s">
         <v>24</v>
@@ -3226,33 +3223,33 @@
         <v>31</v>
       </c>
       <c r="F18" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I18" t="s">
         <v>34</v>
       </c>
       <c r="J18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K18" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B19" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D19" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="H19" t="s">
         <v>17</v>
@@ -3261,24 +3258,24 @@
         <v>34</v>
       </c>
       <c r="J19" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K19" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B20" t="s">
+        <v>84</v>
+      </c>
+      <c r="C20" t="s">
         <v>85</v>
       </c>
-      <c r="C20" t="s">
-        <v>86</v>
-      </c>
       <c r="D20" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="H20" t="s">
         <v>26</v>
@@ -3287,79 +3284,79 @@
         <v>34</v>
       </c>
       <c r="J20" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B21" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C21" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D21" t="s">
         <v>24</v>
       </c>
       <c r="H21" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K21" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B22" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C22" t="s">
+        <v>76</v>
+      </c>
+      <c r="D22" t="s">
+        <v>14</v>
+      </c>
+      <c r="H22" t="s">
         <v>77</v>
       </c>
-      <c r="D22" t="s">
-        <v>38</v>
-      </c>
-      <c r="H22" t="s">
-        <v>78</v>
-      </c>
       <c r="I22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J22" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K22" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
+        <v>88</v>
+      </c>
+      <c r="B23" t="s">
         <v>89</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>90</v>
-      </c>
-      <c r="C23" t="s">
-        <v>91</v>
       </c>
       <c r="D23" t="s">
         <v>24</v>
       </c>
       <c r="F23" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H23" t="s">
         <v>26</v>
@@ -3368,129 +3365,129 @@
         <v>18</v>
       </c>
       <c r="J23" t="s">
+        <v>92</v>
+      </c>
+      <c r="K23" t="s">
         <v>93</v>
-      </c>
-      <c r="K23" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" t="s">
+        <v>94</v>
+      </c>
+      <c r="B24" t="s">
         <v>95</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>96</v>
-      </c>
-      <c r="C24" t="s">
-        <v>97</v>
       </c>
       <c r="D24" t="s">
         <v>24</v>
       </c>
       <c r="E24" t="s">
+        <v>97</v>
+      </c>
+      <c r="F24" t="s">
         <v>98</v>
       </c>
-      <c r="F24" t="s">
+      <c r="G24" t="s">
         <v>99</v>
-      </c>
-      <c r="G24" t="s">
-        <v>100</v>
       </c>
       <c r="H24" t="s">
         <v>26</v>
       </c>
       <c r="I24" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J24" t="s">
+        <v>92</v>
+      </c>
+      <c r="K24" t="s">
         <v>93</v>
-      </c>
-      <c r="K24" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" t="s">
+        <v>100</v>
+      </c>
+      <c r="B25" t="s">
         <v>101</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>102</v>
       </c>
-      <c r="C25" t="s">
-        <v>103</v>
-      </c>
       <c r="D25" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="E25" t="s">
         <v>31</v>
       </c>
       <c r="F25" t="s">
+        <v>103</v>
+      </c>
+      <c r="H25" t="s">
         <v>104</v>
       </c>
-      <c r="H25" t="s">
-        <v>105</v>
-      </c>
       <c r="I25" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J25" t="s">
+        <v>92</v>
+      </c>
+      <c r="K25" t="s">
         <v>93</v>
-      </c>
-      <c r="K25" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" t="s">
+        <v>105</v>
+      </c>
+      <c r="B26" t="s">
         <v>106</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
         <v>107</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" t="s">
+        <v>15</v>
+      </c>
+      <c r="F26" t="s">
         <v>108</v>
       </c>
-      <c r="D26" t="s">
-        <v>38</v>
-      </c>
-      <c r="E26" t="s">
-        <v>15</v>
-      </c>
-      <c r="F26" t="s">
+      <c r="H26" t="s">
         <v>109</v>
-      </c>
-      <c r="H26" t="s">
-        <v>110</v>
       </c>
       <c r="I26" t="s">
         <v>27</v>
       </c>
       <c r="J26" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K26" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" t="s">
+        <v>111</v>
+      </c>
+      <c r="B27" t="s">
         <v>112</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
         <v>113</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" t="s">
+        <v>15</v>
+      </c>
+      <c r="F27" t="s">
         <v>114</v>
-      </c>
-      <c r="D27" t="s">
-        <v>38</v>
-      </c>
-      <c r="E27" t="s">
-        <v>15</v>
-      </c>
-      <c r="F27" t="s">
-        <v>115</v>
       </c>
       <c r="H27" t="s">
         <v>26</v>
@@ -3499,18 +3496,18 @@
         <v>27</v>
       </c>
       <c r="J27" t="s">
+        <v>92</v>
+      </c>
+      <c r="K27" t="s">
         <v>93</v>
-      </c>
-      <c r="K27" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" t="s">
+        <v>115</v>
+      </c>
+      <c r="B28" t="s">
         <v>116</v>
-      </c>
-      <c r="B28" t="s">
-        <v>117</v>
       </c>
       <c r="C28" t="s">
         <v>13</v>
@@ -3525,36 +3522,36 @@
         <v>16</v>
       </c>
       <c r="H28" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I28" t="s">
         <v>34</v>
       </c>
       <c r="J28" t="s">
+        <v>92</v>
+      </c>
+      <c r="K28" t="s">
         <v>93</v>
-      </c>
-      <c r="K28" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" t="s">
+        <v>117</v>
+      </c>
+      <c r="B29" t="s">
         <v>118</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>119</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" t="s">
+        <v>15</v>
+      </c>
+      <c r="F29" t="s">
         <v>120</v>
-      </c>
-      <c r="D29" t="s">
-        <v>38</v>
-      </c>
-      <c r="E29" t="s">
-        <v>15</v>
-      </c>
-      <c r="F29" t="s">
-        <v>121</v>
       </c>
       <c r="H29" t="s">
         <v>26</v>
@@ -3563,321 +3560,321 @@
         <v>34</v>
       </c>
       <c r="J29" t="s">
+        <v>92</v>
+      </c>
+      <c r="K29" t="s">
         <v>93</v>
-      </c>
-      <c r="K29" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" t="s">
+        <v>121</v>
+      </c>
+      <c r="B30" t="s">
         <v>122</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
         <v>123</v>
-      </c>
-      <c r="C30" t="s">
-        <v>124</v>
       </c>
       <c r="D30" t="s">
         <v>24</v>
       </c>
       <c r="F30" t="s">
+        <v>124</v>
+      </c>
+      <c r="G30" t="s">
         <v>125</v>
       </c>
-      <c r="G30" t="s">
-        <v>126</v>
-      </c>
       <c r="H30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I30" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J30" t="s">
+        <v>92</v>
+      </c>
+      <c r="K30" t="s">
         <v>93</v>
-      </c>
-      <c r="K30" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" t="s">
+        <v>126</v>
+      </c>
+      <c r="B31" t="s">
         <v>127</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
         <v>128</v>
-      </c>
-      <c r="C31" t="s">
-        <v>129</v>
       </c>
       <c r="D31" t="s">
         <v>24</v>
       </c>
       <c r="E31" t="s">
+        <v>129</v>
+      </c>
+      <c r="F31" t="s">
         <v>130</v>
       </c>
-      <c r="F31" t="s">
+      <c r="G31" t="s">
         <v>131</v>
       </c>
-      <c r="G31" t="s">
+      <c r="H31" t="s">
+        <v>109</v>
+      </c>
+      <c r="I31" t="s">
+        <v>54</v>
+      </c>
+      <c r="J31" t="s">
         <v>132</v>
       </c>
-      <c r="H31" t="s">
-        <v>110</v>
-      </c>
-      <c r="I31" t="s">
-        <v>55</v>
-      </c>
-      <c r="J31" t="s">
+      <c r="K31" t="s">
         <v>133</v>
-      </c>
-      <c r="K31" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" t="s">
+        <v>134</v>
+      </c>
+      <c r="B32" t="s">
         <v>135</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" t="s">
         <v>136</v>
-      </c>
-      <c r="C32" t="s">
-        <v>137</v>
       </c>
       <c r="D32" t="s">
         <v>24</v>
       </c>
       <c r="F32" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H32" t="s">
         <v>26</v>
       </c>
       <c r="I32" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J32" t="s">
+        <v>132</v>
+      </c>
+      <c r="K32" t="s">
         <v>133</v>
-      </c>
-      <c r="K32" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" t="s">
+        <v>138</v>
+      </c>
+      <c r="B33" t="s">
         <v>139</v>
       </c>
-      <c r="B33" t="s">
-        <v>140</v>
-      </c>
       <c r="C33" t="s">
+        <v>107</v>
+      </c>
+      <c r="D33" t="s">
+        <v>14</v>
+      </c>
+      <c r="E33" t="s">
+        <v>15</v>
+      </c>
+      <c r="F33" t="s">
         <v>108</v>
       </c>
-      <c r="D33" t="s">
-        <v>38</v>
-      </c>
-      <c r="E33" t="s">
-        <v>15</v>
-      </c>
-      <c r="F33" t="s">
+      <c r="H33" t="s">
         <v>109</v>
-      </c>
-      <c r="H33" t="s">
-        <v>110</v>
       </c>
       <c r="I33" t="s">
         <v>27</v>
       </c>
       <c r="J33" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="K33" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" t="s">
+        <v>141</v>
+      </c>
+      <c r="B34" t="s">
         <v>142</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
         <v>143</v>
       </c>
-      <c r="C34" t="s">
+      <c r="D34" t="s">
+        <v>14</v>
+      </c>
+      <c r="E34" t="s">
+        <v>15</v>
+      </c>
+      <c r="F34" t="s">
         <v>144</v>
       </c>
-      <c r="D34" t="s">
-        <v>38</v>
-      </c>
-      <c r="E34" t="s">
-        <v>15</v>
-      </c>
-      <c r="F34" t="s">
-        <v>145</v>
-      </c>
       <c r="H34" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I34" t="s">
         <v>27</v>
       </c>
       <c r="J34" t="s">
+        <v>132</v>
+      </c>
+      <c r="K34" t="s">
         <v>133</v>
-      </c>
-      <c r="K34" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" t="s">
+        <v>145</v>
+      </c>
+      <c r="B35" t="s">
         <v>146</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" t="s">
         <v>147</v>
       </c>
-      <c r="C35" t="s">
+      <c r="D35" t="s">
+        <v>14</v>
+      </c>
+      <c r="E35" t="s">
+        <v>15</v>
+      </c>
+      <c r="F35" t="s">
         <v>148</v>
       </c>
-      <c r="D35" t="s">
-        <v>38</v>
-      </c>
-      <c r="E35" t="s">
-        <v>15</v>
-      </c>
-      <c r="F35" t="s">
-        <v>149</v>
-      </c>
       <c r="H35" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I35" t="s">
         <v>34</v>
       </c>
       <c r="J35" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K35" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" t="s">
+        <v>150</v>
+      </c>
+      <c r="B36" t="s">
         <v>151</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
         <v>152</v>
-      </c>
-      <c r="C36" t="s">
-        <v>153</v>
       </c>
       <c r="D36" t="s">
         <v>24</v>
       </c>
       <c r="E36" t="s">
+        <v>153</v>
+      </c>
+      <c r="F36" t="s">
         <v>154</v>
       </c>
-      <c r="F36" t="s">
+      <c r="G36" t="s">
         <v>155</v>
-      </c>
-      <c r="G36" t="s">
-        <v>156</v>
       </c>
       <c r="H36" t="s">
         <v>17</v>
       </c>
       <c r="I36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J36" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K36" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="37" spans="1:11">
       <c r="A37" t="s">
+        <v>156</v>
+      </c>
+      <c r="B37" t="s">
         <v>157</v>
       </c>
-      <c r="B37" t="s">
-        <v>158</v>
-      </c>
       <c r="C37" t="s">
+        <v>119</v>
+      </c>
+      <c r="D37" t="s">
+        <v>14</v>
+      </c>
+      <c r="E37" t="s">
+        <v>15</v>
+      </c>
+      <c r="F37" t="s">
         <v>120</v>
-      </c>
-      <c r="D37" t="s">
-        <v>38</v>
-      </c>
-      <c r="E37" t="s">
-        <v>15</v>
-      </c>
-      <c r="F37" t="s">
-        <v>121</v>
       </c>
       <c r="H37" t="s">
         <v>26</v>
       </c>
       <c r="I37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J37" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K37" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="38" spans="1:11">
       <c r="A38" t="s">
+        <v>159</v>
+      </c>
+      <c r="B38" t="s">
         <v>160</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" t="s">
         <v>161</v>
       </c>
-      <c r="C38" t="s">
+      <c r="D38" t="s">
+        <v>14</v>
+      </c>
+      <c r="E38" t="s">
         <v>162</v>
       </c>
-      <c r="D38" t="s">
-        <v>14</v>
-      </c>
-      <c r="E38" t="s">
+      <c r="F38" t="s">
         <v>163</v>
       </c>
-      <c r="F38" t="s">
-        <v>164</v>
-      </c>
       <c r="H38" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I38" t="s">
         <v>18</v>
       </c>
       <c r="J38" t="s">
+        <v>164</v>
+      </c>
+      <c r="K38" t="s">
         <v>165</v>
-      </c>
-      <c r="K38" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="39" spans="1:11">
       <c r="A39" t="s">
+        <v>166</v>
+      </c>
+      <c r="B39" t="s">
         <v>167</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" t="s">
         <v>168</v>
       </c>
-      <c r="C39" t="s">
+      <c r="D39" t="s">
+        <v>14</v>
+      </c>
+      <c r="E39" t="s">
+        <v>15</v>
+      </c>
+      <c r="F39" t="s">
         <v>169</v>
-      </c>
-      <c r="D39" t="s">
-        <v>38</v>
-      </c>
-      <c r="E39" t="s">
-        <v>15</v>
-      </c>
-      <c r="F39" t="s">
-        <v>170</v>
       </c>
       <c r="H39" t="s">
         <v>17</v>
@@ -3886,30 +3883,30 @@
         <v>18</v>
       </c>
       <c r="J39" t="s">
+        <v>164</v>
+      </c>
+      <c r="K39" t="s">
         <v>165</v>
-      </c>
-      <c r="K39" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="40" spans="1:11">
       <c r="A40" t="s">
+        <v>170</v>
+      </c>
+      <c r="B40" t="s">
         <v>171</v>
       </c>
-      <c r="B40" t="s">
-        <v>172</v>
-      </c>
       <c r="C40" t="s">
+        <v>147</v>
+      </c>
+      <c r="D40" t="s">
+        <v>14</v>
+      </c>
+      <c r="E40" t="s">
+        <v>15</v>
+      </c>
+      <c r="F40" t="s">
         <v>148</v>
-      </c>
-      <c r="D40" t="s">
-        <v>38</v>
-      </c>
-      <c r="E40" t="s">
-        <v>15</v>
-      </c>
-      <c r="F40" t="s">
-        <v>149</v>
       </c>
       <c r="H40" t="s">
         <v>26</v>
@@ -3918,62 +3915,62 @@
         <v>18</v>
       </c>
       <c r="J40" t="s">
+        <v>164</v>
+      </c>
+      <c r="K40" t="s">
         <v>165</v>
-      </c>
-      <c r="K40" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="41" spans="1:11">
       <c r="A41" t="s">
+        <v>172</v>
+      </c>
+      <c r="B41" t="s">
         <v>173</v>
       </c>
-      <c r="B41" t="s">
+      <c r="C41" t="s">
         <v>174</v>
       </c>
-      <c r="C41" t="s">
-        <v>175</v>
-      </c>
       <c r="D41" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="E41" t="s">
         <v>31</v>
       </c>
       <c r="F41" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H41" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I41" t="s">
         <v>27</v>
       </c>
       <c r="J41" t="s">
+        <v>164</v>
+      </c>
+      <c r="K41" t="s">
         <v>165</v>
-      </c>
-      <c r="K41" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="42" spans="1:11">
       <c r="A42" t="s">
+        <v>176</v>
+      </c>
+      <c r="B42" t="s">
         <v>177</v>
       </c>
-      <c r="B42" t="s">
+      <c r="C42" t="s">
         <v>178</v>
       </c>
-      <c r="C42" t="s">
+      <c r="D42" t="s">
+        <v>14</v>
+      </c>
+      <c r="E42" t="s">
+        <v>15</v>
+      </c>
+      <c r="F42" t="s">
         <v>179</v>
-      </c>
-      <c r="D42" t="s">
-        <v>38</v>
-      </c>
-      <c r="E42" t="s">
-        <v>15</v>
-      </c>
-      <c r="F42" t="s">
-        <v>180</v>
       </c>
       <c r="H42" t="s">
         <v>26</v>
@@ -3982,21 +3979,21 @@
         <v>27</v>
       </c>
       <c r="J42" t="s">
+        <v>164</v>
+      </c>
+      <c r="K42" t="s">
         <v>165</v>
-      </c>
-      <c r="K42" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="43" spans="1:11">
       <c r="A43" t="s">
+        <v>180</v>
+      </c>
+      <c r="B43" t="s">
         <v>181</v>
       </c>
-      <c r="B43" t="s">
+      <c r="C43" t="s">
         <v>182</v>
-      </c>
-      <c r="C43" t="s">
-        <v>183</v>
       </c>
       <c r="D43" t="s">
         <v>14</v>
@@ -4005,39 +4002,39 @@
         <v>31</v>
       </c>
       <c r="F43" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H43" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I43" t="s">
         <v>34</v>
       </c>
       <c r="J43" t="s">
+        <v>164</v>
+      </c>
+      <c r="K43" t="s">
         <v>165</v>
-      </c>
-      <c r="K43" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="44" spans="1:11">
       <c r="A44" t="s">
+        <v>184</v>
+      </c>
+      <c r="B44" t="s">
         <v>185</v>
       </c>
-      <c r="B44" t="s">
+      <c r="C44" t="s">
         <v>186</v>
       </c>
-      <c r="C44" t="s">
-        <v>187</v>
-      </c>
       <c r="D44" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="E44" t="s">
         <v>31</v>
       </c>
       <c r="F44" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H44" t="s">
         <v>26</v>
@@ -4046,59 +4043,59 @@
         <v>34</v>
       </c>
       <c r="J44" t="s">
+        <v>164</v>
+      </c>
+      <c r="K44" t="s">
         <v>165</v>
-      </c>
-      <c r="K44" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="45" spans="1:11">
       <c r="A45" t="s">
+        <v>188</v>
+      </c>
+      <c r="B45" t="s">
         <v>189</v>
       </c>
-      <c r="B45" t="s">
-        <v>190</v>
-      </c>
       <c r="C45" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D45" t="s">
         <v>24</v>
       </c>
       <c r="H45" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I45" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J45" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="K45" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="46" spans="1:11">
       <c r="A46" t="s">
+        <v>191</v>
+      </c>
+      <c r="B46" t="s">
         <v>192</v>
       </c>
-      <c r="B46" t="s">
+      <c r="C46" t="s">
         <v>193</v>
-      </c>
-      <c r="C46" t="s">
-        <v>194</v>
       </c>
       <c r="D46" t="s">
         <v>24</v>
       </c>
       <c r="E46" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F46" t="s">
+        <v>194</v>
+      </c>
+      <c r="G46" t="s">
         <v>195</v>
-      </c>
-      <c r="G46" t="s">
-        <v>196</v>
       </c>
       <c r="H46" t="s">
         <v>17</v>
@@ -4107,30 +4104,30 @@
         <v>18</v>
       </c>
       <c r="J46" t="s">
+        <v>196</v>
+      </c>
+      <c r="K46" t="s">
         <v>197</v>
-      </c>
-      <c r="K46" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="47" spans="1:11">
       <c r="A47" t="s">
+        <v>198</v>
+      </c>
+      <c r="B47" t="s">
         <v>199</v>
       </c>
-      <c r="B47" t="s">
+      <c r="C47" t="s">
         <v>200</v>
       </c>
-      <c r="C47" t="s">
+      <c r="D47" t="s">
+        <v>14</v>
+      </c>
+      <c r="E47" t="s">
+        <v>15</v>
+      </c>
+      <c r="F47" t="s">
         <v>201</v>
-      </c>
-      <c r="D47" t="s">
-        <v>38</v>
-      </c>
-      <c r="E47" t="s">
-        <v>15</v>
-      </c>
-      <c r="F47" t="s">
-        <v>202</v>
       </c>
       <c r="H47" t="s">
         <v>26</v>
@@ -4139,132 +4136,132 @@
         <v>18</v>
       </c>
       <c r="J47" t="s">
+        <v>196</v>
+      </c>
+      <c r="K47" t="s">
         <v>197</v>
-      </c>
-      <c r="K47" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="48" spans="1:11">
       <c r="A48" t="s">
+        <v>202</v>
+      </c>
+      <c r="B48" t="s">
         <v>203</v>
       </c>
-      <c r="B48" t="s">
+      <c r="C48" t="s">
         <v>204</v>
       </c>
-      <c r="C48" t="s">
+      <c r="D48" t="s">
+        <v>14</v>
+      </c>
+      <c r="E48" t="s">
+        <v>15</v>
+      </c>
+      <c r="F48" t="s">
         <v>205</v>
       </c>
-      <c r="D48" t="s">
-        <v>38</v>
-      </c>
-      <c r="E48" t="s">
-        <v>15</v>
-      </c>
-      <c r="F48" t="s">
+      <c r="G48" t="s">
         <v>206</v>
       </c>
-      <c r="G48" t="s">
-        <v>207</v>
-      </c>
       <c r="H48" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I48" t="s">
         <v>18</v>
       </c>
       <c r="J48" t="s">
+        <v>196</v>
+      </c>
+      <c r="K48" t="s">
         <v>197</v>
-      </c>
-      <c r="K48" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="49" spans="1:11">
       <c r="A49" t="s">
+        <v>207</v>
+      </c>
+      <c r="B49" t="s">
         <v>208</v>
       </c>
-      <c r="B49" t="s">
+      <c r="C49" t="s">
         <v>209</v>
-      </c>
-      <c r="C49" t="s">
-        <v>210</v>
       </c>
       <c r="D49" t="s">
         <v>24</v>
       </c>
       <c r="E49" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F49" t="s">
+        <v>210</v>
+      </c>
+      <c r="G49" t="s">
         <v>211</v>
-      </c>
-      <c r="G49" t="s">
-        <v>212</v>
       </c>
       <c r="H49" t="s">
         <v>17</v>
       </c>
       <c r="I49" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J49" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K49" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="50" spans="1:11">
       <c r="A50" t="s">
+        <v>213</v>
+      </c>
+      <c r="B50" t="s">
         <v>214</v>
       </c>
-      <c r="B50" t="s">
+      <c r="C50" t="s">
         <v>215</v>
       </c>
-      <c r="C50" t="s">
+      <c r="D50" t="s">
+        <v>14</v>
+      </c>
+      <c r="E50" t="s">
+        <v>15</v>
+      </c>
+      <c r="F50" t="s">
         <v>216</v>
       </c>
-      <c r="D50" t="s">
-        <v>38</v>
-      </c>
-      <c r="E50" t="s">
-        <v>15</v>
-      </c>
-      <c r="F50" t="s">
-        <v>217</v>
-      </c>
       <c r="H50" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I50" t="s">
         <v>27</v>
       </c>
       <c r="J50" t="s">
+        <v>196</v>
+      </c>
+      <c r="K50" t="s">
         <v>197</v>
-      </c>
-      <c r="K50" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="51" spans="1:11">
       <c r="A51" t="s">
+        <v>217</v>
+      </c>
+      <c r="B51" t="s">
         <v>218</v>
       </c>
-      <c r="B51" t="s">
+      <c r="C51" t="s">
         <v>219</v>
       </c>
-      <c r="C51" t="s">
+      <c r="D51" t="s">
+        <v>14</v>
+      </c>
+      <c r="E51" t="s">
+        <v>15</v>
+      </c>
+      <c r="F51" t="s">
         <v>220</v>
-      </c>
-      <c r="D51" t="s">
-        <v>38</v>
-      </c>
-      <c r="E51" t="s">
-        <v>15</v>
-      </c>
-      <c r="F51" t="s">
-        <v>221</v>
       </c>
       <c r="H51" t="s">
         <v>26</v>
@@ -4273,152 +4270,152 @@
         <v>34</v>
       </c>
       <c r="J51" t="s">
+        <v>196</v>
+      </c>
+      <c r="K51" t="s">
         <v>197</v>
-      </c>
-      <c r="K51" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="52" spans="1:11">
       <c r="A52" t="s">
+        <v>221</v>
+      </c>
+      <c r="B52" t="s">
         <v>222</v>
       </c>
-      <c r="B52" t="s">
+      <c r="C52" t="s">
         <v>223</v>
       </c>
-      <c r="C52" t="s">
+      <c r="D52" t="s">
+        <v>14</v>
+      </c>
+      <c r="E52" t="s">
+        <v>15</v>
+      </c>
+      <c r="F52" t="s">
         <v>224</v>
       </c>
-      <c r="D52" t="s">
-        <v>38</v>
-      </c>
-      <c r="E52" t="s">
-        <v>15</v>
-      </c>
-      <c r="F52" t="s">
-        <v>225</v>
-      </c>
       <c r="H52" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I52" t="s">
         <v>34</v>
       </c>
       <c r="J52" t="s">
+        <v>196</v>
+      </c>
+      <c r="K52" t="s">
         <v>197</v>
-      </c>
-      <c r="K52" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="53" spans="1:11">
       <c r="A53" t="s">
+        <v>225</v>
+      </c>
+      <c r="B53" t="s">
         <v>226</v>
       </c>
-      <c r="B53" t="s">
-        <v>227</v>
-      </c>
       <c r="C53" t="s">
+        <v>168</v>
+      </c>
+      <c r="D53" t="s">
+        <v>14</v>
+      </c>
+      <c r="E53" t="s">
+        <v>15</v>
+      </c>
+      <c r="F53" t="s">
         <v>169</v>
-      </c>
-      <c r="D53" t="s">
-        <v>38</v>
-      </c>
-      <c r="E53" t="s">
-        <v>15</v>
-      </c>
-      <c r="F53" t="s">
-        <v>170</v>
       </c>
       <c r="H53" t="s">
         <v>26</v>
       </c>
       <c r="I53" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J53" t="s">
+        <v>196</v>
+      </c>
+      <c r="K53" t="s">
         <v>197</v>
-      </c>
-      <c r="K53" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="54" spans="1:11">
       <c r="A54" t="s">
+        <v>227</v>
+      </c>
+      <c r="B54" t="s">
         <v>228</v>
       </c>
-      <c r="B54" t="s">
+      <c r="C54" t="s">
         <v>229</v>
-      </c>
-      <c r="C54" t="s">
-        <v>230</v>
       </c>
       <c r="D54" t="s">
         <v>24</v>
       </c>
       <c r="H54" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I54" t="s">
         <v>18</v>
       </c>
       <c r="J54" t="s">
+        <v>230</v>
+      </c>
+      <c r="K54" t="s">
         <v>231</v>
-      </c>
-      <c r="K54" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="55" spans="1:11">
       <c r="A55" t="s">
+        <v>232</v>
+      </c>
+      <c r="B55" t="s">
         <v>233</v>
       </c>
-      <c r="B55" t="s">
+      <c r="C55" t="s">
         <v>234</v>
       </c>
-      <c r="C55" t="s">
+      <c r="D55" t="s">
+        <v>14</v>
+      </c>
+      <c r="E55" t="s">
+        <v>15</v>
+      </c>
+      <c r="F55" t="s">
         <v>235</v>
       </c>
-      <c r="D55" t="s">
-        <v>38</v>
-      </c>
-      <c r="E55" t="s">
-        <v>15</v>
-      </c>
-      <c r="F55" t="s">
-        <v>236</v>
-      </c>
       <c r="H55" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I55" t="s">
         <v>18</v>
       </c>
       <c r="J55" t="s">
+        <v>230</v>
+      </c>
+      <c r="K55" t="s">
         <v>231</v>
-      </c>
-      <c r="K55" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="56" spans="1:11">
       <c r="A56" t="s">
+        <v>236</v>
+      </c>
+      <c r="B56" t="s">
         <v>237</v>
       </c>
-      <c r="B56" t="s">
+      <c r="C56" t="s">
         <v>238</v>
       </c>
-      <c r="C56" t="s">
+      <c r="D56" t="s">
+        <v>14</v>
+      </c>
+      <c r="E56" t="s">
+        <v>15</v>
+      </c>
+      <c r="F56" t="s">
         <v>239</v>
-      </c>
-      <c r="D56" t="s">
-        <v>38</v>
-      </c>
-      <c r="E56" t="s">
-        <v>15</v>
-      </c>
-      <c r="F56" t="s">
-        <v>240</v>
       </c>
       <c r="H56" t="s">
         <v>26</v>
@@ -4427,62 +4424,62 @@
         <v>18</v>
       </c>
       <c r="J56" t="s">
+        <v>230</v>
+      </c>
+      <c r="K56" t="s">
         <v>231</v>
-      </c>
-      <c r="K56" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="57" spans="1:11">
       <c r="A57" t="s">
+        <v>240</v>
+      </c>
+      <c r="B57" t="s">
         <v>241</v>
       </c>
-      <c r="B57" t="s">
-        <v>242</v>
-      </c>
       <c r="C57" t="s">
+        <v>238</v>
+      </c>
+      <c r="D57" t="s">
+        <v>14</v>
+      </c>
+      <c r="E57" t="s">
+        <v>15</v>
+      </c>
+      <c r="F57" t="s">
         <v>239</v>
       </c>
-      <c r="D57" t="s">
-        <v>38</v>
-      </c>
-      <c r="E57" t="s">
-        <v>15</v>
-      </c>
-      <c r="F57" t="s">
-        <v>240</v>
-      </c>
       <c r="H57" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I57" t="s">
         <v>27</v>
       </c>
       <c r="J57" t="s">
+        <v>230</v>
+      </c>
+      <c r="K57" t="s">
         <v>231</v>
-      </c>
-      <c r="K57" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="58" spans="1:11">
       <c r="A58" t="s">
+        <v>242</v>
+      </c>
+      <c r="B58" t="s">
         <v>243</v>
       </c>
-      <c r="B58" t="s">
+      <c r="C58" t="s">
         <v>244</v>
       </c>
-      <c r="C58" t="s">
-        <v>245</v>
-      </c>
       <c r="D58" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="E58" t="s">
         <v>31</v>
       </c>
       <c r="F58" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H58" t="s">
         <v>26</v>
@@ -4491,62 +4488,62 @@
         <v>27</v>
       </c>
       <c r="J58" t="s">
+        <v>230</v>
+      </c>
+      <c r="K58" t="s">
         <v>231</v>
-      </c>
-      <c r="K58" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="59" spans="1:11">
       <c r="A59" t="s">
+        <v>246</v>
+      </c>
+      <c r="B59" t="s">
         <v>247</v>
       </c>
-      <c r="B59" t="s">
+      <c r="C59" t="s">
         <v>248</v>
       </c>
-      <c r="C59" t="s">
+      <c r="D59" t="s">
+        <v>14</v>
+      </c>
+      <c r="E59" t="s">
+        <v>15</v>
+      </c>
+      <c r="F59" t="s">
         <v>249</v>
       </c>
-      <c r="D59" t="s">
-        <v>38</v>
-      </c>
-      <c r="E59" t="s">
-        <v>15</v>
-      </c>
-      <c r="F59" t="s">
-        <v>250</v>
-      </c>
       <c r="H59" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I59" t="s">
         <v>34</v>
       </c>
       <c r="J59" t="s">
+        <v>230</v>
+      </c>
+      <c r="K59" t="s">
         <v>231</v>
-      </c>
-      <c r="K59" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="60" spans="1:11">
       <c r="A60" t="s">
+        <v>250</v>
+      </c>
+      <c r="B60" t="s">
         <v>251</v>
       </c>
-      <c r="B60" t="s">
-        <v>252</v>
-      </c>
       <c r="C60" t="s">
+        <v>219</v>
+      </c>
+      <c r="D60" t="s">
+        <v>14</v>
+      </c>
+      <c r="E60" t="s">
+        <v>15</v>
+      </c>
+      <c r="F60" t="s">
         <v>220</v>
-      </c>
-      <c r="D60" t="s">
-        <v>38</v>
-      </c>
-      <c r="E60" t="s">
-        <v>15</v>
-      </c>
-      <c r="F60" t="s">
-        <v>221</v>
       </c>
       <c r="H60" t="s">
         <v>26</v>
@@ -4555,539 +4552,539 @@
         <v>34</v>
       </c>
       <c r="J60" t="s">
+        <v>230</v>
+      </c>
+      <c r="K60" t="s">
         <v>231</v>
-      </c>
-      <c r="K60" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="61" spans="1:11">
       <c r="A61" t="s">
+        <v>252</v>
+      </c>
+      <c r="B61" t="s">
         <v>253</v>
       </c>
-      <c r="B61" t="s">
-        <v>254</v>
-      </c>
       <c r="C61" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D61" t="s">
         <v>24</v>
       </c>
       <c r="H61" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I61" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J61" t="s">
+        <v>230</v>
+      </c>
+      <c r="K61" t="s">
         <v>231</v>
-      </c>
-      <c r="K61" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="62" spans="1:11">
       <c r="A62" t="s">
+        <v>254</v>
+      </c>
+      <c r="B62" t="s">
         <v>255</v>
       </c>
-      <c r="B62" t="s">
-        <v>256</v>
-      </c>
       <c r="C62" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D62" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="E62" t="s">
         <v>31</v>
       </c>
       <c r="F62" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H62" t="s">
         <v>26</v>
       </c>
       <c r="I62" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J62" t="s">
+        <v>230</v>
+      </c>
+      <c r="K62" t="s">
         <v>231</v>
-      </c>
-      <c r="K62" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="63" spans="1:11">
       <c r="A63" t="s">
+        <v>256</v>
+      </c>
+      <c r="B63" t="s">
         <v>257</v>
       </c>
-      <c r="B63" t="s">
+      <c r="C63" t="s">
         <v>258</v>
-      </c>
-      <c r="C63" t="s">
-        <v>259</v>
       </c>
       <c r="D63" t="s">
         <v>24</v>
       </c>
       <c r="F63" t="s">
+        <v>259</v>
+      </c>
+      <c r="H63" t="s">
         <v>260</v>
       </c>
-      <c r="H63" t="s">
-        <v>261</v>
-      </c>
       <c r="I63" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J63" t="s">
+        <v>230</v>
+      </c>
+      <c r="K63" t="s">
         <v>231</v>
-      </c>
-      <c r="K63" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="64" spans="1:11">
       <c r="A64" t="s">
+        <v>261</v>
+      </c>
+      <c r="B64" t="s">
         <v>262</v>
       </c>
-      <c r="B64" t="s">
+      <c r="C64" t="s">
         <v>263</v>
-      </c>
-      <c r="C64" t="s">
-        <v>264</v>
       </c>
       <c r="D64" t="s">
         <v>24</v>
       </c>
       <c r="F64" t="s">
+        <v>264</v>
+      </c>
+      <c r="G64" t="s">
         <v>265</v>
       </c>
-      <c r="G64" t="s">
+      <c r="H64" t="s">
         <v>266</v>
-      </c>
-      <c r="H64" t="s">
-        <v>267</v>
       </c>
       <c r="I64" t="s">
         <v>18</v>
       </c>
       <c r="J64" t="s">
+        <v>267</v>
+      </c>
+      <c r="K64" t="s">
         <v>268</v>
-      </c>
-      <c r="K64" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="65" spans="1:11">
       <c r="A65" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B65" t="s">
+        <v>269</v>
+      </c>
+      <c r="C65" t="s">
         <v>270</v>
       </c>
-      <c r="C65" t="s">
+      <c r="D65" t="s">
+        <v>14</v>
+      </c>
+      <c r="E65" t="s">
+        <v>15</v>
+      </c>
+      <c r="F65" t="s">
         <v>271</v>
       </c>
-      <c r="D65" t="s">
-        <v>38</v>
-      </c>
-      <c r="E65" t="s">
-        <v>15</v>
-      </c>
-      <c r="F65" t="s">
+      <c r="G65" t="s">
         <v>272</v>
       </c>
-      <c r="G65" t="s">
+      <c r="H65" t="s">
         <v>273</v>
-      </c>
-      <c r="H65" t="s">
-        <v>274</v>
       </c>
       <c r="I65" t="s">
         <v>18</v>
       </c>
       <c r="J65" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="K65" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="66" spans="1:11">
       <c r="A66" t="s">
+        <v>275</v>
+      </c>
+      <c r="B66" t="s">
         <v>276</v>
       </c>
-      <c r="B66" t="s">
+      <c r="C66" t="s">
+        <v>270</v>
+      </c>
+      <c r="D66" t="s">
+        <v>14</v>
+      </c>
+      <c r="E66" t="s">
+        <v>15</v>
+      </c>
+      <c r="F66" t="s">
+        <v>271</v>
+      </c>
+      <c r="G66" t="s">
+        <v>272</v>
+      </c>
+      <c r="H66" t="s">
         <v>277</v>
-      </c>
-      <c r="C66" t="s">
-        <v>271</v>
-      </c>
-      <c r="D66" t="s">
-        <v>38</v>
-      </c>
-      <c r="E66" t="s">
-        <v>15</v>
-      </c>
-      <c r="F66" t="s">
-        <v>272</v>
-      </c>
-      <c r="G66" t="s">
-        <v>273</v>
-      </c>
-      <c r="H66" t="s">
-        <v>278</v>
       </c>
       <c r="I66" t="s">
         <v>18</v>
       </c>
       <c r="J66" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="K66" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="67" spans="1:11">
       <c r="A67" t="s">
+        <v>261</v>
+      </c>
+      <c r="B67" t="s">
         <v>262</v>
       </c>
-      <c r="B67" t="s">
+      <c r="C67" t="s">
         <v>263</v>
-      </c>
-      <c r="C67" t="s">
-        <v>264</v>
       </c>
       <c r="D67" t="s">
         <v>24</v>
       </c>
       <c r="F67" t="s">
+        <v>264</v>
+      </c>
+      <c r="G67" t="s">
         <v>265</v>
       </c>
-      <c r="G67" t="s">
-        <v>266</v>
-      </c>
       <c r="H67" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I67" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J67" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="K67" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="68" spans="1:11">
       <c r="A68" t="s">
+        <v>279</v>
+      </c>
+      <c r="B68" t="s">
         <v>280</v>
       </c>
-      <c r="B68" t="s">
+      <c r="C68" t="s">
+        <v>119</v>
+      </c>
+      <c r="D68" t="s">
+        <v>14</v>
+      </c>
+      <c r="E68" t="s">
+        <v>15</v>
+      </c>
+      <c r="F68" t="s">
+        <v>120</v>
+      </c>
+      <c r="H68" t="s">
+        <v>273</v>
+      </c>
+      <c r="I68" t="s">
+        <v>54</v>
+      </c>
+      <c r="J68" t="s">
         <v>281</v>
       </c>
-      <c r="C68" t="s">
-        <v>120</v>
-      </c>
-      <c r="D68" t="s">
-        <v>38</v>
-      </c>
-      <c r="E68" t="s">
-        <v>15</v>
-      </c>
-      <c r="F68" t="s">
-        <v>121</v>
-      </c>
-      <c r="H68" t="s">
-        <v>274</v>
-      </c>
-      <c r="I68" t="s">
-        <v>55</v>
-      </c>
-      <c r="J68" t="s">
-        <v>282</v>
-      </c>
       <c r="K68" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="69" spans="1:11">
       <c r="A69" t="s">
+        <v>282</v>
+      </c>
+      <c r="B69" t="s">
         <v>283</v>
       </c>
-      <c r="B69" t="s">
+      <c r="C69" t="s">
         <v>284</v>
       </c>
-      <c r="C69" t="s">
-        <v>285</v>
-      </c>
       <c r="D69" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="E69" t="s">
         <v>31</v>
       </c>
       <c r="F69" t="s">
+        <v>285</v>
+      </c>
+      <c r="G69" t="s">
         <v>286</v>
       </c>
-      <c r="G69" t="s">
-        <v>287</v>
-      </c>
       <c r="H69" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I69" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J69" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="K69" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="70" spans="1:11">
       <c r="A70" t="s">
+        <v>279</v>
+      </c>
+      <c r="B70" t="s">
         <v>280</v>
       </c>
-      <c r="B70" t="s">
-        <v>281</v>
-      </c>
       <c r="C70" t="s">
+        <v>119</v>
+      </c>
+      <c r="D70" t="s">
+        <v>14</v>
+      </c>
+      <c r="E70" t="s">
+        <v>15</v>
+      </c>
+      <c r="F70" t="s">
         <v>120</v>
       </c>
-      <c r="D70" t="s">
-        <v>38</v>
-      </c>
-      <c r="E70" t="s">
-        <v>15</v>
-      </c>
-      <c r="F70" t="s">
-        <v>121</v>
-      </c>
       <c r="H70" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I70" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J70" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="K70" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="71" spans="1:11">
       <c r="A71" t="s">
+        <v>288</v>
+      </c>
+      <c r="B71" t="s">
         <v>289</v>
       </c>
-      <c r="B71" t="s">
+      <c r="C71" t="s">
         <v>290</v>
       </c>
-      <c r="C71" t="s">
+      <c r="D71" t="s">
+        <v>14</v>
+      </c>
+      <c r="E71" t="s">
         <v>291</v>
       </c>
-      <c r="D71" t="s">
-        <v>14</v>
-      </c>
-      <c r="E71" t="s">
+      <c r="F71" t="s">
         <v>292</v>
       </c>
-      <c r="F71" t="s">
+      <c r="G71" t="s">
         <v>293</v>
       </c>
-      <c r="G71" t="s">
-        <v>294</v>
-      </c>
       <c r="H71" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I71" t="s">
         <v>34</v>
       </c>
       <c r="J71" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="K71" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="72" spans="1:11">
       <c r="A72" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B72" t="s">
+        <v>269</v>
+      </c>
+      <c r="C72" t="s">
         <v>270</v>
       </c>
-      <c r="C72" t="s">
+      <c r="D72" t="s">
+        <v>14</v>
+      </c>
+      <c r="E72" t="s">
+        <v>15</v>
+      </c>
+      <c r="F72" t="s">
         <v>271</v>
       </c>
-      <c r="D72" t="s">
-        <v>38</v>
-      </c>
-      <c r="E72" t="s">
-        <v>15</v>
-      </c>
-      <c r="F72" t="s">
+      <c r="G72" t="s">
         <v>272</v>
       </c>
-      <c r="G72" t="s">
+      <c r="H72" t="s">
         <v>273</v>
-      </c>
-      <c r="H72" t="s">
-        <v>274</v>
       </c>
       <c r="I72" t="s">
         <v>34</v>
       </c>
       <c r="J72" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="K72" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="73" spans="1:11">
       <c r="A73" t="s">
+        <v>275</v>
+      </c>
+      <c r="B73" t="s">
         <v>276</v>
       </c>
-      <c r="B73" t="s">
+      <c r="C73" t="s">
+        <v>270</v>
+      </c>
+      <c r="D73" t="s">
+        <v>14</v>
+      </c>
+      <c r="E73" t="s">
+        <v>15</v>
+      </c>
+      <c r="F73" t="s">
+        <v>271</v>
+      </c>
+      <c r="G73" t="s">
+        <v>272</v>
+      </c>
+      <c r="H73" t="s">
         <v>277</v>
-      </c>
-      <c r="C73" t="s">
-        <v>271</v>
-      </c>
-      <c r="D73" t="s">
-        <v>38</v>
-      </c>
-      <c r="E73" t="s">
-        <v>15</v>
-      </c>
-      <c r="F73" t="s">
-        <v>272</v>
-      </c>
-      <c r="G73" t="s">
-        <v>273</v>
-      </c>
-      <c r="H73" t="s">
-        <v>278</v>
       </c>
       <c r="I73" t="s">
         <v>34</v>
       </c>
       <c r="J73" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="K73" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="74" spans="1:11">
       <c r="A74" t="s">
+        <v>282</v>
+      </c>
+      <c r="B74" t="s">
         <v>283</v>
       </c>
-      <c r="B74" t="s">
+      <c r="C74" t="s">
         <v>284</v>
       </c>
-      <c r="C74" t="s">
-        <v>285</v>
-      </c>
       <c r="D74" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="E74" t="s">
         <v>31</v>
       </c>
       <c r="F74" t="s">
+        <v>285</v>
+      </c>
+      <c r="G74" t="s">
         <v>286</v>
       </c>
-      <c r="G74" t="s">
-        <v>287</v>
-      </c>
       <c r="H74" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I74" t="s">
         <v>34</v>
       </c>
       <c r="J74" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="K74" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="75" spans="1:11">
       <c r="A75" t="s">
+        <v>288</v>
+      </c>
+      <c r="B75" t="s">
         <v>289</v>
       </c>
-      <c r="B75" t="s">
+      <c r="C75" t="s">
         <v>290</v>
       </c>
-      <c r="C75" t="s">
+      <c r="D75" t="s">
+        <v>14</v>
+      </c>
+      <c r="E75" t="s">
         <v>291</v>
       </c>
-      <c r="D75" t="s">
-        <v>14</v>
-      </c>
-      <c r="E75" t="s">
+      <c r="F75" t="s">
         <v>292</v>
       </c>
-      <c r="F75" t="s">
+      <c r="G75" t="s">
         <v>293</v>
       </c>
-      <c r="G75" t="s">
-        <v>294</v>
-      </c>
       <c r="H75" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I75" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J75" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="K75" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="76" spans="1:11">
       <c r="A76" t="s">
+        <v>295</v>
+      </c>
+      <c r="B76" t="s">
         <v>296</v>
       </c>
-      <c r="B76" t="s">
+      <c r="C76" t="s">
         <v>297</v>
       </c>
-      <c r="C76" t="s">
+      <c r="D76" t="s">
+        <v>14</v>
+      </c>
+      <c r="H76" t="s">
         <v>298</v>
       </c>
-      <c r="D76" t="s">
-        <v>38</v>
-      </c>
-      <c r="H76" t="s">
+      <c r="I76" t="s">
+        <v>39</v>
+      </c>
+      <c r="J76" t="s">
         <v>299</v>
       </c>
-      <c r="I76" t="s">
-        <v>40</v>
-      </c>
-      <c r="J76" t="s">
-        <v>300</v>
-      </c>
       <c r="K76" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="77" spans="1:11">
       <c r="A77" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B77" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C77" t="s">
         <v>30</v>
@@ -5111,82 +5108,82 @@
         <v>18</v>
       </c>
       <c r="J77" t="s">
+        <v>301</v>
+      </c>
+      <c r="K77" t="s">
         <v>302</v>
-      </c>
-      <c r="K77" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="78" spans="1:11">
       <c r="A78" t="s">
+        <v>303</v>
+      </c>
+      <c r="B78" t="s">
         <v>304</v>
       </c>
-      <c r="B78" t="s">
+      <c r="C78" t="s">
         <v>305</v>
       </c>
-      <c r="C78" t="s">
+      <c r="D78" t="s">
+        <v>14</v>
+      </c>
+      <c r="E78" t="s">
+        <v>15</v>
+      </c>
+      <c r="F78" t="s">
         <v>306</v>
       </c>
-      <c r="D78" t="s">
-        <v>38</v>
-      </c>
-      <c r="E78" t="s">
-        <v>15</v>
-      </c>
-      <c r="F78" t="s">
-        <v>307</v>
-      </c>
       <c r="H78" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I78" t="s">
         <v>18</v>
       </c>
       <c r="J78" t="s">
+        <v>301</v>
+      </c>
+      <c r="K78" t="s">
         <v>302</v>
-      </c>
-      <c r="K78" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="79" spans="1:11">
       <c r="A79" t="s">
+        <v>307</v>
+      </c>
+      <c r="B79" t="s">
         <v>308</v>
       </c>
-      <c r="B79" t="s">
+      <c r="C79" t="s">
         <v>309</v>
-      </c>
-      <c r="C79" t="s">
-        <v>310</v>
       </c>
       <c r="D79" t="s">
         <v>24</v>
       </c>
       <c r="F79" t="s">
+        <v>310</v>
+      </c>
+      <c r="H79" t="s">
+        <v>109</v>
+      </c>
+      <c r="I79" t="s">
+        <v>54</v>
+      </c>
+      <c r="J79" t="s">
         <v>311</v>
       </c>
-      <c r="H79" t="s">
-        <v>110</v>
-      </c>
-      <c r="I79" t="s">
-        <v>55</v>
-      </c>
-      <c r="J79" t="s">
-        <v>312</v>
-      </c>
       <c r="K79" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="80" spans="1:11">
       <c r="A80" t="s">
+        <v>312</v>
+      </c>
+      <c r="B80" t="s">
         <v>313</v>
       </c>
-      <c r="B80" t="s">
-        <v>314</v>
-      </c>
       <c r="C80" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D80" t="s">
         <v>24</v>
@@ -5198,30 +5195,30 @@
         <v>27</v>
       </c>
       <c r="J80" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="K80" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="81" spans="1:11">
       <c r="A81" t="s">
+        <v>314</v>
+      </c>
+      <c r="B81" t="s">
         <v>315</v>
       </c>
-      <c r="B81" t="s">
+      <c r="C81" t="s">
         <v>316</v>
-      </c>
-      <c r="C81" t="s">
-        <v>317</v>
       </c>
       <c r="D81" t="s">
         <v>24</v>
       </c>
       <c r="F81" t="s">
+        <v>317</v>
+      </c>
+      <c r="G81" t="s">
         <v>318</v>
-      </c>
-      <c r="G81" t="s">
-        <v>319</v>
       </c>
       <c r="H81" t="s">
         <v>26</v>
@@ -5230,97 +5227,97 @@
         <v>27</v>
       </c>
       <c r="J81" t="s">
+        <v>301</v>
+      </c>
+      <c r="K81" t="s">
         <v>302</v>
-      </c>
-      <c r="K81" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="82" spans="1:11">
       <c r="A82" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B82" t="s">
+        <v>319</v>
+      </c>
+      <c r="C82" t="s">
         <v>320</v>
-      </c>
-      <c r="C82" t="s">
-        <v>321</v>
       </c>
       <c r="D82" t="s">
         <v>24</v>
       </c>
       <c r="E82" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F82" t="s">
+        <v>321</v>
+      </c>
+      <c r="G82" t="s">
         <v>322</v>
       </c>
-      <c r="G82" t="s">
-        <v>323</v>
-      </c>
       <c r="H82" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I82" t="s">
         <v>34</v>
       </c>
       <c r="J82" t="s">
+        <v>301</v>
+      </c>
+      <c r="K82" t="s">
         <v>302</v>
-      </c>
-      <c r="K82" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="83" spans="1:11">
       <c r="A83" t="s">
+        <v>323</v>
+      </c>
+      <c r="B83" t="s">
         <v>324</v>
       </c>
-      <c r="B83" t="s">
+      <c r="C83" t="s">
         <v>325</v>
       </c>
-      <c r="C83" t="s">
+      <c r="D83" t="s">
+        <v>14</v>
+      </c>
+      <c r="E83" t="s">
+        <v>15</v>
+      </c>
+      <c r="F83" t="s">
         <v>326</v>
-      </c>
-      <c r="D83" t="s">
-        <v>14</v>
-      </c>
-      <c r="E83" t="s">
-        <v>15</v>
-      </c>
-      <c r="F83" t="s">
-        <v>327</v>
       </c>
       <c r="H83" t="s">
         <v>26</v>
       </c>
       <c r="I83" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J83" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="K83" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="84" spans="1:11">
       <c r="A84" t="s">
+        <v>327</v>
+      </c>
+      <c r="B84" t="s">
         <v>328</v>
       </c>
-      <c r="B84" t="s">
-        <v>329</v>
-      </c>
       <c r="C84" t="s">
+        <v>143</v>
+      </c>
+      <c r="D84" t="s">
+        <v>14</v>
+      </c>
+      <c r="E84" t="s">
+        <v>15</v>
+      </c>
+      <c r="F84" t="s">
         <v>144</v>
-      </c>
-      <c r="D84" t="s">
-        <v>38</v>
-      </c>
-      <c r="E84" t="s">
-        <v>15</v>
-      </c>
-      <c r="F84" t="s">
-        <v>145</v>
       </c>
       <c r="H84" t="s">
         <v>26</v>
@@ -5329,94 +5326,94 @@
         <v>18</v>
       </c>
       <c r="J84" t="s">
+        <v>329</v>
+      </c>
+      <c r="K84" t="s">
         <v>330</v>
-      </c>
-      <c r="K84" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="85" spans="1:11">
       <c r="A85" t="s">
+        <v>331</v>
+      </c>
+      <c r="B85" t="s">
         <v>332</v>
       </c>
-      <c r="B85" t="s">
+      <c r="C85" t="s">
         <v>333</v>
       </c>
-      <c r="C85" t="s">
+      <c r="D85" t="s">
+        <v>14</v>
+      </c>
+      <c r="E85" t="s">
+        <v>15</v>
+      </c>
+      <c r="F85" t="s">
         <v>334</v>
       </c>
-      <c r="D85" t="s">
-        <v>38</v>
-      </c>
-      <c r="E85" t="s">
-        <v>15</v>
-      </c>
-      <c r="F85" t="s">
-        <v>335</v>
-      </c>
       <c r="H85" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I85" t="s">
         <v>18</v>
       </c>
       <c r="J85" t="s">
+        <v>329</v>
+      </c>
+      <c r="K85" t="s">
         <v>330</v>
-      </c>
-      <c r="K85" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="86" spans="1:11">
       <c r="A86" t="s">
+        <v>335</v>
+      </c>
+      <c r="B86" t="s">
         <v>336</v>
       </c>
-      <c r="B86" t="s">
+      <c r="C86" t="s">
         <v>337</v>
       </c>
-      <c r="C86" t="s">
+      <c r="D86" t="s">
+        <v>14</v>
+      </c>
+      <c r="E86" t="s">
+        <v>15</v>
+      </c>
+      <c r="F86" t="s">
         <v>338</v>
-      </c>
-      <c r="D86" t="s">
-        <v>38</v>
-      </c>
-      <c r="E86" t="s">
-        <v>15</v>
-      </c>
-      <c r="F86" t="s">
-        <v>339</v>
       </c>
       <c r="H86" t="s">
         <v>26</v>
       </c>
       <c r="I86" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J86" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="K86" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="87" spans="1:11">
       <c r="A87" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B87" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C87" t="s">
+        <v>143</v>
+      </c>
+      <c r="D87" t="s">
+        <v>14</v>
+      </c>
+      <c r="E87" t="s">
+        <v>15</v>
+      </c>
+      <c r="F87" t="s">
         <v>144</v>
-      </c>
-      <c r="D87" t="s">
-        <v>38</v>
-      </c>
-      <c r="E87" t="s">
-        <v>15</v>
-      </c>
-      <c r="F87" t="s">
-        <v>145</v>
       </c>
       <c r="H87" t="s">
         <v>26</v>
@@ -5425,62 +5422,62 @@
         <v>27</v>
       </c>
       <c r="J87" t="s">
+        <v>329</v>
+      </c>
+      <c r="K87" t="s">
         <v>330</v>
-      </c>
-      <c r="K87" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="88" spans="1:11">
       <c r="A88" t="s">
+        <v>340</v>
+      </c>
+      <c r="B88" t="s">
         <v>341</v>
       </c>
-      <c r="B88" t="s">
+      <c r="C88" t="s">
         <v>342</v>
       </c>
-      <c r="C88" t="s">
+      <c r="D88" t="s">
+        <v>14</v>
+      </c>
+      <c r="E88" t="s">
+        <v>15</v>
+      </c>
+      <c r="F88" t="s">
         <v>343</v>
       </c>
-      <c r="D88" t="s">
-        <v>14</v>
-      </c>
-      <c r="E88" t="s">
-        <v>15</v>
-      </c>
-      <c r="F88" t="s">
-        <v>344</v>
-      </c>
       <c r="H88" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I88" t="s">
         <v>34</v>
       </c>
       <c r="J88" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="K88" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="89" spans="1:11">
       <c r="A89" t="s">
+        <v>345</v>
+      </c>
+      <c r="B89" t="s">
         <v>346</v>
       </c>
-      <c r="B89" t="s">
-        <v>347</v>
-      </c>
       <c r="C89" t="s">
+        <v>143</v>
+      </c>
+      <c r="D89" t="s">
+        <v>14</v>
+      </c>
+      <c r="E89" t="s">
+        <v>15</v>
+      </c>
+      <c r="F89" t="s">
         <v>144</v>
-      </c>
-      <c r="D89" t="s">
-        <v>38</v>
-      </c>
-      <c r="E89" t="s">
-        <v>15</v>
-      </c>
-      <c r="F89" t="s">
-        <v>145</v>
       </c>
       <c r="H89" t="s">
         <v>26</v>
@@ -5489,126 +5486,126 @@
         <v>34</v>
       </c>
       <c r="J89" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="K89" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="90" spans="1:11">
       <c r="A90" t="s">
+        <v>347</v>
+      </c>
+      <c r="B90" t="s">
         <v>348</v>
       </c>
-      <c r="B90" t="s">
-        <v>349</v>
-      </c>
       <c r="C90" t="s">
+        <v>107</v>
+      </c>
+      <c r="D90" t="s">
+        <v>14</v>
+      </c>
+      <c r="E90" t="s">
+        <v>15</v>
+      </c>
+      <c r="F90" t="s">
         <v>108</v>
       </c>
-      <c r="D90" t="s">
-        <v>38</v>
-      </c>
-      <c r="E90" t="s">
-        <v>15</v>
-      </c>
-      <c r="F90" t="s">
-        <v>109</v>
-      </c>
       <c r="H90" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I90" t="s">
         <v>34</v>
       </c>
       <c r="J90" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="K90" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="91" spans="1:11">
       <c r="A91" t="s">
+        <v>349</v>
+      </c>
+      <c r="B91" t="s">
         <v>350</v>
       </c>
-      <c r="B91" t="s">
-        <v>351</v>
-      </c>
       <c r="C91" t="s">
+        <v>234</v>
+      </c>
+      <c r="D91" t="s">
+        <v>14</v>
+      </c>
+      <c r="E91" t="s">
+        <v>15</v>
+      </c>
+      <c r="F91" t="s">
         <v>235</v>
       </c>
-      <c r="D91" t="s">
-        <v>38</v>
-      </c>
-      <c r="E91" t="s">
-        <v>15</v>
-      </c>
-      <c r="F91" t="s">
-        <v>236</v>
-      </c>
       <c r="H91" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I91" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J91" t="s">
+        <v>329</v>
+      </c>
+      <c r="K91" t="s">
         <v>330</v>
-      </c>
-      <c r="K91" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="92" spans="1:11">
       <c r="A92" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B92" t="s">
+        <v>351</v>
+      </c>
+      <c r="C92" t="s">
         <v>352</v>
       </c>
-      <c r="C92" t="s">
+      <c r="D92" t="s">
+        <v>14</v>
+      </c>
+      <c r="E92" t="s">
+        <v>15</v>
+      </c>
+      <c r="F92" t="s">
         <v>353</v>
-      </c>
-      <c r="D92" t="s">
-        <v>38</v>
-      </c>
-      <c r="E92" t="s">
-        <v>15</v>
-      </c>
-      <c r="F92" t="s">
-        <v>354</v>
       </c>
       <c r="H92" t="s">
         <v>26</v>
       </c>
       <c r="I92" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J92" t="s">
+        <v>329</v>
+      </c>
+      <c r="K92" t="s">
         <v>330</v>
-      </c>
-      <c r="K92" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="93" spans="1:11">
       <c r="A93" t="s">
+        <v>354</v>
+      </c>
+      <c r="B93" t="s">
         <v>355</v>
       </c>
-      <c r="B93" t="s">
-        <v>356</v>
-      </c>
       <c r="C93" t="s">
+        <v>178</v>
+      </c>
+      <c r="D93" t="s">
+        <v>14</v>
+      </c>
+      <c r="E93" t="s">
+        <v>15</v>
+      </c>
+      <c r="F93" t="s">
         <v>179</v>
-      </c>
-      <c r="D93" t="s">
-        <v>38</v>
-      </c>
-      <c r="E93" t="s">
-        <v>15</v>
-      </c>
-      <c r="F93" t="s">
-        <v>180</v>
       </c>
       <c r="H93" t="s">
         <v>17</v>
@@ -5617,53 +5614,53 @@
         <v>18</v>
       </c>
       <c r="J93" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K93" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="94" spans="1:11">
       <c r="A94" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B94" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C94" t="s">
+        <v>161</v>
+      </c>
+      <c r="D94" t="s">
+        <v>14</v>
+      </c>
+      <c r="E94" t="s">
         <v>162</v>
       </c>
-      <c r="D94" t="s">
-        <v>14</v>
-      </c>
-      <c r="E94" t="s">
+      <c r="F94" t="s">
         <v>163</v>
       </c>
-      <c r="F94" t="s">
-        <v>164</v>
-      </c>
       <c r="H94" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I94" t="s">
         <v>18</v>
       </c>
       <c r="J94" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K94" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="95" spans="1:11">
       <c r="A95" t="s">
+        <v>358</v>
+      </c>
+      <c r="B95" t="s">
         <v>359</v>
       </c>
-      <c r="B95" t="s">
-        <v>360</v>
-      </c>
       <c r="C95" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D95" t="s">
         <v>14</v>
@@ -5672,39 +5669,39 @@
         <v>31</v>
       </c>
       <c r="F95" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H95" t="s">
         <v>26</v>
       </c>
       <c r="I95" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J95" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="K95" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="96" spans="1:11">
       <c r="A96" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B96" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C96" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D96" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="E96" t="s">
         <v>31</v>
       </c>
       <c r="F96" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H96" t="s">
         <v>26</v>
@@ -5713,65 +5710,65 @@
         <v>27</v>
       </c>
       <c r="J96" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K96" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="97" spans="1:11">
       <c r="A97" t="s">
+        <v>362</v>
+      </c>
+      <c r="B97" t="s">
         <v>363</v>
       </c>
-      <c r="B97" t="s">
-        <v>364</v>
-      </c>
       <c r="C97" t="s">
+        <v>200</v>
+      </c>
+      <c r="D97" t="s">
+        <v>14</v>
+      </c>
+      <c r="E97" t="s">
+        <v>15</v>
+      </c>
+      <c r="F97" t="s">
         <v>201</v>
       </c>
-      <c r="D97" t="s">
-        <v>38</v>
-      </c>
-      <c r="E97" t="s">
-        <v>15</v>
-      </c>
-      <c r="F97" t="s">
-        <v>202</v>
-      </c>
       <c r="H97" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I97" t="s">
         <v>34</v>
       </c>
       <c r="J97" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K97" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="98" spans="1:11">
       <c r="A98" t="s">
+        <v>364</v>
+      </c>
+      <c r="B98" t="s">
         <v>365</v>
       </c>
-      <c r="B98" t="s">
-        <v>366</v>
-      </c>
       <c r="C98" t="s">
+        <v>204</v>
+      </c>
+      <c r="D98" t="s">
+        <v>14</v>
+      </c>
+      <c r="E98" t="s">
+        <v>15</v>
+      </c>
+      <c r="F98" t="s">
         <v>205</v>
       </c>
-      <c r="D98" t="s">
-        <v>38</v>
-      </c>
-      <c r="E98" t="s">
-        <v>15</v>
-      </c>
-      <c r="F98" t="s">
+      <c r="G98" t="s">
         <v>206</v>
-      </c>
-      <c r="G98" t="s">
-        <v>207</v>
       </c>
       <c r="H98" t="s">
         <v>26</v>
@@ -5780,18 +5777,18 @@
         <v>34</v>
       </c>
       <c r="J98" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="K98" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="99" spans="1:11">
       <c r="A99" t="s">
+        <v>366</v>
+      </c>
+      <c r="B99" t="s">
         <v>367</v>
-      </c>
-      <c r="B99" t="s">
-        <v>368</v>
       </c>
       <c r="C99" t="s">
         <v>13</v>
@@ -5809,24 +5806,24 @@
         <v>26</v>
       </c>
       <c r="I99" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J99" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K99" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="100" spans="1:11">
       <c r="A100" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B100" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C100" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D100" t="s">
         <v>14</v>
@@ -5835,39 +5832,39 @@
         <v>31</v>
       </c>
       <c r="F100" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H100" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I100" t="s">
         <v>18</v>
       </c>
       <c r="J100" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K100" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="101" spans="1:11">
       <c r="A101" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B101" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C101" t="s">
+        <v>178</v>
+      </c>
+      <c r="D101" t="s">
+        <v>14</v>
+      </c>
+      <c r="E101" t="s">
+        <v>15</v>
+      </c>
+      <c r="F101" t="s">
         <v>179</v>
-      </c>
-      <c r="D101" t="s">
-        <v>38</v>
-      </c>
-      <c r="E101" t="s">
-        <v>15</v>
-      </c>
-      <c r="F101" t="s">
-        <v>180</v>
       </c>
       <c r="H101" t="s">
         <v>17</v>
@@ -5876,62 +5873,62 @@
         <v>18</v>
       </c>
       <c r="J101" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K101" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="102" spans="1:11">
       <c r="A102" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B102" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C102" t="s">
+        <v>161</v>
+      </c>
+      <c r="D102" t="s">
+        <v>14</v>
+      </c>
+      <c r="E102" t="s">
         <v>162</v>
       </c>
-      <c r="D102" t="s">
-        <v>14</v>
-      </c>
-      <c r="E102" t="s">
+      <c r="F102" t="s">
         <v>163</v>
       </c>
-      <c r="F102" t="s">
-        <v>164</v>
-      </c>
       <c r="H102" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I102" t="s">
         <v>18</v>
       </c>
       <c r="J102" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K102" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="103" spans="1:11">
       <c r="A103" t="s">
+        <v>372</v>
+      </c>
+      <c r="B103" t="s">
         <v>373</v>
       </c>
-      <c r="B103" t="s">
-        <v>374</v>
-      </c>
       <c r="C103" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D103" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="E103" t="s">
         <v>31</v>
       </c>
       <c r="F103" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H103" t="s">
         <v>26</v>
@@ -5940,65 +5937,65 @@
         <v>27</v>
       </c>
       <c r="J103" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K103" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="104" spans="1:11">
       <c r="A104" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B104" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C104" t="s">
+        <v>200</v>
+      </c>
+      <c r="D104" t="s">
+        <v>14</v>
+      </c>
+      <c r="E104" t="s">
+        <v>15</v>
+      </c>
+      <c r="F104" t="s">
         <v>201</v>
       </c>
-      <c r="D104" t="s">
-        <v>38</v>
-      </c>
-      <c r="E104" t="s">
-        <v>15</v>
-      </c>
-      <c r="F104" t="s">
-        <v>202</v>
-      </c>
       <c r="H104" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I104" t="s">
         <v>34</v>
       </c>
       <c r="J104" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K104" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="105" spans="1:11">
       <c r="A105" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B105" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C105" t="s">
+        <v>204</v>
+      </c>
+      <c r="D105" t="s">
+        <v>14</v>
+      </c>
+      <c r="E105" t="s">
+        <v>15</v>
+      </c>
+      <c r="F105" t="s">
         <v>205</v>
       </c>
-      <c r="D105" t="s">
-        <v>38</v>
-      </c>
-      <c r="E105" t="s">
-        <v>15</v>
-      </c>
-      <c r="F105" t="s">
+      <c r="G105" t="s">
         <v>206</v>
-      </c>
-      <c r="G105" t="s">
-        <v>207</v>
       </c>
       <c r="H105" t="s">
         <v>26</v>
@@ -6007,18 +6004,18 @@
         <v>34</v>
       </c>
       <c r="J105" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="K105" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="106" spans="1:11">
       <c r="A106" t="s">
+        <v>376</v>
+      </c>
+      <c r="B106" t="s">
         <v>377</v>
-      </c>
-      <c r="B106" t="s">
-        <v>378</v>
       </c>
       <c r="C106" t="s">
         <v>13</v>
@@ -6036,21 +6033,21 @@
         <v>26</v>
       </c>
       <c r="I106" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J106" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K106" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="107" spans="1:11">
       <c r="A107" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B107" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C107" t="s">
         <v>13</v>
@@ -6065,39 +6062,39 @@
         <v>16</v>
       </c>
       <c r="H107" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I107" t="s">
         <v>18</v>
       </c>
       <c r="J107" t="s">
+        <v>379</v>
+      </c>
+      <c r="K107" t="s">
         <v>380</v>
-      </c>
-      <c r="K107" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="108" spans="1:11">
       <c r="A108" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B108" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C108" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D108" t="s">
         <v>24</v>
       </c>
       <c r="E108" t="s">
+        <v>129</v>
+      </c>
+      <c r="F108" t="s">
         <v>130</v>
       </c>
-      <c r="F108" t="s">
+      <c r="G108" t="s">
         <v>131</v>
-      </c>
-      <c r="G108" t="s">
-        <v>132</v>
       </c>
       <c r="H108" t="s">
         <v>26</v>
@@ -6106,216 +6103,216 @@
         <v>18</v>
       </c>
       <c r="J108" t="s">
+        <v>379</v>
+      </c>
+      <c r="K108" t="s">
         <v>380</v>
-      </c>
-      <c r="K108" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="109" spans="1:11">
       <c r="A109" t="s">
+        <v>382</v>
+      </c>
+      <c r="B109" t="s">
         <v>383</v>
       </c>
-      <c r="B109" t="s">
-        <v>384</v>
-      </c>
       <c r="C109" t="s">
+        <v>215</v>
+      </c>
+      <c r="D109" t="s">
+        <v>14</v>
+      </c>
+      <c r="E109" t="s">
+        <v>15</v>
+      </c>
+      <c r="F109" t="s">
         <v>216</v>
       </c>
-      <c r="D109" t="s">
-        <v>38</v>
-      </c>
-      <c r="E109" t="s">
-        <v>15</v>
-      </c>
-      <c r="F109" t="s">
-        <v>217</v>
-      </c>
       <c r="H109" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I109" t="s">
         <v>18</v>
       </c>
       <c r="J109" t="s">
+        <v>379</v>
+      </c>
+      <c r="K109" t="s">
         <v>380</v>
-      </c>
-      <c r="K109" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="110" spans="1:11">
       <c r="A110" t="s">
+        <v>384</v>
+      </c>
+      <c r="B110" t="s">
         <v>385</v>
       </c>
-      <c r="B110" t="s">
-        <v>386</v>
-      </c>
       <c r="C110" t="s">
+        <v>119</v>
+      </c>
+      <c r="D110" t="s">
+        <v>14</v>
+      </c>
+      <c r="E110" t="s">
+        <v>15</v>
+      </c>
+      <c r="F110" t="s">
         <v>120</v>
       </c>
-      <c r="D110" t="s">
-        <v>38</v>
-      </c>
-      <c r="E110" t="s">
-        <v>15</v>
-      </c>
-      <c r="F110" t="s">
-        <v>121</v>
-      </c>
       <c r="H110" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I110" t="s">
         <v>27</v>
       </c>
       <c r="J110" t="s">
+        <v>379</v>
+      </c>
+      <c r="K110" t="s">
         <v>380</v>
-      </c>
-      <c r="K110" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="111" spans="1:11">
       <c r="A111" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B111" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C111" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D111" t="s">
         <v>24</v>
       </c>
       <c r="E111" t="s">
+        <v>129</v>
+      </c>
+      <c r="F111" t="s">
         <v>130</v>
       </c>
-      <c r="F111" t="s">
+      <c r="G111" t="s">
         <v>131</v>
       </c>
-      <c r="G111" t="s">
-        <v>132</v>
-      </c>
       <c r="H111" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I111" t="s">
         <v>34</v>
       </c>
       <c r="J111" t="s">
+        <v>379</v>
+      </c>
+      <c r="K111" t="s">
         <v>380</v>
-      </c>
-      <c r="K111" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="112" spans="1:11">
       <c r="A112" t="s">
+        <v>386</v>
+      </c>
+      <c r="B112" t="s">
         <v>387</v>
       </c>
-      <c r="B112" t="s">
-        <v>388</v>
-      </c>
       <c r="C112" t="s">
+        <v>119</v>
+      </c>
+      <c r="D112" t="s">
+        <v>14</v>
+      </c>
+      <c r="E112" t="s">
+        <v>15</v>
+      </c>
+      <c r="F112" t="s">
         <v>120</v>
       </c>
-      <c r="D112" t="s">
-        <v>38</v>
-      </c>
-      <c r="E112" t="s">
-        <v>15</v>
-      </c>
-      <c r="F112" t="s">
-        <v>121</v>
-      </c>
       <c r="H112" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I112" t="s">
         <v>34</v>
       </c>
       <c r="J112" t="s">
+        <v>379</v>
+      </c>
+      <c r="K112" t="s">
         <v>380</v>
-      </c>
-      <c r="K112" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="113" spans="1:11">
       <c r="A113" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B113" t="s">
+        <v>388</v>
+      </c>
+      <c r="C113" t="s">
         <v>389</v>
       </c>
-      <c r="C113" t="s">
+      <c r="D113" t="s">
+        <v>14</v>
+      </c>
+      <c r="E113" t="s">
+        <v>162</v>
+      </c>
+      <c r="F113" t="s">
         <v>390</v>
       </c>
-      <c r="D113" t="s">
-        <v>14</v>
-      </c>
-      <c r="E113" t="s">
-        <v>163</v>
-      </c>
-      <c r="F113" t="s">
-        <v>391</v>
-      </c>
       <c r="H113" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I113" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J113" t="s">
+        <v>379</v>
+      </c>
+      <c r="K113" t="s">
         <v>380</v>
-      </c>
-      <c r="K113" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="114" spans="1:11">
       <c r="A114" t="s">
+        <v>382</v>
+      </c>
+      <c r="B114" t="s">
         <v>383</v>
       </c>
-      <c r="B114" t="s">
-        <v>384</v>
-      </c>
       <c r="C114" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D114" t="s">
         <v>24</v>
       </c>
       <c r="F114" t="s">
+        <v>317</v>
+      </c>
+      <c r="G114" t="s">
         <v>318</v>
       </c>
-      <c r="G114" t="s">
-        <v>319</v>
-      </c>
       <c r="H114" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I114" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J114" t="s">
+        <v>379</v>
+      </c>
+      <c r="K114" t="s">
         <v>380</v>
-      </c>
-      <c r="K114" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="115" spans="1:11">
       <c r="A115" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B115" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C115" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D115" t="s">
         <v>14</v>
@@ -6324,39 +6321,39 @@
         <v>31</v>
       </c>
       <c r="F115" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H115" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I115" t="s">
         <v>18</v>
       </c>
       <c r="J115" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K115" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="116" spans="1:11">
       <c r="A116" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B116" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C116" t="s">
+        <v>178</v>
+      </c>
+      <c r="D116" t="s">
+        <v>14</v>
+      </c>
+      <c r="E116" t="s">
+        <v>15</v>
+      </c>
+      <c r="F116" t="s">
         <v>179</v>
-      </c>
-      <c r="D116" t="s">
-        <v>38</v>
-      </c>
-      <c r="E116" t="s">
-        <v>15</v>
-      </c>
-      <c r="F116" t="s">
-        <v>180</v>
       </c>
       <c r="H116" t="s">
         <v>17</v>
@@ -6365,30 +6362,30 @@
         <v>18</v>
       </c>
       <c r="J116" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K116" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="117" spans="1:11">
       <c r="A117" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B117" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C117" t="s">
+        <v>389</v>
+      </c>
+      <c r="D117" t="s">
+        <v>14</v>
+      </c>
+      <c r="E117" t="s">
+        <v>162</v>
+      </c>
+      <c r="F117" t="s">
         <v>390</v>
-      </c>
-      <c r="D117" t="s">
-        <v>14</v>
-      </c>
-      <c r="E117" t="s">
-        <v>163</v>
-      </c>
-      <c r="F117" t="s">
-        <v>391</v>
       </c>
       <c r="H117" t="s">
         <v>26</v>
@@ -6397,65 +6394,65 @@
         <v>18</v>
       </c>
       <c r="J117" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="K117" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="118" spans="1:11">
       <c r="A118" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B118" t="s">
+        <v>395</v>
+      </c>
+      <c r="C118" t="s">
         <v>396</v>
       </c>
-      <c r="C118" t="s">
+      <c r="D118" t="s">
+        <v>14</v>
+      </c>
+      <c r="E118" t="s">
+        <v>15</v>
+      </c>
+      <c r="F118" t="s">
         <v>397</v>
       </c>
-      <c r="D118" t="s">
-        <v>38</v>
-      </c>
-      <c r="E118" t="s">
-        <v>15</v>
-      </c>
-      <c r="F118" t="s">
-        <v>398</v>
-      </c>
       <c r="H118" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I118" t="s">
         <v>27</v>
       </c>
       <c r="J118" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="K118" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="119" spans="1:11">
       <c r="A119" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B119" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C119" t="s">
+        <v>204</v>
+      </c>
+      <c r="D119" t="s">
+        <v>14</v>
+      </c>
+      <c r="E119" t="s">
+        <v>15</v>
+      </c>
+      <c r="F119" t="s">
         <v>205</v>
       </c>
-      <c r="D119" t="s">
-        <v>38</v>
-      </c>
-      <c r="E119" t="s">
-        <v>15</v>
-      </c>
-      <c r="F119" t="s">
+      <c r="G119" t="s">
         <v>206</v>
-      </c>
-      <c r="G119" t="s">
-        <v>207</v>
       </c>
       <c r="H119" t="s">
         <v>26</v>
@@ -6464,94 +6461,94 @@
         <v>34</v>
       </c>
       <c r="J119" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="K119" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="120" spans="1:11">
       <c r="A120" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B120" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C120" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D120" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="E120" t="s">
         <v>31</v>
       </c>
       <c r="F120" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H120" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I120" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J120" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="K120" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="121" spans="1:11">
       <c r="A121" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B121" t="s">
+        <v>401</v>
+      </c>
+      <c r="C121" t="s">
         <v>402</v>
       </c>
-      <c r="C121" t="s">
+      <c r="D121" t="s">
+        <v>14</v>
+      </c>
+      <c r="E121" t="s">
+        <v>15</v>
+      </c>
+      <c r="F121" t="s">
         <v>403</v>
-      </c>
-      <c r="D121" t="s">
-        <v>38</v>
-      </c>
-      <c r="E121" t="s">
-        <v>15</v>
-      </c>
-      <c r="F121" t="s">
-        <v>404</v>
       </c>
       <c r="H121" t="s">
         <v>26</v>
       </c>
       <c r="I121" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J121" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="K121" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="122" spans="1:11">
       <c r="A122" t="s">
+        <v>404</v>
+      </c>
+      <c r="B122" t="s">
         <v>405</v>
       </c>
-      <c r="B122" t="s">
-        <v>406</v>
-      </c>
       <c r="C122" t="s">
+        <v>389</v>
+      </c>
+      <c r="D122" t="s">
+        <v>14</v>
+      </c>
+      <c r="E122" t="s">
+        <v>162</v>
+      </c>
+      <c r="F122" t="s">
         <v>390</v>
-      </c>
-      <c r="D122" t="s">
-        <v>14</v>
-      </c>
-      <c r="E122" t="s">
-        <v>163</v>
-      </c>
-      <c r="F122" t="s">
-        <v>391</v>
       </c>
       <c r="H122" t="s">
         <v>26</v>
@@ -6560,33 +6557,33 @@
         <v>18</v>
       </c>
       <c r="J122" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="K122" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="123" spans="1:11">
       <c r="A123" t="s">
+        <v>407</v>
+      </c>
+      <c r="B123" t="s">
         <v>408</v>
       </c>
-      <c r="B123" t="s">
-        <v>409</v>
-      </c>
       <c r="C123" t="s">
+        <v>143</v>
+      </c>
+      <c r="D123" t="s">
+        <v>14</v>
+      </c>
+      <c r="E123" t="s">
+        <v>15</v>
+      </c>
+      <c r="F123" t="s">
         <v>144</v>
       </c>
-      <c r="D123" t="s">
-        <v>38</v>
-      </c>
-      <c r="E123" t="s">
-        <v>15</v>
-      </c>
-      <c r="F123" t="s">
-        <v>145</v>
-      </c>
       <c r="H123" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I123" t="s">
         <v>18</v>
@@ -6595,18 +6592,18 @@
         <v>19</v>
       </c>
       <c r="K123" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="124" spans="1:11">
       <c r="A124" t="s">
+        <v>409</v>
+      </c>
+      <c r="B124" t="s">
         <v>410</v>
       </c>
-      <c r="B124" t="s">
-        <v>411</v>
-      </c>
       <c r="C124" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D124" t="s">
         <v>14</v>
@@ -6615,74 +6612,74 @@
         <v>31</v>
       </c>
       <c r="F124" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H124" t="s">
         <v>26</v>
       </c>
       <c r="I124" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J124" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="K124" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="125" spans="1:11">
       <c r="A125" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B125" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C125" t="s">
+        <v>396</v>
+      </c>
+      <c r="D125" t="s">
+        <v>14</v>
+      </c>
+      <c r="E125" t="s">
+        <v>15</v>
+      </c>
+      <c r="F125" t="s">
         <v>397</v>
       </c>
-      <c r="D125" t="s">
-        <v>38</v>
-      </c>
-      <c r="E125" t="s">
-        <v>15</v>
-      </c>
-      <c r="F125" t="s">
-        <v>398</v>
-      </c>
       <c r="H125" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I125" t="s">
         <v>27</v>
       </c>
       <c r="J125" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="K125" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="126" spans="1:11">
       <c r="A126" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B126" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C126" t="s">
+        <v>204</v>
+      </c>
+      <c r="D126" t="s">
+        <v>14</v>
+      </c>
+      <c r="E126" t="s">
+        <v>15</v>
+      </c>
+      <c r="F126" t="s">
         <v>205</v>
       </c>
-      <c r="D126" t="s">
-        <v>38</v>
-      </c>
-      <c r="E126" t="s">
-        <v>15</v>
-      </c>
-      <c r="F126" t="s">
+      <c r="G126" t="s">
         <v>206</v>
-      </c>
-      <c r="G126" t="s">
-        <v>207</v>
       </c>
       <c r="H126" t="s">
         <v>26</v>
@@ -6691,126 +6688,126 @@
         <v>34</v>
       </c>
       <c r="J126" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="K126" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="127" spans="1:11">
       <c r="A127" t="s">
+        <v>404</v>
+      </c>
+      <c r="B127" t="s">
         <v>405</v>
       </c>
-      <c r="B127" t="s">
-        <v>406</v>
-      </c>
       <c r="C127" t="s">
+        <v>389</v>
+      </c>
+      <c r="D127" t="s">
+        <v>14</v>
+      </c>
+      <c r="E127" t="s">
+        <v>162</v>
+      </c>
+      <c r="F127" t="s">
         <v>390</v>
       </c>
-      <c r="D127" t="s">
-        <v>14</v>
-      </c>
-      <c r="E127" t="s">
-        <v>163</v>
-      </c>
-      <c r="F127" t="s">
-        <v>391</v>
-      </c>
       <c r="H127" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I127" t="s">
         <v>34</v>
       </c>
       <c r="J127" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="K127" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="128" spans="1:11">
       <c r="A128" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B128" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C128" t="s">
+        <v>402</v>
+      </c>
+      <c r="D128" t="s">
+        <v>14</v>
+      </c>
+      <c r="E128" t="s">
+        <v>15</v>
+      </c>
+      <c r="F128" t="s">
         <v>403</v>
-      </c>
-      <c r="D128" t="s">
-        <v>38</v>
-      </c>
-      <c r="E128" t="s">
-        <v>15</v>
-      </c>
-      <c r="F128" t="s">
-        <v>404</v>
       </c>
       <c r="H128" t="s">
         <v>26</v>
       </c>
       <c r="I128" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J128" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="K128" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="129" spans="1:11">
       <c r="A129" t="s">
+        <v>414</v>
+      </c>
+      <c r="B129" t="s">
         <v>415</v>
       </c>
-      <c r="B129" t="s">
+      <c r="C129" t="s">
         <v>416</v>
       </c>
-      <c r="C129" t="s">
-        <v>417</v>
-      </c>
       <c r="D129" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="E129" t="s">
         <v>31</v>
       </c>
       <c r="F129" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H129" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I129" t="s">
         <v>18</v>
       </c>
       <c r="J129" t="s">
+        <v>418</v>
+      </c>
+      <c r="K129" t="s">
         <v>419</v>
-      </c>
-      <c r="K129" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="130" spans="1:11">
       <c r="A130" t="s">
+        <v>420</v>
+      </c>
+      <c r="B130" t="s">
         <v>421</v>
       </c>
-      <c r="B130" t="s">
+      <c r="C130" t="s">
         <v>422</v>
       </c>
-      <c r="C130" t="s">
+      <c r="D130" t="s">
+        <v>14</v>
+      </c>
+      <c r="E130" t="s">
+        <v>15</v>
+      </c>
+      <c r="F130" t="s">
         <v>423</v>
-      </c>
-      <c r="D130" t="s">
-        <v>38</v>
-      </c>
-      <c r="E130" t="s">
-        <v>15</v>
-      </c>
-      <c r="F130" t="s">
-        <v>424</v>
       </c>
       <c r="H130" t="s">
         <v>26</v>
@@ -6819,62 +6816,62 @@
         <v>18</v>
       </c>
       <c r="J130" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="K130" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="131" spans="1:11">
       <c r="A131" t="s">
+        <v>425</v>
+      </c>
+      <c r="B131" t="s">
         <v>426</v>
       </c>
-      <c r="B131" t="s">
+      <c r="C131" t="s">
         <v>427</v>
       </c>
-      <c r="C131" t="s">
+      <c r="D131" t="s">
+        <v>14</v>
+      </c>
+      <c r="E131" t="s">
+        <v>15</v>
+      </c>
+      <c r="F131" t="s">
         <v>428</v>
       </c>
-      <c r="D131" t="s">
-        <v>38</v>
-      </c>
-      <c r="E131" t="s">
-        <v>15</v>
-      </c>
-      <c r="F131" t="s">
-        <v>429</v>
-      </c>
       <c r="H131" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I131" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J131" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K131" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="132" spans="1:11">
       <c r="A132" t="s">
+        <v>429</v>
+      </c>
+      <c r="B132" t="s">
         <v>430</v>
       </c>
-      <c r="B132" t="s">
-        <v>431</v>
-      </c>
       <c r="C132" t="s">
+        <v>147</v>
+      </c>
+      <c r="D132" t="s">
+        <v>14</v>
+      </c>
+      <c r="E132" t="s">
+        <v>15</v>
+      </c>
+      <c r="F132" t="s">
         <v>148</v>
-      </c>
-      <c r="D132" t="s">
-        <v>38</v>
-      </c>
-      <c r="E132" t="s">
-        <v>15</v>
-      </c>
-      <c r="F132" t="s">
-        <v>149</v>
       </c>
       <c r="H132" t="s">
         <v>26</v>
@@ -6883,62 +6880,62 @@
         <v>27</v>
       </c>
       <c r="J132" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="K132" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="133" spans="1:11">
       <c r="A133" t="s">
+        <v>431</v>
+      </c>
+      <c r="B133" t="s">
         <v>432</v>
       </c>
-      <c r="B133" t="s">
-        <v>433</v>
-      </c>
       <c r="C133" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D133" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="E133" t="s">
         <v>31</v>
       </c>
       <c r="F133" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H133" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I133" t="s">
         <v>34</v>
       </c>
       <c r="J133" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="K133" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="134" spans="1:11">
       <c r="A134" t="s">
+        <v>433</v>
+      </c>
+      <c r="B134" t="s">
         <v>434</v>
       </c>
-      <c r="B134" t="s">
+      <c r="C134" t="s">
         <v>435</v>
       </c>
-      <c r="C134" t="s">
-        <v>436</v>
-      </c>
       <c r="D134" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="E134" t="s">
         <v>31</v>
       </c>
       <c r="F134" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H134" t="s">
         <v>17</v>
@@ -6947,30 +6944,30 @@
         <v>34</v>
       </c>
       <c r="J134" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="K134" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="135" spans="1:11">
       <c r="A135" t="s">
+        <v>420</v>
+      </c>
+      <c r="B135" t="s">
         <v>421</v>
       </c>
-      <c r="B135" t="s">
+      <c r="C135" t="s">
         <v>422</v>
       </c>
-      <c r="C135" t="s">
+      <c r="D135" t="s">
+        <v>14</v>
+      </c>
+      <c r="E135" t="s">
+        <v>15</v>
+      </c>
+      <c r="F135" t="s">
         <v>423</v>
-      </c>
-      <c r="D135" t="s">
-        <v>38</v>
-      </c>
-      <c r="E135" t="s">
-        <v>15</v>
-      </c>
-      <c r="F135" t="s">
-        <v>424</v>
       </c>
       <c r="H135" t="s">
         <v>26</v>
@@ -6979,82 +6976,82 @@
         <v>34</v>
       </c>
       <c r="J135" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="K135" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="136" spans="1:11">
       <c r="A136" t="s">
+        <v>437</v>
+      </c>
+      <c r="B136" t="s">
         <v>438</v>
       </c>
-      <c r="B136" t="s">
+      <c r="C136" t="s">
         <v>439</v>
-      </c>
-      <c r="C136" t="s">
-        <v>440</v>
       </c>
       <c r="D136" t="s">
         <v>24</v>
       </c>
       <c r="F136" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H136" t="s">
         <v>17</v>
       </c>
       <c r="I136" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J136" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="K136" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="137" spans="1:11">
       <c r="A137" t="s">
+        <v>441</v>
+      </c>
+      <c r="B137" t="s">
         <v>442</v>
       </c>
-      <c r="B137" t="s">
-        <v>443</v>
-      </c>
       <c r="C137" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D137" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="E137" t="s">
         <v>31</v>
       </c>
       <c r="F137" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H137" t="s">
         <v>26</v>
       </c>
       <c r="I137" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J137" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="K137" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="138" spans="1:11">
       <c r="A138" t="s">
+        <v>443</v>
+      </c>
+      <c r="B138" t="s">
         <v>444</v>
       </c>
-      <c r="B138" t="s">
-        <v>445</v>
-      </c>
       <c r="C138" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D138" t="s">
         <v>14</v>
@@ -7063,7 +7060,7 @@
         <v>31</v>
       </c>
       <c r="F138" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H138" t="s">
         <v>26</v>
@@ -7072,94 +7069,94 @@
         <v>18</v>
       </c>
       <c r="J138" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K138" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="139" spans="1:11">
       <c r="A139" t="s">
+        <v>446</v>
+      </c>
+      <c r="B139" t="s">
         <v>447</v>
       </c>
-      <c r="B139" t="s">
-        <v>448</v>
-      </c>
       <c r="C139" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D139" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="E139" t="s">
         <v>31</v>
       </c>
       <c r="F139" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H139" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I139" t="s">
         <v>18</v>
       </c>
       <c r="J139" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K139" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="140" spans="1:11">
       <c r="A140" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B140" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C140" t="s">
+        <v>427</v>
+      </c>
+      <c r="D140" t="s">
+        <v>14</v>
+      </c>
+      <c r="E140" t="s">
+        <v>15</v>
+      </c>
+      <c r="F140" t="s">
         <v>428</v>
       </c>
-      <c r="D140" t="s">
-        <v>38</v>
-      </c>
-      <c r="E140" t="s">
-        <v>15</v>
-      </c>
-      <c r="F140" t="s">
-        <v>429</v>
-      </c>
       <c r="H140" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I140" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J140" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K140" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="141" spans="1:11">
       <c r="A141" t="s">
+        <v>449</v>
+      </c>
+      <c r="B141" t="s">
         <v>450</v>
       </c>
-      <c r="B141" t="s">
-        <v>451</v>
-      </c>
       <c r="C141" t="s">
+        <v>248</v>
+      </c>
+      <c r="D141" t="s">
+        <v>14</v>
+      </c>
+      <c r="E141" t="s">
+        <v>15</v>
+      </c>
+      <c r="F141" t="s">
         <v>249</v>
-      </c>
-      <c r="D141" t="s">
-        <v>38</v>
-      </c>
-      <c r="E141" t="s">
-        <v>15</v>
-      </c>
-      <c r="F141" t="s">
-        <v>250</v>
       </c>
       <c r="H141" t="s">
         <v>26</v>
@@ -7168,91 +7165,91 @@
         <v>27</v>
       </c>
       <c r="J141" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K141" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="142" spans="1:11">
       <c r="A142" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B142" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C142" t="s">
+        <v>219</v>
+      </c>
+      <c r="D142" t="s">
+        <v>14</v>
+      </c>
+      <c r="E142" t="s">
+        <v>15</v>
+      </c>
+      <c r="F142" t="s">
         <v>220</v>
       </c>
-      <c r="D142" t="s">
-        <v>38</v>
-      </c>
-      <c r="E142" t="s">
-        <v>15</v>
-      </c>
-      <c r="F142" t="s">
-        <v>221</v>
-      </c>
       <c r="H142" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I142" t="s">
         <v>27</v>
       </c>
       <c r="J142" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K142" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="143" spans="1:11">
       <c r="A143" t="s">
+        <v>452</v>
+      </c>
+      <c r="B143" t="s">
         <v>453</v>
       </c>
-      <c r="B143" t="s">
-        <v>454</v>
-      </c>
       <c r="C143" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D143" t="s">
         <v>24</v>
       </c>
       <c r="F143" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H143" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I143" t="s">
         <v>34</v>
       </c>
       <c r="J143" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K143" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="144" spans="1:11">
       <c r="A144" t="s">
+        <v>454</v>
+      </c>
+      <c r="B144" t="s">
         <v>455</v>
       </c>
-      <c r="B144" t="s">
+      <c r="C144" t="s">
         <v>456</v>
       </c>
-      <c r="C144" t="s">
+      <c r="D144" t="s">
+        <v>14</v>
+      </c>
+      <c r="E144" t="s">
+        <v>15</v>
+      </c>
+      <c r="F144" t="s">
         <v>457</v>
-      </c>
-      <c r="D144" t="s">
-        <v>38</v>
-      </c>
-      <c r="E144" t="s">
-        <v>15</v>
-      </c>
-      <c r="F144" t="s">
-        <v>458</v>
       </c>
       <c r="H144" t="s">
         <v>26</v>
@@ -7261,129 +7258,129 @@
         <v>34</v>
       </c>
       <c r="J144" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="K144" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="145" spans="1:11">
       <c r="A145" t="s">
+        <v>458</v>
+      </c>
+      <c r="B145" t="s">
         <v>459</v>
       </c>
-      <c r="B145" t="s">
-        <v>460</v>
-      </c>
       <c r="C145" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D145" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="E145" t="s">
         <v>31</v>
       </c>
       <c r="F145" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H145" t="s">
         <v>26</v>
       </c>
       <c r="I145" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J145" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K145" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="146" spans="1:11">
       <c r="A146" t="s">
+        <v>460</v>
+      </c>
+      <c r="B146" t="s">
         <v>461</v>
       </c>
-      <c r="B146" t="s">
-        <v>462</v>
-      </c>
       <c r="C146" t="s">
+        <v>204</v>
+      </c>
+      <c r="D146" t="s">
+        <v>14</v>
+      </c>
+      <c r="E146" t="s">
+        <v>15</v>
+      </c>
+      <c r="F146" t="s">
         <v>205</v>
       </c>
-      <c r="D146" t="s">
-        <v>38</v>
-      </c>
-      <c r="E146" t="s">
-        <v>15</v>
-      </c>
-      <c r="F146" t="s">
+      <c r="G146" t="s">
         <v>206</v>
       </c>
-      <c r="G146" t="s">
-        <v>207</v>
-      </c>
       <c r="H146" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I146" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J146" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K146" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="147" spans="1:11">
       <c r="A147" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B147" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C147" t="s">
+        <v>168</v>
+      </c>
+      <c r="D147" t="s">
+        <v>14</v>
+      </c>
+      <c r="E147" t="s">
+        <v>15</v>
+      </c>
+      <c r="F147" t="s">
         <v>169</v>
       </c>
-      <c r="D147" t="s">
-        <v>38</v>
-      </c>
-      <c r="E147" t="s">
-        <v>15</v>
-      </c>
-      <c r="F147" t="s">
-        <v>170</v>
-      </c>
       <c r="H147" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I147" t="s">
         <v>18</v>
       </c>
       <c r="J147" t="s">
+        <v>463</v>
+      </c>
+      <c r="K147" t="s">
         <v>464</v>
-      </c>
-      <c r="K147" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="148" spans="1:11">
       <c r="A148" t="s">
+        <v>465</v>
+      </c>
+      <c r="B148" t="s">
         <v>466</v>
       </c>
-      <c r="B148" t="s">
-        <v>467</v>
-      </c>
       <c r="C148" t="s">
+        <v>215</v>
+      </c>
+      <c r="D148" t="s">
+        <v>14</v>
+      </c>
+      <c r="E148" t="s">
+        <v>15</v>
+      </c>
+      <c r="F148" t="s">
         <v>216</v>
-      </c>
-      <c r="D148" t="s">
-        <v>38</v>
-      </c>
-      <c r="E148" t="s">
-        <v>15</v>
-      </c>
-      <c r="F148" t="s">
-        <v>217</v>
       </c>
       <c r="H148" t="s">
         <v>17</v>
@@ -7392,21 +7389,21 @@
         <v>18</v>
       </c>
       <c r="J148" t="s">
+        <v>463</v>
+      </c>
+      <c r="K148" t="s">
         <v>464</v>
-      </c>
-      <c r="K148" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="149" spans="1:11">
       <c r="A149" t="s">
+        <v>467</v>
+      </c>
+      <c r="B149" t="s">
         <v>468</v>
       </c>
-      <c r="B149" t="s">
-        <v>469</v>
-      </c>
       <c r="C149" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D149" t="s">
         <v>14</v>
@@ -7415,71 +7412,71 @@
         <v>31</v>
       </c>
       <c r="F149" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H149" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I149" t="s">
         <v>18</v>
       </c>
       <c r="J149" t="s">
+        <v>463</v>
+      </c>
+      <c r="K149" t="s">
         <v>464</v>
-      </c>
-      <c r="K149" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="150" spans="1:11">
       <c r="A150" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B150" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C150" t="s">
+        <v>427</v>
+      </c>
+      <c r="D150" t="s">
+        <v>14</v>
+      </c>
+      <c r="E150" t="s">
+        <v>15</v>
+      </c>
+      <c r="F150" t="s">
         <v>428</v>
       </c>
-      <c r="D150" t="s">
-        <v>38</v>
-      </c>
-      <c r="E150" t="s">
-        <v>15</v>
-      </c>
-      <c r="F150" t="s">
-        <v>429</v>
-      </c>
       <c r="H150" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I150" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J150" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K150" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="151" spans="1:11">
       <c r="A151" t="s">
+        <v>470</v>
+      </c>
+      <c r="B151" t="s">
         <v>471</v>
       </c>
-      <c r="B151" t="s">
-        <v>472</v>
-      </c>
       <c r="C151" t="s">
+        <v>238</v>
+      </c>
+      <c r="D151" t="s">
+        <v>14</v>
+      </c>
+      <c r="E151" t="s">
+        <v>15</v>
+      </c>
+      <c r="F151" t="s">
         <v>239</v>
-      </c>
-      <c r="D151" t="s">
-        <v>38</v>
-      </c>
-      <c r="E151" t="s">
-        <v>15</v>
-      </c>
-      <c r="F151" t="s">
-        <v>240</v>
       </c>
       <c r="H151" t="s">
         <v>17</v>
@@ -7488,30 +7485,30 @@
         <v>27</v>
       </c>
       <c r="J151" t="s">
+        <v>463</v>
+      </c>
+      <c r="K151" t="s">
         <v>464</v>
-      </c>
-      <c r="K151" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="152" spans="1:11">
       <c r="A152" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B152" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C152" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D152" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="E152" t="s">
         <v>31</v>
       </c>
       <c r="F152" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H152" t="s">
         <v>26</v>
@@ -7520,62 +7517,62 @@
         <v>27</v>
       </c>
       <c r="J152" t="s">
+        <v>463</v>
+      </c>
+      <c r="K152" t="s">
         <v>464</v>
-      </c>
-      <c r="K152" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="153" spans="1:11">
       <c r="A153" t="s">
+        <v>473</v>
+      </c>
+      <c r="B153" t="s">
         <v>474</v>
       </c>
-      <c r="B153" t="s">
-        <v>475</v>
-      </c>
       <c r="C153" t="s">
+        <v>427</v>
+      </c>
+      <c r="D153" t="s">
+        <v>14</v>
+      </c>
+      <c r="E153" t="s">
+        <v>15</v>
+      </c>
+      <c r="F153" t="s">
         <v>428</v>
       </c>
-      <c r="D153" t="s">
-        <v>38</v>
-      </c>
-      <c r="E153" t="s">
-        <v>15</v>
-      </c>
-      <c r="F153" t="s">
-        <v>429</v>
-      </c>
       <c r="H153" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I153" t="s">
         <v>27</v>
       </c>
       <c r="J153" t="s">
+        <v>463</v>
+      </c>
+      <c r="K153" t="s">
         <v>464</v>
-      </c>
-      <c r="K153" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="154" spans="1:11">
       <c r="A154" t="s">
+        <v>475</v>
+      </c>
+      <c r="B154" t="s">
         <v>476</v>
       </c>
-      <c r="B154" t="s">
-        <v>477</v>
-      </c>
       <c r="C154" t="s">
+        <v>219</v>
+      </c>
+      <c r="D154" t="s">
+        <v>14</v>
+      </c>
+      <c r="E154" t="s">
+        <v>15</v>
+      </c>
+      <c r="F154" t="s">
         <v>220</v>
-      </c>
-      <c r="D154" t="s">
-        <v>38</v>
-      </c>
-      <c r="E154" t="s">
-        <v>15</v>
-      </c>
-      <c r="F154" t="s">
-        <v>221</v>
       </c>
       <c r="H154" t="s">
         <v>17</v>
@@ -7584,94 +7581,94 @@
         <v>34</v>
       </c>
       <c r="J154" t="s">
+        <v>463</v>
+      </c>
+      <c r="K154" t="s">
         <v>464</v>
-      </c>
-      <c r="K154" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="155" spans="1:11">
       <c r="A155" t="s">
+        <v>477</v>
+      </c>
+      <c r="B155" t="s">
         <v>478</v>
       </c>
-      <c r="B155" t="s">
-        <v>479</v>
-      </c>
       <c r="C155" t="s">
+        <v>234</v>
+      </c>
+      <c r="D155" t="s">
+        <v>14</v>
+      </c>
+      <c r="E155" t="s">
+        <v>15</v>
+      </c>
+      <c r="F155" t="s">
         <v>235</v>
       </c>
-      <c r="D155" t="s">
-        <v>38</v>
-      </c>
-      <c r="E155" t="s">
-        <v>15</v>
-      </c>
-      <c r="F155" t="s">
-        <v>236</v>
-      </c>
       <c r="H155" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I155" t="s">
         <v>34</v>
       </c>
       <c r="J155" t="s">
+        <v>463</v>
+      </c>
+      <c r="K155" t="s">
         <v>464</v>
-      </c>
-      <c r="K155" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="156" spans="1:11">
       <c r="A156" t="s">
+        <v>479</v>
+      </c>
+      <c r="B156" t="s">
         <v>480</v>
       </c>
-      <c r="B156" t="s">
+      <c r="C156" t="s">
         <v>481</v>
       </c>
-      <c r="C156" t="s">
+      <c r="D156" t="s">
+        <v>14</v>
+      </c>
+      <c r="E156" t="s">
+        <v>15</v>
+      </c>
+      <c r="F156" t="s">
         <v>482</v>
       </c>
-      <c r="D156" t="s">
-        <v>38</v>
-      </c>
-      <c r="E156" t="s">
-        <v>15</v>
-      </c>
-      <c r="F156" t="s">
-        <v>483</v>
-      </c>
       <c r="H156" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I156" t="s">
         <v>18</v>
       </c>
       <c r="J156" t="s">
+        <v>483</v>
+      </c>
+      <c r="K156" t="s">
         <v>484</v>
-      </c>
-      <c r="K156" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="157" spans="1:11">
       <c r="A157" t="s">
+        <v>485</v>
+      </c>
+      <c r="B157" t="s">
         <v>486</v>
       </c>
-      <c r="B157" t="s">
-        <v>487</v>
-      </c>
       <c r="C157" t="s">
+        <v>481</v>
+      </c>
+      <c r="D157" t="s">
+        <v>14</v>
+      </c>
+      <c r="E157" t="s">
+        <v>15</v>
+      </c>
+      <c r="F157" t="s">
         <v>482</v>
-      </c>
-      <c r="D157" t="s">
-        <v>38</v>
-      </c>
-      <c r="E157" t="s">
-        <v>15</v>
-      </c>
-      <c r="F157" t="s">
-        <v>483</v>
       </c>
       <c r="H157" t="s">
         <v>26</v>
@@ -7680,62 +7677,62 @@
         <v>18</v>
       </c>
       <c r="J157" t="s">
+        <v>483</v>
+      </c>
+      <c r="K157" t="s">
         <v>484</v>
-      </c>
-      <c r="K157" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="158" spans="1:11">
       <c r="A158" t="s">
+        <v>487</v>
+      </c>
+      <c r="B158" t="s">
         <v>488</v>
       </c>
-      <c r="B158" t="s">
-        <v>489</v>
-      </c>
       <c r="C158" t="s">
+        <v>427</v>
+      </c>
+      <c r="D158" t="s">
+        <v>14</v>
+      </c>
+      <c r="E158" t="s">
+        <v>15</v>
+      </c>
+      <c r="F158" t="s">
         <v>428</v>
       </c>
-      <c r="D158" t="s">
-        <v>38</v>
-      </c>
-      <c r="E158" t="s">
-        <v>15</v>
-      </c>
-      <c r="F158" t="s">
-        <v>429</v>
-      </c>
       <c r="H158" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I158" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J158" t="s">
+        <v>483</v>
+      </c>
+      <c r="K158" t="s">
         <v>484</v>
-      </c>
-      <c r="K158" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="159" spans="1:11">
       <c r="A159" t="s">
+        <v>489</v>
+      </c>
+      <c r="B159" t="s">
         <v>490</v>
       </c>
-      <c r="B159" t="s">
+      <c r="C159" t="s">
         <v>491</v>
-      </c>
-      <c r="C159" t="s">
-        <v>492</v>
       </c>
       <c r="D159" t="s">
         <v>24</v>
       </c>
       <c r="F159" t="s">
+        <v>492</v>
+      </c>
+      <c r="G159" t="s">
         <v>493</v>
-      </c>
-      <c r="G159" t="s">
-        <v>494</v>
       </c>
       <c r="H159" t="s">
         <v>17</v>
@@ -7744,30 +7741,30 @@
         <v>27</v>
       </c>
       <c r="J159" t="s">
+        <v>483</v>
+      </c>
+      <c r="K159" t="s">
         <v>484</v>
-      </c>
-      <c r="K159" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="160" spans="1:11">
       <c r="A160" t="s">
+        <v>494</v>
+      </c>
+      <c r="B160" t="s">
         <v>495</v>
       </c>
-      <c r="B160" t="s">
-        <v>496</v>
-      </c>
       <c r="C160" t="s">
+        <v>402</v>
+      </c>
+      <c r="D160" t="s">
+        <v>14</v>
+      </c>
+      <c r="E160" t="s">
+        <v>15</v>
+      </c>
+      <c r="F160" t="s">
         <v>403</v>
-      </c>
-      <c r="D160" t="s">
-        <v>38</v>
-      </c>
-      <c r="E160" t="s">
-        <v>15</v>
-      </c>
-      <c r="F160" t="s">
-        <v>404</v>
       </c>
       <c r="H160" t="s">
         <v>26</v>
@@ -7776,62 +7773,62 @@
         <v>27</v>
       </c>
       <c r="J160" t="s">
+        <v>483</v>
+      </c>
+      <c r="K160" t="s">
         <v>484</v>
-      </c>
-      <c r="K160" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="161" spans="1:11">
       <c r="A161" t="s">
+        <v>496</v>
+      </c>
+      <c r="B161" t="s">
         <v>497</v>
       </c>
-      <c r="B161" t="s">
-        <v>498</v>
-      </c>
       <c r="C161" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D161" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="E161" t="s">
         <v>31</v>
       </c>
       <c r="F161" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H161" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I161" t="s">
         <v>34</v>
       </c>
       <c r="J161" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="K161" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="162" spans="1:11">
       <c r="A162" t="s">
+        <v>498</v>
+      </c>
+      <c r="B162" t="s">
         <v>499</v>
       </c>
-      <c r="B162" t="s">
+      <c r="C162" t="s">
         <v>500</v>
       </c>
-      <c r="C162" t="s">
+      <c r="D162" t="s">
+        <v>14</v>
+      </c>
+      <c r="E162" t="s">
+        <v>15</v>
+      </c>
+      <c r="F162" t="s">
         <v>501</v>
-      </c>
-      <c r="D162" t="s">
-        <v>38</v>
-      </c>
-      <c r="E162" t="s">
-        <v>15</v>
-      </c>
-      <c r="F162" t="s">
-        <v>502</v>
       </c>
       <c r="H162" t="s">
         <v>26</v>
@@ -7840,126 +7837,126 @@
         <v>34</v>
       </c>
       <c r="J162" t="s">
+        <v>483</v>
+      </c>
+      <c r="K162" t="s">
         <v>484</v>
-      </c>
-      <c r="K162" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="163" spans="1:11">
       <c r="A163" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B163" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C163" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D163" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="E163" t="s">
         <v>31</v>
       </c>
       <c r="F163" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H163" t="s">
         <v>26</v>
       </c>
       <c r="I163" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J163" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K163" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="164" spans="1:11">
       <c r="A164" t="s">
+        <v>503</v>
+      </c>
+      <c r="B164" t="s">
         <v>504</v>
       </c>
-      <c r="B164" t="s">
-        <v>505</v>
-      </c>
       <c r="C164" t="s">
+        <v>396</v>
+      </c>
+      <c r="D164" t="s">
+        <v>14</v>
+      </c>
+      <c r="E164" t="s">
+        <v>15</v>
+      </c>
+      <c r="F164" t="s">
         <v>397</v>
       </c>
-      <c r="D164" t="s">
-        <v>38</v>
-      </c>
-      <c r="E164" t="s">
-        <v>15</v>
-      </c>
-      <c r="F164" t="s">
-        <v>398</v>
-      </c>
       <c r="H164" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I164" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J164" t="s">
+        <v>483</v>
+      </c>
+      <c r="K164" t="s">
         <v>484</v>
-      </c>
-      <c r="K164" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="165" spans="1:11">
       <c r="A165" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B165" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C165" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D165" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="E165" t="s">
         <v>31</v>
       </c>
       <c r="F165" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H165" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I165" t="s">
         <v>18</v>
       </c>
       <c r="J165" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="K165" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="166" spans="1:11">
       <c r="A166" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B166" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C166" t="s">
+        <v>168</v>
+      </c>
+      <c r="D166" t="s">
+        <v>14</v>
+      </c>
+      <c r="E166" t="s">
+        <v>15</v>
+      </c>
+      <c r="F166" t="s">
         <v>169</v>
-      </c>
-      <c r="D166" t="s">
-        <v>38</v>
-      </c>
-      <c r="E166" t="s">
-        <v>15</v>
-      </c>
-      <c r="F166" t="s">
-        <v>170</v>
       </c>
       <c r="H166" t="s">
         <v>26</v>
@@ -7968,94 +7965,94 @@
         <v>18</v>
       </c>
       <c r="J166" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="K166" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="167" spans="1:11">
       <c r="A167" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B167" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C167" t="s">
+        <v>427</v>
+      </c>
+      <c r="D167" t="s">
+        <v>14</v>
+      </c>
+      <c r="E167" t="s">
+        <v>15</v>
+      </c>
+      <c r="F167" t="s">
         <v>428</v>
       </c>
-      <c r="D167" t="s">
-        <v>38</v>
-      </c>
-      <c r="E167" t="s">
-        <v>15</v>
-      </c>
-      <c r="F167" t="s">
-        <v>429</v>
-      </c>
       <c r="H167" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I167" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J167" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K167" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="168" spans="1:11">
       <c r="A168" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B168" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C168" t="s">
+        <v>402</v>
+      </c>
+      <c r="D168" t="s">
+        <v>14</v>
+      </c>
+      <c r="E168" t="s">
+        <v>15</v>
+      </c>
+      <c r="F168" t="s">
         <v>403</v>
       </c>
-      <c r="D168" t="s">
-        <v>38</v>
-      </c>
-      <c r="E168" t="s">
-        <v>15</v>
-      </c>
-      <c r="F168" t="s">
-        <v>404</v>
-      </c>
       <c r="H168" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I168" t="s">
         <v>27</v>
       </c>
       <c r="J168" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="K168" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="169" spans="1:11">
       <c r="A169" t="s">
+        <v>510</v>
+      </c>
+      <c r="B169" t="s">
         <v>511</v>
       </c>
-      <c r="B169" t="s">
-        <v>512</v>
-      </c>
       <c r="C169" t="s">
+        <v>178</v>
+      </c>
+      <c r="D169" t="s">
+        <v>14</v>
+      </c>
+      <c r="E169" t="s">
+        <v>15</v>
+      </c>
+      <c r="F169" t="s">
         <v>179</v>
-      </c>
-      <c r="D169" t="s">
-        <v>38</v>
-      </c>
-      <c r="E169" t="s">
-        <v>15</v>
-      </c>
-      <c r="F169" t="s">
-        <v>180</v>
       </c>
       <c r="H169" t="s">
         <v>17</v>
@@ -8064,30 +8061,30 @@
         <v>27</v>
       </c>
       <c r="J169" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="K169" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="170" spans="1:11">
       <c r="A170" t="s">
+        <v>512</v>
+      </c>
+      <c r="B170" t="s">
         <v>513</v>
       </c>
-      <c r="B170" t="s">
-        <v>514</v>
-      </c>
       <c r="C170" t="s">
+        <v>234</v>
+      </c>
+      <c r="D170" t="s">
+        <v>14</v>
+      </c>
+      <c r="E170" t="s">
+        <v>15</v>
+      </c>
+      <c r="F170" t="s">
         <v>235</v>
-      </c>
-      <c r="D170" t="s">
-        <v>38</v>
-      </c>
-      <c r="E170" t="s">
-        <v>15</v>
-      </c>
-      <c r="F170" t="s">
-        <v>236</v>
       </c>
       <c r="H170" t="s">
         <v>17</v>
@@ -8096,152 +8093,152 @@
         <v>34</v>
       </c>
       <c r="J170" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="K170" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="171" spans="1:11">
       <c r="A171" t="s">
+        <v>514</v>
+      </c>
+      <c r="B171" t="s">
         <v>515</v>
       </c>
-      <c r="B171" t="s">
-        <v>516</v>
-      </c>
       <c r="C171" t="s">
+        <v>238</v>
+      </c>
+      <c r="D171" t="s">
+        <v>14</v>
+      </c>
+      <c r="E171" t="s">
+        <v>15</v>
+      </c>
+      <c r="F171" t="s">
         <v>239</v>
       </c>
-      <c r="D171" t="s">
-        <v>38</v>
-      </c>
-      <c r="E171" t="s">
-        <v>15</v>
-      </c>
-      <c r="F171" t="s">
-        <v>240</v>
-      </c>
       <c r="H171" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I171" t="s">
         <v>34</v>
       </c>
       <c r="J171" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="K171" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="172" spans="1:11">
       <c r="A172" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B172" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C172" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D172" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="E172" t="s">
         <v>31</v>
       </c>
       <c r="F172" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H172" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I172" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J172" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="K172" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="173" spans="1:11">
       <c r="A173" t="s">
+        <v>517</v>
+      </c>
+      <c r="B173" t="s">
         <v>518</v>
       </c>
-      <c r="B173" t="s">
-        <v>519</v>
-      </c>
       <c r="C173" t="s">
+        <v>178</v>
+      </c>
+      <c r="D173" t="s">
+        <v>14</v>
+      </c>
+      <c r="E173" t="s">
+        <v>15</v>
+      </c>
+      <c r="F173" t="s">
         <v>179</v>
-      </c>
-      <c r="D173" t="s">
-        <v>38</v>
-      </c>
-      <c r="E173" t="s">
-        <v>15</v>
-      </c>
-      <c r="F173" t="s">
-        <v>180</v>
       </c>
       <c r="H173" t="s">
         <v>26</v>
       </c>
       <c r="I173" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J173" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="K173" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="174" spans="1:11">
       <c r="A174" t="s">
+        <v>519</v>
+      </c>
+      <c r="B174" t="s">
         <v>520</v>
       </c>
-      <c r="B174" t="s">
-        <v>521</v>
-      </c>
       <c r="C174" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D174" t="s">
         <v>24</v>
       </c>
       <c r="H174" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I174" t="s">
         <v>18</v>
       </c>
       <c r="J174" t="s">
+        <v>521</v>
+      </c>
+      <c r="K174" t="s">
         <v>522</v>
-      </c>
-      <c r="K174" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="175" spans="1:11">
       <c r="A175" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B175" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C175" t="s">
         <v>37</v>
       </c>
       <c r="D175" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="E175" t="s">
         <v>31</v>
       </c>
       <c r="F175" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H175" t="s">
         <v>26</v>
@@ -8250,62 +8247,62 @@
         <v>18</v>
       </c>
       <c r="J175" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="K175" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="176" spans="1:11">
       <c r="A176" t="s">
+        <v>525</v>
+      </c>
+      <c r="B176" t="s">
         <v>526</v>
       </c>
-      <c r="B176" t="s">
-        <v>527</v>
-      </c>
       <c r="C176" t="s">
+        <v>238</v>
+      </c>
+      <c r="D176" t="s">
+        <v>14</v>
+      </c>
+      <c r="E176" t="s">
+        <v>15</v>
+      </c>
+      <c r="F176" t="s">
         <v>239</v>
       </c>
-      <c r="D176" t="s">
-        <v>38</v>
-      </c>
-      <c r="E176" t="s">
-        <v>15</v>
-      </c>
-      <c r="F176" t="s">
-        <v>240</v>
-      </c>
       <c r="H176" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I176" t="s">
         <v>27</v>
       </c>
       <c r="J176" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="K176" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="177" spans="1:11">
       <c r="A177" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B177" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C177" t="s">
+        <v>200</v>
+      </c>
+      <c r="D177" t="s">
+        <v>14</v>
+      </c>
+      <c r="E177" t="s">
+        <v>15</v>
+      </c>
+      <c r="F177" t="s">
         <v>201</v>
-      </c>
-      <c r="D177" t="s">
-        <v>38</v>
-      </c>
-      <c r="E177" t="s">
-        <v>15</v>
-      </c>
-      <c r="F177" t="s">
-        <v>202</v>
       </c>
       <c r="H177" t="s">
         <v>26</v>
@@ -8314,62 +8311,62 @@
         <v>27</v>
       </c>
       <c r="J177" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="K177" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="178" spans="1:11">
       <c r="A178" t="s">
+        <v>529</v>
+      </c>
+      <c r="B178" t="s">
         <v>530</v>
       </c>
-      <c r="B178" t="s">
-        <v>531</v>
-      </c>
       <c r="C178" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D178" t="s">
         <v>24</v>
       </c>
       <c r="F178" t="s">
+        <v>317</v>
+      </c>
+      <c r="G178" t="s">
         <v>318</v>
       </c>
-      <c r="G178" t="s">
-        <v>319</v>
-      </c>
       <c r="H178" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I178" t="s">
         <v>34</v>
       </c>
       <c r="J178" t="s">
+        <v>521</v>
+      </c>
+      <c r="K178" t="s">
         <v>522</v>
-      </c>
-      <c r="K178" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="179" spans="1:11">
       <c r="A179" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B179" t="s">
+        <v>531</v>
+      </c>
+      <c r="C179" t="s">
         <v>532</v>
-      </c>
-      <c r="C179" t="s">
-        <v>533</v>
       </c>
       <c r="D179" t="s">
         <v>24</v>
       </c>
       <c r="E179" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F179" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H179" t="s">
         <v>26</v>
@@ -8378,18 +8375,18 @@
         <v>34</v>
       </c>
       <c r="J179" t="s">
+        <v>521</v>
+      </c>
+      <c r="K179" t="s">
         <v>522</v>
-      </c>
-      <c r="K179" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="180" spans="1:11">
       <c r="A180" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B180" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C180" t="s">
         <v>30</v>
@@ -8407,103 +8404,103 @@
         <v>33</v>
       </c>
       <c r="H180" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I180" t="s">
         <v>34</v>
       </c>
       <c r="J180" t="s">
+        <v>521</v>
+      </c>
+      <c r="K180" t="s">
         <v>522</v>
-      </c>
-      <c r="K180" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="181" spans="1:11">
       <c r="A181" t="s">
+        <v>535</v>
+      </c>
+      <c r="B181" t="s">
         <v>536</v>
       </c>
-      <c r="B181" t="s">
-        <v>537</v>
-      </c>
       <c r="C181" t="s">
+        <v>325</v>
+      </c>
+      <c r="D181" t="s">
+        <v>14</v>
+      </c>
+      <c r="E181" t="s">
+        <v>15</v>
+      </c>
+      <c r="F181" t="s">
         <v>326</v>
       </c>
-      <c r="D181" t="s">
-        <v>14</v>
-      </c>
-      <c r="E181" t="s">
-        <v>15</v>
-      </c>
-      <c r="F181" t="s">
-        <v>327</v>
-      </c>
       <c r="H181" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I181" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J181" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="K181" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="182" spans="1:11">
       <c r="A182" t="s">
+        <v>537</v>
+      </c>
+      <c r="B182" t="s">
         <v>538</v>
       </c>
-      <c r="B182" t="s">
+      <c r="C182" t="s">
         <v>539</v>
-      </c>
-      <c r="C182" t="s">
-        <v>540</v>
       </c>
       <c r="D182" t="s">
         <v>24</v>
       </c>
       <c r="F182" t="s">
+        <v>540</v>
+      </c>
+      <c r="G182" t="s">
         <v>541</v>
       </c>
-      <c r="G182" t="s">
-        <v>542</v>
-      </c>
       <c r="H182" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I182" t="s">
         <v>18</v>
       </c>
       <c r="J182" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K182" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="183" spans="1:11">
       <c r="A183" t="s">
+        <v>543</v>
+      </c>
+      <c r="B183" t="s">
         <v>544</v>
       </c>
-      <c r="B183" t="s">
+      <c r="C183" t="s">
         <v>545</v>
-      </c>
-      <c r="C183" t="s">
-        <v>546</v>
       </c>
       <c r="D183" t="s">
         <v>24</v>
       </c>
       <c r="E183" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F183" t="s">
+        <v>546</v>
+      </c>
+      <c r="G183" t="s">
         <v>547</v>
-      </c>
-      <c r="G183" t="s">
-        <v>548</v>
       </c>
       <c r="H183" t="s">
         <v>17</v>
@@ -8512,30 +8509,30 @@
         <v>18</v>
       </c>
       <c r="J183" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="K183" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="184" spans="1:11">
       <c r="A184" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B184" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C184" t="s">
+        <v>113</v>
+      </c>
+      <c r="D184" t="s">
+        <v>14</v>
+      </c>
+      <c r="E184" t="s">
+        <v>15</v>
+      </c>
+      <c r="F184" t="s">
         <v>114</v>
-      </c>
-      <c r="D184" t="s">
-        <v>38</v>
-      </c>
-      <c r="E184" t="s">
-        <v>15</v>
-      </c>
-      <c r="F184" t="s">
-        <v>115</v>
       </c>
       <c r="H184" t="s">
         <v>26</v>
@@ -8544,94 +8541,94 @@
         <v>18</v>
       </c>
       <c r="J184" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K184" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="185" spans="1:11">
       <c r="A185" t="s">
+        <v>549</v>
+      </c>
+      <c r="B185" t="s">
         <v>550</v>
       </c>
-      <c r="B185" t="s">
-        <v>551</v>
-      </c>
       <c r="C185" t="s">
+        <v>337</v>
+      </c>
+      <c r="D185" t="s">
+        <v>14</v>
+      </c>
+      <c r="E185" t="s">
+        <v>15</v>
+      </c>
+      <c r="F185" t="s">
         <v>338</v>
-      </c>
-      <c r="D185" t="s">
-        <v>38</v>
-      </c>
-      <c r="E185" t="s">
-        <v>15</v>
-      </c>
-      <c r="F185" t="s">
-        <v>339</v>
       </c>
       <c r="H185" t="s">
         <v>26</v>
       </c>
       <c r="I185" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J185" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K185" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="186" spans="1:11">
       <c r="A186" t="s">
+        <v>551</v>
+      </c>
+      <c r="B186" t="s">
         <v>552</v>
       </c>
-      <c r="B186" t="s">
-        <v>553</v>
-      </c>
       <c r="C186" t="s">
+        <v>107</v>
+      </c>
+      <c r="D186" t="s">
+        <v>14</v>
+      </c>
+      <c r="E186" t="s">
+        <v>15</v>
+      </c>
+      <c r="F186" t="s">
         <v>108</v>
       </c>
-      <c r="D186" t="s">
-        <v>38</v>
-      </c>
-      <c r="E186" t="s">
-        <v>15</v>
-      </c>
-      <c r="F186" t="s">
+      <c r="H186" t="s">
         <v>109</v>
-      </c>
-      <c r="H186" t="s">
-        <v>110</v>
       </c>
       <c r="I186" t="s">
         <v>27</v>
       </c>
       <c r="J186" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K186" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="187" spans="1:11">
       <c r="A187" t="s">
+        <v>553</v>
+      </c>
+      <c r="B187" t="s">
         <v>554</v>
       </c>
-      <c r="B187" t="s">
-        <v>555</v>
-      </c>
       <c r="C187" t="s">
+        <v>143</v>
+      </c>
+      <c r="D187" t="s">
+        <v>14</v>
+      </c>
+      <c r="E187" t="s">
+        <v>15</v>
+      </c>
+      <c r="F187" t="s">
         <v>144</v>
-      </c>
-      <c r="D187" t="s">
-        <v>38</v>
-      </c>
-      <c r="E187" t="s">
-        <v>15</v>
-      </c>
-      <c r="F187" t="s">
-        <v>145</v>
       </c>
       <c r="H187" t="s">
         <v>26</v>
@@ -8640,106 +8637,106 @@
         <v>27</v>
       </c>
       <c r="J187" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K187" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="188" spans="1:11">
       <c r="A188" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B188" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C188" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D188" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="E188" t="s">
         <v>31</v>
       </c>
       <c r="F188" t="s">
+        <v>103</v>
+      </c>
+      <c r="H188" t="s">
         <v>104</v>
-      </c>
-      <c r="H188" t="s">
-        <v>105</v>
       </c>
       <c r="I188" t="s">
         <v>27</v>
       </c>
       <c r="J188" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K188" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="189" spans="1:11">
       <c r="A189" t="s">
+        <v>556</v>
+      </c>
+      <c r="B189" t="s">
         <v>557</v>
       </c>
-      <c r="B189" t="s">
-        <v>558</v>
-      </c>
       <c r="C189" t="s">
+        <v>219</v>
+      </c>
+      <c r="D189" t="s">
+        <v>14</v>
+      </c>
+      <c r="E189" t="s">
+        <v>15</v>
+      </c>
+      <c r="F189" t="s">
         <v>220</v>
       </c>
-      <c r="D189" t="s">
-        <v>38</v>
-      </c>
-      <c r="E189" t="s">
-        <v>15</v>
-      </c>
-      <c r="F189" t="s">
-        <v>221</v>
-      </c>
       <c r="H189" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I189" t="s">
         <v>34</v>
       </c>
       <c r="J189" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K189" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="190" spans="1:11">
       <c r="A190" t="s">
+        <v>556</v>
+      </c>
+      <c r="B190" t="s">
         <v>557</v>
       </c>
-      <c r="B190" t="s">
-        <v>558</v>
-      </c>
       <c r="C190" t="s">
+        <v>219</v>
+      </c>
+      <c r="D190" t="s">
+        <v>14</v>
+      </c>
+      <c r="E190" t="s">
+        <v>15</v>
+      </c>
+      <c r="F190" t="s">
         <v>220</v>
-      </c>
-      <c r="D190" t="s">
-        <v>38</v>
-      </c>
-      <c r="E190" t="s">
-        <v>15</v>
-      </c>
-      <c r="F190" t="s">
-        <v>221</v>
       </c>
       <c r="H190" t="s">
         <v>26</v>
       </c>
       <c r="I190" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J190" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K190" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
   </sheetData>

--- a/DATA-ENS-2026-2027_surveillances.xlsx
+++ b/DATA-ENS-2026-2027_surveillances.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1885" uniqueCount="558">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1911" uniqueCount="556">
   <si>
     <t>Enseignements</t>
   </si>
@@ -107,6 +107,9 @@
     <t>Vacataire</t>
   </si>
   <si>
+    <t xml:space="preserve">Doctorant (Master) </t>
+  </si>
+  <si>
     <t>amrais@yahoo.com</t>
   </si>
   <si>
@@ -323,9 +326,6 @@
     <t>ARAB ABDELMADJID</t>
   </si>
   <si>
-    <t>Doctorat</t>
-  </si>
-  <si>
     <t>arab4abdelmadjid@gmail.com</t>
   </si>
   <si>
@@ -419,9 +419,6 @@
     <t>GHALEM ABDELHAK</t>
   </si>
   <si>
-    <t xml:space="preserve">Doctorant (Master) </t>
-  </si>
-  <si>
     <t>ghalem.abdelhak@yahoo.com</t>
   </si>
   <si>
@@ -489,9 +486,6 @@
   </si>
   <si>
     <t>MAHKOUKA ZAZA</t>
-  </si>
-  <si>
-    <t>Master</t>
   </si>
   <si>
     <t>mahkouka.zaza@gmail.com</t>
@@ -1877,12 +1871,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -2216,7 +2216,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2240,16 +2240,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -2258,93 +2258,94 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2690,14 +2691,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:K190"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="42.4285714285714" customWidth="1"/>
     <col min="3" max="3" width="33.4285714285714" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="5.14285714285714" customWidth="1"/>
+    <col min="5" max="5" width="32.2857142857143" customWidth="1"/>
     <col min="6" max="6" width="15.8571428571429" customWidth="1"/>
     <col min="7" max="7" width="15.7142857142857" customWidth="1"/>
     <col min="8" max="8" width="15.8571428571429" customWidth="1"/>
@@ -2739,7 +2740,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" hidden="1" spans="1:11">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -2784,17 +2785,17 @@
       <c r="D3" t="s">
         <v>24</v>
       </c>
-      <c r="E3" t="s">
-        <v>15</v>
+      <c r="E3" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="F3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J3" t="s">
         <v>19</v>
@@ -2803,33 +2804,33 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" hidden="1" spans="1:11">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
         <v>14</v>
       </c>
       <c r="E4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J4" t="s">
         <v>19</v>
@@ -2838,30 +2839,30 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" hidden="1" spans="1:11">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
         <v>14</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H5" t="s">
         <v>17</v>
       </c>
       <c r="I5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J5" t="s">
         <v>19</v>
@@ -2872,28 +2873,31 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
         <v>24</v>
       </c>
+      <c r="E6" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="F6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J6" t="s">
         <v>19</v>
@@ -2902,131 +2906,137 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" hidden="1" spans="1:11">
       <c r="A7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D7" t="s">
         <v>14</v>
       </c>
       <c r="H7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I7" t="s">
         <v>18</v>
       </c>
       <c r="J7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D8" t="s">
         <v>24</v>
       </c>
+      <c r="E8" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="H8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D9" t="s">
         <v>24</v>
       </c>
+      <c r="E9" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="F9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H9" t="s">
         <v>17</v>
       </c>
       <c r="I9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D10" t="s">
         <v>24</v>
       </c>
-      <c r="E10" t="s">
-        <v>31</v>
+      <c r="E10" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="F10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" hidden="1" spans="1:11">
       <c r="A11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D11" t="s">
         <v>14</v>
@@ -3035,218 +3045,227 @@
         <v>17</v>
       </c>
       <c r="I11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K11" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" hidden="1" spans="1:11">
+      <c r="A12" t="s">
+        <v>69</v>
+      </c>
+      <c r="B12" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" t="s">
+        <v>71</v>
+      </c>
+      <c r="D12" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I12" t="s">
+        <v>35</v>
+      </c>
+      <c r="J12" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" t="s">
-        <v>68</v>
-      </c>
-      <c r="B12" t="s">
-        <v>69</v>
-      </c>
-      <c r="C12" t="s">
-        <v>70</v>
-      </c>
-      <c r="D12" t="s">
-        <v>14</v>
-      </c>
-      <c r="H12" t="s">
-        <v>26</v>
-      </c>
-      <c r="I12" t="s">
-        <v>34</v>
-      </c>
-      <c r="J12" t="s">
-        <v>49</v>
-      </c>
       <c r="K12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D13" t="s">
         <v>24</v>
       </c>
+      <c r="E13" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="H13" t="s">
+        <v>49</v>
+      </c>
+      <c r="I13" t="s">
+        <v>40</v>
+      </c>
+      <c r="J13" t="s">
+        <v>56</v>
+      </c>
+      <c r="K13" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="14" hidden="1" spans="1:11">
+      <c r="A14" t="s">
+        <v>75</v>
+      </c>
+      <c r="B14" t="s">
+        <v>76</v>
+      </c>
+      <c r="C14" t="s">
+        <v>77</v>
+      </c>
+      <c r="D14" t="s">
+        <v>14</v>
+      </c>
+      <c r="H14" t="s">
+        <v>78</v>
+      </c>
+      <c r="I14" t="s">
+        <v>40</v>
+      </c>
+      <c r="J14" t="s">
+        <v>56</v>
+      </c>
+      <c r="K14" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" hidden="1" spans="1:11">
+      <c r="A15" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" t="s">
+        <v>79</v>
+      </c>
+      <c r="C15" t="s">
         <v>48</v>
       </c>
-      <c r="I13" t="s">
-        <v>39</v>
-      </c>
-      <c r="J13" t="s">
-        <v>55</v>
-      </c>
-      <c r="K13" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14" t="s">
-        <v>74</v>
-      </c>
-      <c r="B14" t="s">
-        <v>75</v>
-      </c>
-      <c r="C14" t="s">
-        <v>76</v>
-      </c>
-      <c r="D14" t="s">
-        <v>14</v>
-      </c>
-      <c r="H14" t="s">
-        <v>77</v>
-      </c>
-      <c r="I14" t="s">
-        <v>39</v>
-      </c>
-      <c r="J14" t="s">
-        <v>55</v>
-      </c>
-      <c r="K14" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" t="s">
-        <v>45</v>
-      </c>
-      <c r="B15" t="s">
-        <v>78</v>
-      </c>
-      <c r="C15" t="s">
-        <v>47</v>
-      </c>
       <c r="D15" t="s">
         <v>14</v>
       </c>
       <c r="H15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I15" t="s">
         <v>18</v>
       </c>
       <c r="J15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D16" t="s">
         <v>24</v>
       </c>
+      <c r="E16" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="H16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I16" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J16" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D17" t="s">
         <v>24</v>
       </c>
+      <c r="E17" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="F17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H17" t="s">
         <v>17</v>
       </c>
       <c r="I17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B18" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C18" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D18" t="s">
         <v>24</v>
       </c>
-      <c r="E18" t="s">
-        <v>31</v>
+      <c r="E18" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="F18" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J18" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K18" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="19" hidden="1" spans="1:11">
       <c r="A19" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B19" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C19" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D19" t="s">
         <v>14</v>
@@ -3255,137 +3274,143 @@
         <v>17</v>
       </c>
       <c r="I19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K19" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" hidden="1" spans="1:11">
       <c r="A20" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B20" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C20" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D20" t="s">
         <v>14</v>
       </c>
       <c r="H20" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I20" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J20" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B21" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C21" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D21" t="s">
         <v>24</v>
       </c>
+      <c r="E21" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="H21" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I21" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J21" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K21" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="22" hidden="1" spans="1:11">
       <c r="A22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B22" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C22" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D22" t="s">
         <v>14</v>
       </c>
       <c r="H22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I22" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B23" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C23" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D23" t="s">
         <v>24</v>
       </c>
+      <c r="E23" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="F23" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I23" t="s">
         <v>18</v>
       </c>
       <c r="J23" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K23" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B24" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C24" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D24" t="s">
         <v>24</v>
       </c>
-      <c r="E24" t="s">
-        <v>97</v>
+      <c r="E24" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="F24" t="s">
         <v>98</v>
@@ -3394,19 +3419,19 @@
         <v>99</v>
       </c>
       <c r="H24" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I24" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J24" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K24" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="25" hidden="1" spans="1:11">
       <c r="A25" t="s">
         <v>100</v>
       </c>
@@ -3420,7 +3445,7 @@
         <v>14</v>
       </c>
       <c r="E25" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F25" t="s">
         <v>103</v>
@@ -3429,16 +3454,16 @@
         <v>104</v>
       </c>
       <c r="I25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J25" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K25" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="26" hidden="1" spans="1:11">
       <c r="A26" t="s">
         <v>105</v>
       </c>
@@ -3461,16 +3486,16 @@
         <v>109</v>
       </c>
       <c r="I26" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J26" t="s">
         <v>110</v>
       </c>
       <c r="K26" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="27" hidden="1" spans="1:11">
       <c r="A27" t="s">
         <v>111</v>
       </c>
@@ -3490,19 +3515,19 @@
         <v>114</v>
       </c>
       <c r="H27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J27" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K27" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="28" hidden="1" spans="1:11">
       <c r="A28" t="s">
         <v>115</v>
       </c>
@@ -3525,16 +3550,16 @@
         <v>109</v>
       </c>
       <c r="I28" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J28" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K28" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="29" hidden="1" spans="1:11">
       <c r="A29" t="s">
         <v>117</v>
       </c>
@@ -3554,16 +3579,16 @@
         <v>120</v>
       </c>
       <c r="H29" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I29" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J29" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K29" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -3579,6 +3604,9 @@
       <c r="D30" t="s">
         <v>24</v>
       </c>
+      <c r="E30" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="F30" t="s">
         <v>124</v>
       </c>
@@ -3589,85 +3617,88 @@
         <v>104</v>
       </c>
       <c r="I30" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J30" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K30" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="31" spans="1:11">
-      <c r="A31" t="s">
+      <c r="A31" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D31" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E31" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F31" t="s">
         <v>129</v>
       </c>
-      <c r="F31" t="s">
+      <c r="G31" t="s">
         <v>130</v>
-      </c>
-      <c r="G31" t="s">
-        <v>131</v>
       </c>
       <c r="H31" t="s">
         <v>109</v>
       </c>
       <c r="I31" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J31" t="s">
+        <v>131</v>
+      </c>
+      <c r="K31" t="s">
         <v>132</v>
-      </c>
-      <c r="K31" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" t="s">
+        <v>133</v>
+      </c>
+      <c r="B32" t="s">
         <v>134</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" t="s">
         <v>135</v>
-      </c>
-      <c r="C32" t="s">
-        <v>136</v>
       </c>
       <c r="D32" t="s">
         <v>24</v>
       </c>
+      <c r="E32" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="F32" t="s">
+        <v>136</v>
+      </c>
+      <c r="H32" t="s">
+        <v>27</v>
+      </c>
+      <c r="I32" t="s">
+        <v>55</v>
+      </c>
+      <c r="J32" t="s">
+        <v>131</v>
+      </c>
+      <c r="K32" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="33" hidden="1" spans="1:11">
+      <c r="A33" t="s">
         <v>137</v>
       </c>
-      <c r="H32" t="s">
-        <v>26</v>
-      </c>
-      <c r="I32" t="s">
-        <v>54</v>
-      </c>
-      <c r="J32" t="s">
-        <v>132</v>
-      </c>
-      <c r="K32" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11">
-      <c r="A33" t="s">
+      <c r="B33" t="s">
         <v>138</v>
-      </c>
-      <c r="B33" t="s">
-        <v>139</v>
       </c>
       <c r="C33" t="s">
         <v>107</v>
@@ -3685,120 +3716,120 @@
         <v>109</v>
       </c>
       <c r="I33" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J33" t="s">
+        <v>139</v>
+      </c>
+      <c r="K33" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="34" hidden="1" spans="1:11">
+      <c r="A34" t="s">
         <v>140</v>
       </c>
-      <c r="K33" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11">
-      <c r="A34" t="s">
+      <c r="B34" t="s">
         <v>141</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
         <v>142</v>
       </c>
-      <c r="C34" t="s">
+      <c r="D34" t="s">
+        <v>14</v>
+      </c>
+      <c r="E34" t="s">
+        <v>15</v>
+      </c>
+      <c r="F34" t="s">
         <v>143</v>
-      </c>
-      <c r="D34" t="s">
-        <v>14</v>
-      </c>
-      <c r="E34" t="s">
-        <v>15</v>
-      </c>
-      <c r="F34" t="s">
-        <v>144</v>
       </c>
       <c r="H34" t="s">
         <v>104</v>
       </c>
       <c r="I34" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J34" t="s">
+        <v>131</v>
+      </c>
+      <c r="K34" t="s">
         <v>132</v>
       </c>
-      <c r="K34" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11">
+    </row>
+    <row r="35" hidden="1" spans="1:11">
       <c r="A35" t="s">
+        <v>144</v>
+      </c>
+      <c r="B35" t="s">
         <v>145</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" t="s">
         <v>146</v>
       </c>
-      <c r="C35" t="s">
+      <c r="D35" t="s">
+        <v>14</v>
+      </c>
+      <c r="E35" t="s">
+        <v>15</v>
+      </c>
+      <c r="F35" t="s">
         <v>147</v>
-      </c>
-      <c r="D35" t="s">
-        <v>14</v>
-      </c>
-      <c r="E35" t="s">
-        <v>15</v>
-      </c>
-      <c r="F35" t="s">
-        <v>148</v>
       </c>
       <c r="H35" t="s">
         <v>109</v>
       </c>
       <c r="I35" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J35" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K35" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" t="s">
+        <v>149</v>
+      </c>
+      <c r="B36" t="s">
         <v>150</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
         <v>151</v>
-      </c>
-      <c r="C36" t="s">
-        <v>152</v>
       </c>
       <c r="D36" t="s">
         <v>24</v>
       </c>
-      <c r="E36" t="s">
+      <c r="E36" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F36" t="s">
+        <v>152</v>
+      </c>
+      <c r="G36" t="s">
         <v>153</v>
-      </c>
-      <c r="F36" t="s">
-        <v>154</v>
-      </c>
-      <c r="G36" t="s">
-        <v>155</v>
       </c>
       <c r="H36" t="s">
         <v>17</v>
       </c>
       <c r="I36" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J36" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K36" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="37" hidden="1" spans="1:11">
       <c r="A37" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B37" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C37" t="s">
         <v>119</v>
@@ -3813,36 +3844,36 @@
         <v>120</v>
       </c>
       <c r="H37" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I37" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J37" t="s">
+        <v>156</v>
+      </c>
+      <c r="K37" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="38" hidden="1" spans="1:11">
+      <c r="A38" t="s">
+        <v>157</v>
+      </c>
+      <c r="B38" t="s">
         <v>158</v>
       </c>
-      <c r="K37" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11">
-      <c r="A38" t="s">
+      <c r="C38" t="s">
         <v>159</v>
       </c>
-      <c r="B38" t="s">
+      <c r="D38" t="s">
+        <v>14</v>
+      </c>
+      <c r="E38" t="s">
         <v>160</v>
       </c>
-      <c r="C38" t="s">
+      <c r="F38" t="s">
         <v>161</v>
-      </c>
-      <c r="D38" t="s">
-        <v>14</v>
-      </c>
-      <c r="E38" t="s">
-        <v>162</v>
-      </c>
-      <c r="F38" t="s">
-        <v>163</v>
       </c>
       <c r="H38" t="s">
         <v>109</v>
@@ -3851,30 +3882,30 @@
         <v>18</v>
       </c>
       <c r="J38" t="s">
+        <v>162</v>
+      </c>
+      <c r="K38" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="39" hidden="1" spans="1:11">
+      <c r="A39" t="s">
         <v>164</v>
       </c>
-      <c r="K38" t="s">
+      <c r="B39" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="39" spans="1:11">
-      <c r="A39" t="s">
+      <c r="C39" t="s">
         <v>166</v>
       </c>
-      <c r="B39" t="s">
+      <c r="D39" t="s">
+        <v>14</v>
+      </c>
+      <c r="E39" t="s">
+        <v>15</v>
+      </c>
+      <c r="F39" t="s">
         <v>167</v>
-      </c>
-      <c r="C39" t="s">
-        <v>168</v>
-      </c>
-      <c r="D39" t="s">
-        <v>14</v>
-      </c>
-      <c r="E39" t="s">
-        <v>15</v>
-      </c>
-      <c r="F39" t="s">
-        <v>169</v>
       </c>
       <c r="H39" t="s">
         <v>17</v>
@@ -3883,219 +3914,222 @@
         <v>18</v>
       </c>
       <c r="J39" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="K39" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="40" hidden="1" spans="1:11">
       <c r="A40" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B40" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C40" t="s">
+        <v>146</v>
+      </c>
+      <c r="D40" t="s">
+        <v>14</v>
+      </c>
+      <c r="E40" t="s">
+        <v>15</v>
+      </c>
+      <c r="F40" t="s">
         <v>147</v>
       </c>
-      <c r="D40" t="s">
-        <v>14</v>
-      </c>
-      <c r="E40" t="s">
-        <v>15</v>
-      </c>
-      <c r="F40" t="s">
-        <v>148</v>
-      </c>
       <c r="H40" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I40" t="s">
         <v>18</v>
       </c>
       <c r="J40" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="K40" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="41" hidden="1" spans="1:11">
       <c r="A41" t="s">
+        <v>170</v>
+      </c>
+      <c r="B41" t="s">
+        <v>171</v>
+      </c>
+      <c r="C41" t="s">
         <v>172</v>
       </c>
-      <c r="B41" t="s">
+      <c r="D41" t="s">
+        <v>14</v>
+      </c>
+      <c r="E41" t="s">
+        <v>32</v>
+      </c>
+      <c r="F41" t="s">
         <v>173</v>
-      </c>
-      <c r="C41" t="s">
-        <v>174</v>
-      </c>
-      <c r="D41" t="s">
-        <v>14</v>
-      </c>
-      <c r="E41" t="s">
-        <v>31</v>
-      </c>
-      <c r="F41" t="s">
-        <v>175</v>
       </c>
       <c r="H41" t="s">
         <v>109</v>
       </c>
       <c r="I41" t="s">
+        <v>28</v>
+      </c>
+      <c r="J41" t="s">
+        <v>162</v>
+      </c>
+      <c r="K41" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="42" hidden="1" spans="1:11">
+      <c r="A42" t="s">
+        <v>174</v>
+      </c>
+      <c r="B42" t="s">
+        <v>175</v>
+      </c>
+      <c r="C42" t="s">
+        <v>176</v>
+      </c>
+      <c r="D42" t="s">
+        <v>14</v>
+      </c>
+      <c r="E42" t="s">
+        <v>15</v>
+      </c>
+      <c r="F42" t="s">
+        <v>177</v>
+      </c>
+      <c r="H42" t="s">
         <v>27</v>
       </c>
-      <c r="J41" t="s">
-        <v>164</v>
-      </c>
-      <c r="K41" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11">
-      <c r="A42" t="s">
-        <v>176</v>
-      </c>
-      <c r="B42" t="s">
-        <v>177</v>
-      </c>
-      <c r="C42" t="s">
+      <c r="I42" t="s">
+        <v>28</v>
+      </c>
+      <c r="J42" t="s">
+        <v>162</v>
+      </c>
+      <c r="K42" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="43" hidden="1" spans="1:11">
+      <c r="A43" t="s">
         <v>178</v>
       </c>
-      <c r="D42" t="s">
-        <v>14</v>
-      </c>
-      <c r="E42" t="s">
-        <v>15</v>
-      </c>
-      <c r="F42" t="s">
+      <c r="B43" t="s">
         <v>179</v>
       </c>
-      <c r="H42" t="s">
-        <v>26</v>
-      </c>
-      <c r="I42" t="s">
-        <v>27</v>
-      </c>
-      <c r="J42" t="s">
-        <v>164</v>
-      </c>
-      <c r="K42" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11">
-      <c r="A43" t="s">
+      <c r="C43" t="s">
         <v>180</v>
       </c>
-      <c r="B43" t="s">
+      <c r="D43" t="s">
+        <v>14</v>
+      </c>
+      <c r="E43" t="s">
+        <v>32</v>
+      </c>
+      <c r="F43" t="s">
         <v>181</v>
-      </c>
-      <c r="C43" t="s">
-        <v>182</v>
-      </c>
-      <c r="D43" t="s">
-        <v>14</v>
-      </c>
-      <c r="E43" t="s">
-        <v>31</v>
-      </c>
-      <c r="F43" t="s">
-        <v>183</v>
       </c>
       <c r="H43" t="s">
         <v>109</v>
       </c>
       <c r="I43" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J43" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="K43" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="44" hidden="1" spans="1:11">
       <c r="A44" t="s">
+        <v>182</v>
+      </c>
+      <c r="B44" t="s">
+        <v>183</v>
+      </c>
+      <c r="C44" t="s">
         <v>184</v>
       </c>
-      <c r="B44" t="s">
+      <c r="D44" t="s">
+        <v>14</v>
+      </c>
+      <c r="E44" t="s">
+        <v>32</v>
+      </c>
+      <c r="F44" t="s">
         <v>185</v>
       </c>
-      <c r="C44" t="s">
-        <v>186</v>
-      </c>
-      <c r="D44" t="s">
-        <v>14</v>
-      </c>
-      <c r="E44" t="s">
-        <v>31</v>
-      </c>
-      <c r="F44" t="s">
-        <v>187</v>
-      </c>
       <c r="H44" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I44" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J44" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="K44" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="45" spans="1:11">
       <c r="A45" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B45" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C45" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D45" t="s">
         <v>24</v>
       </c>
+      <c r="E45" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="H45" t="s">
         <v>109</v>
       </c>
       <c r="I45" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J45" t="s">
+        <v>188</v>
+      </c>
+      <c r="K45" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11">
+      <c r="A46" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B46" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="K45" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11">
-      <c r="A46" t="s">
+      <c r="C46" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="B46" t="s">
+      <c r="D46" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F46" t="s">
         <v>192</v>
       </c>
-      <c r="C46" t="s">
+      <c r="G46" t="s">
         <v>193</v>
-      </c>
-      <c r="D46" t="s">
-        <v>24</v>
-      </c>
-      <c r="E46" t="s">
-        <v>129</v>
-      </c>
-      <c r="F46" t="s">
-        <v>194</v>
-      </c>
-      <c r="G46" t="s">
-        <v>195</v>
       </c>
       <c r="H46" t="s">
         <v>17</v>
@@ -4104,65 +4138,65 @@
         <v>18</v>
       </c>
       <c r="J46" t="s">
+        <v>194</v>
+      </c>
+      <c r="K46" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="47" hidden="1" spans="1:11">
+      <c r="A47" t="s">
         <v>196</v>
       </c>
-      <c r="K46" t="s">
+      <c r="B47" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="47" spans="1:11">
-      <c r="A47" t="s">
+      <c r="C47" t="s">
         <v>198</v>
       </c>
-      <c r="B47" t="s">
+      <c r="D47" t="s">
+        <v>14</v>
+      </c>
+      <c r="E47" t="s">
+        <v>15</v>
+      </c>
+      <c r="F47" t="s">
         <v>199</v>
       </c>
-      <c r="C47" t="s">
-        <v>200</v>
-      </c>
-      <c r="D47" t="s">
-        <v>14</v>
-      </c>
-      <c r="E47" t="s">
-        <v>15</v>
-      </c>
-      <c r="F47" t="s">
-        <v>201</v>
-      </c>
       <c r="H47" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I47" t="s">
         <v>18</v>
       </c>
       <c r="J47" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="K47" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="48" hidden="1" spans="1:11">
       <c r="A48" t="s">
+        <v>200</v>
+      </c>
+      <c r="B48" t="s">
+        <v>201</v>
+      </c>
+      <c r="C48" t="s">
         <v>202</v>
       </c>
-      <c r="B48" t="s">
+      <c r="D48" t="s">
+        <v>14</v>
+      </c>
+      <c r="E48" t="s">
+        <v>15</v>
+      </c>
+      <c r="F48" t="s">
         <v>203</v>
       </c>
-      <c r="C48" t="s">
+      <c r="G48" t="s">
         <v>204</v>
-      </c>
-      <c r="D48" t="s">
-        <v>14</v>
-      </c>
-      <c r="E48" t="s">
-        <v>15</v>
-      </c>
-      <c r="F48" t="s">
-        <v>205</v>
-      </c>
-      <c r="G48" t="s">
-        <v>206</v>
       </c>
       <c r="H48" t="s">
         <v>104</v>
@@ -4171,152 +4205,152 @@
         <v>18</v>
       </c>
       <c r="J48" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="K48" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="49" spans="1:11">
       <c r="A49" t="s">
+        <v>205</v>
+      </c>
+      <c r="B49" t="s">
+        <v>206</v>
+      </c>
+      <c r="C49" t="s">
         <v>207</v>
-      </c>
-      <c r="B49" t="s">
-        <v>208</v>
-      </c>
-      <c r="C49" t="s">
-        <v>209</v>
       </c>
       <c r="D49" t="s">
         <v>24</v>
       </c>
-      <c r="E49" t="s">
-        <v>97</v>
+      <c r="E49" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="F49" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G49" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="H49" t="s">
         <v>17</v>
       </c>
       <c r="I49" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J49" t="s">
+        <v>210</v>
+      </c>
+      <c r="K49" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="50" hidden="1" spans="1:11">
+      <c r="A50" t="s">
+        <v>211</v>
+      </c>
+      <c r="B50" t="s">
         <v>212</v>
       </c>
-      <c r="K49" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11">
-      <c r="A50" t="s">
+      <c r="C50" t="s">
         <v>213</v>
       </c>
-      <c r="B50" t="s">
+      <c r="D50" t="s">
+        <v>14</v>
+      </c>
+      <c r="E50" t="s">
+        <v>15</v>
+      </c>
+      <c r="F50" t="s">
         <v>214</v>
-      </c>
-      <c r="C50" t="s">
-        <v>215</v>
-      </c>
-      <c r="D50" t="s">
-        <v>14</v>
-      </c>
-      <c r="E50" t="s">
-        <v>15</v>
-      </c>
-      <c r="F50" t="s">
-        <v>216</v>
       </c>
       <c r="H50" t="s">
         <v>104</v>
       </c>
       <c r="I50" t="s">
+        <v>28</v>
+      </c>
+      <c r="J50" t="s">
+        <v>194</v>
+      </c>
+      <c r="K50" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="51" hidden="1" spans="1:11">
+      <c r="A51" t="s">
+        <v>215</v>
+      </c>
+      <c r="B51" t="s">
+        <v>216</v>
+      </c>
+      <c r="C51" t="s">
+        <v>217</v>
+      </c>
+      <c r="D51" t="s">
+        <v>14</v>
+      </c>
+      <c r="E51" t="s">
+        <v>15</v>
+      </c>
+      <c r="F51" t="s">
+        <v>218</v>
+      </c>
+      <c r="H51" t="s">
         <v>27</v>
       </c>
-      <c r="J50" t="s">
-        <v>196</v>
-      </c>
-      <c r="K50" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11">
-      <c r="A51" t="s">
-        <v>217</v>
-      </c>
-      <c r="B51" t="s">
-        <v>218</v>
-      </c>
-      <c r="C51" t="s">
+      <c r="I51" t="s">
+        <v>35</v>
+      </c>
+      <c r="J51" t="s">
+        <v>194</v>
+      </c>
+      <c r="K51" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="52" hidden="1" spans="1:11">
+      <c r="A52" t="s">
         <v>219</v>
       </c>
-      <c r="D51" t="s">
-        <v>14</v>
-      </c>
-      <c r="E51" t="s">
-        <v>15</v>
-      </c>
-      <c r="F51" t="s">
+      <c r="B52" t="s">
         <v>220</v>
       </c>
-      <c r="H51" t="s">
-        <v>26</v>
-      </c>
-      <c r="I51" t="s">
-        <v>34</v>
-      </c>
-      <c r="J51" t="s">
-        <v>196</v>
-      </c>
-      <c r="K51" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11">
-      <c r="A52" t="s">
+      <c r="C52" t="s">
         <v>221</v>
       </c>
-      <c r="B52" t="s">
+      <c r="D52" t="s">
+        <v>14</v>
+      </c>
+      <c r="E52" t="s">
+        <v>15</v>
+      </c>
+      <c r="F52" t="s">
         <v>222</v>
-      </c>
-      <c r="C52" t="s">
-        <v>223</v>
-      </c>
-      <c r="D52" t="s">
-        <v>14</v>
-      </c>
-      <c r="E52" t="s">
-        <v>15</v>
-      </c>
-      <c r="F52" t="s">
-        <v>224</v>
       </c>
       <c r="H52" t="s">
         <v>104</v>
       </c>
       <c r="I52" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J52" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="K52" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="53" hidden="1" spans="1:11">
       <c r="A53" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B53" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C53" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D53" t="s">
         <v>14</v>
@@ -4325,34 +4359,37 @@
         <v>15</v>
       </c>
       <c r="F53" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H53" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I53" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J53" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="K53" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="54" spans="1:11">
       <c r="A54" t="s">
+        <v>225</v>
+      </c>
+      <c r="B54" t="s">
+        <v>226</v>
+      </c>
+      <c r="C54" t="s">
         <v>227</v>
-      </c>
-      <c r="B54" t="s">
-        <v>228</v>
-      </c>
-      <c r="C54" t="s">
-        <v>229</v>
       </c>
       <c r="D54" t="s">
         <v>24</v>
       </c>
+      <c r="E54" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="H54" t="s">
         <v>109</v>
       </c>
@@ -4360,85 +4397,85 @@
         <v>18</v>
       </c>
       <c r="J54" t="s">
+        <v>228</v>
+      </c>
+      <c r="K54" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="55" hidden="1" spans="1:11">
+      <c r="A55" t="s">
         <v>230</v>
       </c>
-      <c r="K54" t="s">
+      <c r="B55" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="55" spans="1:11">
-      <c r="A55" t="s">
+      <c r="C55" t="s">
         <v>232</v>
       </c>
-      <c r="B55" t="s">
+      <c r="D55" t="s">
+        <v>14</v>
+      </c>
+      <c r="E55" t="s">
+        <v>15</v>
+      </c>
+      <c r="F55" t="s">
         <v>233</v>
       </c>
-      <c r="C55" t="s">
-        <v>234</v>
-      </c>
-      <c r="D55" t="s">
-        <v>14</v>
-      </c>
-      <c r="E55" t="s">
-        <v>15</v>
-      </c>
-      <c r="F55" t="s">
-        <v>235</v>
-      </c>
       <c r="H55" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I55" t="s">
         <v>18</v>
       </c>
       <c r="J55" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="K55" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="56" hidden="1" spans="1:11">
       <c r="A56" t="s">
+        <v>234</v>
+      </c>
+      <c r="B56" t="s">
+        <v>235</v>
+      </c>
+      <c r="C56" t="s">
         <v>236</v>
       </c>
-      <c r="B56" t="s">
+      <c r="D56" t="s">
+        <v>14</v>
+      </c>
+      <c r="E56" t="s">
+        <v>15</v>
+      </c>
+      <c r="F56" t="s">
         <v>237</v>
       </c>
-      <c r="C56" t="s">
-        <v>238</v>
-      </c>
-      <c r="D56" t="s">
-        <v>14</v>
-      </c>
-      <c r="E56" t="s">
-        <v>15</v>
-      </c>
-      <c r="F56" t="s">
-        <v>239</v>
-      </c>
       <c r="H56" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I56" t="s">
         <v>18</v>
       </c>
       <c r="J56" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="K56" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="57" hidden="1" spans="1:11">
       <c r="A57" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B57" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C57" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D57" t="s">
         <v>14</v>
@@ -4447,94 +4484,94 @@
         <v>15</v>
       </c>
       <c r="F57" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="H57" t="s">
         <v>109</v>
       </c>
       <c r="I57" t="s">
+        <v>28</v>
+      </c>
+      <c r="J57" t="s">
+        <v>228</v>
+      </c>
+      <c r="K57" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="58" hidden="1" spans="1:11">
+      <c r="A58" t="s">
+        <v>240</v>
+      </c>
+      <c r="B58" t="s">
+        <v>241</v>
+      </c>
+      <c r="C58" t="s">
+        <v>242</v>
+      </c>
+      <c r="D58" t="s">
+        <v>14</v>
+      </c>
+      <c r="E58" t="s">
+        <v>32</v>
+      </c>
+      <c r="F58" t="s">
+        <v>243</v>
+      </c>
+      <c r="H58" t="s">
         <v>27</v>
       </c>
-      <c r="J57" t="s">
-        <v>230</v>
-      </c>
-      <c r="K57" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11">
-      <c r="A58" t="s">
-        <v>242</v>
-      </c>
-      <c r="B58" t="s">
-        <v>243</v>
-      </c>
-      <c r="C58" t="s">
+      <c r="I58" t="s">
+        <v>28</v>
+      </c>
+      <c r="J58" t="s">
+        <v>228</v>
+      </c>
+      <c r="K58" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="59" hidden="1" spans="1:11">
+      <c r="A59" t="s">
         <v>244</v>
       </c>
-      <c r="D58" t="s">
-        <v>14</v>
-      </c>
-      <c r="E58" t="s">
-        <v>31</v>
-      </c>
-      <c r="F58" t="s">
+      <c r="B59" t="s">
         <v>245</v>
       </c>
-      <c r="H58" t="s">
-        <v>26</v>
-      </c>
-      <c r="I58" t="s">
-        <v>27</v>
-      </c>
-      <c r="J58" t="s">
-        <v>230</v>
-      </c>
-      <c r="K58" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11">
-      <c r="A59" t="s">
+      <c r="C59" t="s">
         <v>246</v>
       </c>
-      <c r="B59" t="s">
+      <c r="D59" t="s">
+        <v>14</v>
+      </c>
+      <c r="E59" t="s">
+        <v>15</v>
+      </c>
+      <c r="F59" t="s">
         <v>247</v>
-      </c>
-      <c r="C59" t="s">
-        <v>248</v>
-      </c>
-      <c r="D59" t="s">
-        <v>14</v>
-      </c>
-      <c r="E59" t="s">
-        <v>15</v>
-      </c>
-      <c r="F59" t="s">
-        <v>249</v>
       </c>
       <c r="H59" t="s">
         <v>109</v>
       </c>
       <c r="I59" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J59" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="K59" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="60" hidden="1" spans="1:11">
       <c r="A60" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B60" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C60" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D60" t="s">
         <v>14</v>
@@ -4543,53 +4580,56 @@
         <v>15</v>
       </c>
       <c r="F60" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H60" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I60" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J60" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="K60" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="61" spans="1:11">
       <c r="A61" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B61" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C61" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D61" t="s">
         <v>24</v>
       </c>
+      <c r="E61" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="H61" t="s">
         <v>109</v>
       </c>
       <c r="I61" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J61" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="K61" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="62" hidden="1" spans="1:11">
       <c r="A62" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B62" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C62" t="s">
         <v>102</v>
@@ -4598,193 +4638,202 @@
         <v>14</v>
       </c>
       <c r="E62" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F62" t="s">
         <v>103</v>
       </c>
       <c r="H62" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I62" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J62" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="K62" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="63" spans="1:11">
       <c r="A63" t="s">
+        <v>254</v>
+      </c>
+      <c r="B63" t="s">
+        <v>255</v>
+      </c>
+      <c r="C63" t="s">
         <v>256</v>
-      </c>
-      <c r="B63" t="s">
-        <v>257</v>
-      </c>
-      <c r="C63" t="s">
-        <v>258</v>
       </c>
       <c r="D63" t="s">
         <v>24</v>
       </c>
+      <c r="E63" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="F63" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="H63" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="I63" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J63" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="K63" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="64" spans="1:11">
       <c r="A64" t="s">
+        <v>259</v>
+      </c>
+      <c r="B64" t="s">
+        <v>260</v>
+      </c>
+      <c r="C64" t="s">
         <v>261</v>
-      </c>
-      <c r="B64" t="s">
-        <v>262</v>
-      </c>
-      <c r="C64" t="s">
-        <v>263</v>
       </c>
       <c r="D64" t="s">
         <v>24</v>
       </c>
+      <c r="E64" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="F64" t="s">
+        <v>262</v>
+      </c>
+      <c r="G64" t="s">
+        <v>263</v>
+      </c>
+      <c r="H64" t="s">
         <v>264</v>
-      </c>
-      <c r="G64" t="s">
-        <v>265</v>
-      </c>
-      <c r="H64" t="s">
-        <v>266</v>
       </c>
       <c r="I64" t="s">
         <v>18</v>
       </c>
       <c r="J64" t="s">
+        <v>265</v>
+      </c>
+      <c r="K64" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="65" hidden="1" spans="1:11">
+      <c r="A65" t="s">
+        <v>41</v>
+      </c>
+      <c r="B65" t="s">
         <v>267</v>
       </c>
-      <c r="K64" t="s">
+      <c r="C65" t="s">
         <v>268</v>
       </c>
-    </row>
-    <row r="65" spans="1:11">
-      <c r="A65" t="s">
-        <v>40</v>
-      </c>
-      <c r="B65" t="s">
+      <c r="D65" t="s">
+        <v>14</v>
+      </c>
+      <c r="E65" t="s">
+        <v>15</v>
+      </c>
+      <c r="F65" t="s">
         <v>269</v>
       </c>
-      <c r="C65" t="s">
+      <c r="G65" t="s">
         <v>270</v>
       </c>
-      <c r="D65" t="s">
-        <v>14</v>
-      </c>
-      <c r="E65" t="s">
-        <v>15</v>
-      </c>
-      <c r="F65" t="s">
+      <c r="H65" t="s">
         <v>271</v>
-      </c>
-      <c r="G65" t="s">
-        <v>272</v>
-      </c>
-      <c r="H65" t="s">
-        <v>273</v>
       </c>
       <c r="I65" t="s">
         <v>18</v>
       </c>
       <c r="J65" t="s">
+        <v>272</v>
+      </c>
+      <c r="K65" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="66" hidden="1" spans="1:11">
+      <c r="A66" t="s">
+        <v>273</v>
+      </c>
+      <c r="B66" t="s">
         <v>274</v>
       </c>
-      <c r="K65" t="s">
+      <c r="C66" t="s">
         <v>268</v>
       </c>
-    </row>
-    <row r="66" spans="1:11">
-      <c r="A66" t="s">
+      <c r="D66" t="s">
+        <v>14</v>
+      </c>
+      <c r="E66" t="s">
+        <v>15</v>
+      </c>
+      <c r="F66" t="s">
+        <v>269</v>
+      </c>
+      <c r="G66" t="s">
+        <v>270</v>
+      </c>
+      <c r="H66" t="s">
         <v>275</v>
-      </c>
-      <c r="B66" t="s">
-        <v>276</v>
-      </c>
-      <c r="C66" t="s">
-        <v>270</v>
-      </c>
-      <c r="D66" t="s">
-        <v>14</v>
-      </c>
-      <c r="E66" t="s">
-        <v>15</v>
-      </c>
-      <c r="F66" t="s">
-        <v>271</v>
-      </c>
-      <c r="G66" t="s">
-        <v>272</v>
-      </c>
-      <c r="H66" t="s">
-        <v>277</v>
       </c>
       <c r="I66" t="s">
         <v>18</v>
       </c>
       <c r="J66" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="K66" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="67" spans="1:11">
       <c r="A67" t="s">
+        <v>259</v>
+      </c>
+      <c r="B67" t="s">
+        <v>260</v>
+      </c>
+      <c r="C67" t="s">
         <v>261</v>
-      </c>
-      <c r="B67" t="s">
-        <v>262</v>
-      </c>
-      <c r="C67" t="s">
-        <v>263</v>
       </c>
       <c r="D67" t="s">
         <v>24</v>
       </c>
+      <c r="E67" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="F67" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="G67" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H67" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="I67" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J67" t="s">
+        <v>276</v>
+      </c>
+      <c r="K67" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="68" hidden="1" spans="1:11">
+      <c r="A68" t="s">
+        <v>277</v>
+      </c>
+      <c r="B68" t="s">
         <v>278</v>
-      </c>
-      <c r="K67" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11">
-      <c r="A68" t="s">
-        <v>279</v>
-      </c>
-      <c r="B68" t="s">
-        <v>280</v>
       </c>
       <c r="C68" t="s">
         <v>119</v>
@@ -4799,59 +4848,59 @@
         <v>120</v>
       </c>
       <c r="H68" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="I68" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J68" t="s">
+        <v>279</v>
+      </c>
+      <c r="K68" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="69" hidden="1" spans="1:11">
+      <c r="A69" t="s">
+        <v>280</v>
+      </c>
+      <c r="B69" t="s">
         <v>281</v>
       </c>
-      <c r="K68" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11">
-      <c r="A69" t="s">
+      <c r="C69" t="s">
         <v>282</v>
       </c>
-      <c r="B69" t="s">
+      <c r="D69" t="s">
+        <v>14</v>
+      </c>
+      <c r="E69" t="s">
+        <v>32</v>
+      </c>
+      <c r="F69" t="s">
         <v>283</v>
       </c>
-      <c r="C69" t="s">
+      <c r="G69" t="s">
         <v>284</v>
       </c>
-      <c r="D69" t="s">
-        <v>14</v>
-      </c>
-      <c r="E69" t="s">
-        <v>31</v>
-      </c>
-      <c r="F69" t="s">
-        <v>285</v>
-      </c>
-      <c r="G69" t="s">
-        <v>286</v>
-      </c>
       <c r="H69" t="s">
+        <v>275</v>
+      </c>
+      <c r="I69" t="s">
+        <v>55</v>
+      </c>
+      <c r="J69" t="s">
+        <v>279</v>
+      </c>
+      <c r="K69" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="70" hidden="1" spans="1:11">
+      <c r="A70" t="s">
         <v>277</v>
       </c>
-      <c r="I69" t="s">
-        <v>54</v>
-      </c>
-      <c r="J69" t="s">
-        <v>281</v>
-      </c>
-      <c r="K69" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11">
-      <c r="A70" t="s">
-        <v>279</v>
-      </c>
       <c r="B70" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C70" t="s">
         <v>119</v>
@@ -4866,272 +4915,272 @@
         <v>120</v>
       </c>
       <c r="H70" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="I70" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J70" t="s">
+        <v>285</v>
+      </c>
+      <c r="K70" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="71" hidden="1" spans="1:11">
+      <c r="A71" t="s">
+        <v>286</v>
+      </c>
+      <c r="B71" t="s">
         <v>287</v>
       </c>
-      <c r="K70" t="s">
+      <c r="C71" t="s">
+        <v>288</v>
+      </c>
+      <c r="D71" t="s">
+        <v>14</v>
+      </c>
+      <c r="E71" t="s">
+        <v>289</v>
+      </c>
+      <c r="F71" t="s">
+        <v>290</v>
+      </c>
+      <c r="G71" t="s">
+        <v>291</v>
+      </c>
+      <c r="H71" t="s">
+        <v>271</v>
+      </c>
+      <c r="I71" t="s">
+        <v>35</v>
+      </c>
+      <c r="J71" t="s">
+        <v>272</v>
+      </c>
+      <c r="K71" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="72" hidden="1" spans="1:11">
+      <c r="A72" t="s">
+        <v>41</v>
+      </c>
+      <c r="B72" t="s">
+        <v>267</v>
+      </c>
+      <c r="C72" t="s">
         <v>268</v>
       </c>
-    </row>
-    <row r="71" spans="1:11">
-      <c r="A71" t="s">
+      <c r="D72" t="s">
+        <v>14</v>
+      </c>
+      <c r="E72" t="s">
+        <v>15</v>
+      </c>
+      <c r="F72" t="s">
+        <v>269</v>
+      </c>
+      <c r="G72" t="s">
+        <v>270</v>
+      </c>
+      <c r="H72" t="s">
+        <v>271</v>
+      </c>
+      <c r="I72" t="s">
+        <v>35</v>
+      </c>
+      <c r="J72" t="s">
+        <v>292</v>
+      </c>
+      <c r="K72" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="73" hidden="1" spans="1:11">
+      <c r="A73" t="s">
+        <v>273</v>
+      </c>
+      <c r="B73" t="s">
+        <v>274</v>
+      </c>
+      <c r="C73" t="s">
+        <v>268</v>
+      </c>
+      <c r="D73" t="s">
+        <v>14</v>
+      </c>
+      <c r="E73" t="s">
+        <v>15</v>
+      </c>
+      <c r="F73" t="s">
+        <v>269</v>
+      </c>
+      <c r="G73" t="s">
+        <v>270</v>
+      </c>
+      <c r="H73" t="s">
+        <v>275</v>
+      </c>
+      <c r="I73" t="s">
+        <v>35</v>
+      </c>
+      <c r="J73" t="s">
+        <v>292</v>
+      </c>
+      <c r="K73" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="74" hidden="1" spans="1:11">
+      <c r="A74" t="s">
+        <v>280</v>
+      </c>
+      <c r="B74" t="s">
+        <v>281</v>
+      </c>
+      <c r="C74" t="s">
+        <v>282</v>
+      </c>
+      <c r="D74" t="s">
+        <v>14</v>
+      </c>
+      <c r="E74" t="s">
+        <v>32</v>
+      </c>
+      <c r="F74" t="s">
+        <v>283</v>
+      </c>
+      <c r="G74" t="s">
+        <v>284</v>
+      </c>
+      <c r="H74" t="s">
+        <v>275</v>
+      </c>
+      <c r="I74" t="s">
+        <v>35</v>
+      </c>
+      <c r="J74" t="s">
+        <v>272</v>
+      </c>
+      <c r="K74" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="75" hidden="1" spans="1:11">
+      <c r="A75" t="s">
+        <v>286</v>
+      </c>
+      <c r="B75" t="s">
+        <v>287</v>
+      </c>
+      <c r="C75" t="s">
         <v>288</v>
       </c>
-      <c r="B71" t="s">
+      <c r="D75" t="s">
+        <v>14</v>
+      </c>
+      <c r="E75" t="s">
         <v>289</v>
       </c>
-      <c r="C71" t="s">
+      <c r="F75" t="s">
         <v>290</v>
       </c>
-      <c r="D71" t="s">
-        <v>14</v>
-      </c>
-      <c r="E71" t="s">
+      <c r="G75" t="s">
         <v>291</v>
       </c>
-      <c r="F71" t="s">
-        <v>292</v>
-      </c>
-      <c r="G71" t="s">
+      <c r="H75" t="s">
+        <v>264</v>
+      </c>
+      <c r="I75" t="s">
+        <v>40</v>
+      </c>
+      <c r="J75" t="s">
+        <v>276</v>
+      </c>
+      <c r="K75" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="76" hidden="1" spans="1:11">
+      <c r="A76" t="s">
         <v>293</v>
       </c>
-      <c r="H71" t="s">
-        <v>273</v>
-      </c>
-      <c r="I71" t="s">
+      <c r="B76" t="s">
+        <v>294</v>
+      </c>
+      <c r="C76" t="s">
+        <v>295</v>
+      </c>
+      <c r="D76" t="s">
+        <v>14</v>
+      </c>
+      <c r="H76" t="s">
+        <v>296</v>
+      </c>
+      <c r="I76" t="s">
+        <v>40</v>
+      </c>
+      <c r="J76" t="s">
+        <v>297</v>
+      </c>
+      <c r="K76" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="77" hidden="1" spans="1:11">
+      <c r="A77" t="s">
+        <v>46</v>
+      </c>
+      <c r="B77" t="s">
+        <v>298</v>
+      </c>
+      <c r="C77" t="s">
+        <v>31</v>
+      </c>
+      <c r="D77" t="s">
+        <v>14</v>
+      </c>
+      <c r="E77" t="s">
+        <v>32</v>
+      </c>
+      <c r="F77" t="s">
+        <v>33</v>
+      </c>
+      <c r="G77" t="s">
         <v>34</v>
       </c>
-      <c r="J71" t="s">
-        <v>274</v>
-      </c>
-      <c r="K71" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11">
-      <c r="A72" t="s">
-        <v>40</v>
-      </c>
-      <c r="B72" t="s">
-        <v>269</v>
-      </c>
-      <c r="C72" t="s">
-        <v>270</v>
-      </c>
-      <c r="D72" t="s">
-        <v>14</v>
-      </c>
-      <c r="E72" t="s">
-        <v>15</v>
-      </c>
-      <c r="F72" t="s">
-        <v>271</v>
-      </c>
-      <c r="G72" t="s">
-        <v>272</v>
-      </c>
-      <c r="H72" t="s">
-        <v>273</v>
-      </c>
-      <c r="I72" t="s">
-        <v>34</v>
-      </c>
-      <c r="J72" t="s">
-        <v>294</v>
-      </c>
-      <c r="K72" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11">
-      <c r="A73" t="s">
-        <v>275</v>
-      </c>
-      <c r="B73" t="s">
-        <v>276</v>
-      </c>
-      <c r="C73" t="s">
-        <v>270</v>
-      </c>
-      <c r="D73" t="s">
-        <v>14</v>
-      </c>
-      <c r="E73" t="s">
-        <v>15</v>
-      </c>
-      <c r="F73" t="s">
-        <v>271</v>
-      </c>
-      <c r="G73" t="s">
-        <v>272</v>
-      </c>
-      <c r="H73" t="s">
-        <v>277</v>
-      </c>
-      <c r="I73" t="s">
-        <v>34</v>
-      </c>
-      <c r="J73" t="s">
-        <v>294</v>
-      </c>
-      <c r="K73" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11">
-      <c r="A74" t="s">
-        <v>282</v>
-      </c>
-      <c r="B74" t="s">
-        <v>283</v>
-      </c>
-      <c r="C74" t="s">
-        <v>284</v>
-      </c>
-      <c r="D74" t="s">
-        <v>14</v>
-      </c>
-      <c r="E74" t="s">
-        <v>31</v>
-      </c>
-      <c r="F74" t="s">
-        <v>285</v>
-      </c>
-      <c r="G74" t="s">
-        <v>286</v>
-      </c>
-      <c r="H74" t="s">
-        <v>277</v>
-      </c>
-      <c r="I74" t="s">
-        <v>34</v>
-      </c>
-      <c r="J74" t="s">
-        <v>274</v>
-      </c>
-      <c r="K74" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11">
-      <c r="A75" t="s">
-        <v>288</v>
-      </c>
-      <c r="B75" t="s">
-        <v>289</v>
-      </c>
-      <c r="C75" t="s">
-        <v>290</v>
-      </c>
-      <c r="D75" t="s">
-        <v>14</v>
-      </c>
-      <c r="E75" t="s">
-        <v>291</v>
-      </c>
-      <c r="F75" t="s">
-        <v>292</v>
-      </c>
-      <c r="G75" t="s">
-        <v>293</v>
-      </c>
-      <c r="H75" t="s">
-        <v>266</v>
-      </c>
-      <c r="I75" t="s">
-        <v>39</v>
-      </c>
-      <c r="J75" t="s">
-        <v>278</v>
-      </c>
-      <c r="K75" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11">
-      <c r="A76" t="s">
-        <v>295</v>
-      </c>
-      <c r="B76" t="s">
-        <v>296</v>
-      </c>
-      <c r="C76" t="s">
-        <v>297</v>
-      </c>
-      <c r="D76" t="s">
-        <v>14</v>
-      </c>
-      <c r="H76" t="s">
-        <v>298</v>
-      </c>
-      <c r="I76" t="s">
-        <v>39</v>
-      </c>
-      <c r="J76" t="s">
-        <v>299</v>
-      </c>
-      <c r="K76" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11">
-      <c r="A77" t="s">
-        <v>45</v>
-      </c>
-      <c r="B77" t="s">
-        <v>300</v>
-      </c>
-      <c r="C77" t="s">
-        <v>30</v>
-      </c>
-      <c r="D77" t="s">
-        <v>14</v>
-      </c>
-      <c r="E77" t="s">
-        <v>31</v>
-      </c>
-      <c r="F77" t="s">
-        <v>32</v>
-      </c>
-      <c r="G77" t="s">
-        <v>33</v>
-      </c>
       <c r="H77" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I77" t="s">
         <v>18</v>
       </c>
       <c r="J77" t="s">
+        <v>299</v>
+      </c>
+      <c r="K77" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="78" hidden="1" spans="1:11">
+      <c r="A78" t="s">
         <v>301</v>
       </c>
-      <c r="K77" t="s">
+      <c r="B78" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="78" spans="1:11">
-      <c r="A78" t="s">
+      <c r="C78" t="s">
         <v>303</v>
       </c>
-      <c r="B78" t="s">
+      <c r="D78" t="s">
+        <v>14</v>
+      </c>
+      <c r="E78" t="s">
+        <v>15</v>
+      </c>
+      <c r="F78" t="s">
         <v>304</v>
-      </c>
-      <c r="C78" t="s">
-        <v>305</v>
-      </c>
-      <c r="D78" t="s">
-        <v>14</v>
-      </c>
-      <c r="E78" t="s">
-        <v>15</v>
-      </c>
-      <c r="F78" t="s">
-        <v>306</v>
       </c>
       <c r="H78" t="s">
         <v>104</v>
@@ -5140,216 +5189,225 @@
         <v>18</v>
       </c>
       <c r="J78" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="K78" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="79" spans="1:11">
       <c r="A79" t="s">
+        <v>305</v>
+      </c>
+      <c r="B79" t="s">
+        <v>306</v>
+      </c>
+      <c r="C79" t="s">
         <v>307</v>
-      </c>
-      <c r="B79" t="s">
-        <v>308</v>
-      </c>
-      <c r="C79" t="s">
-        <v>309</v>
       </c>
       <c r="D79" t="s">
         <v>24</v>
       </c>
+      <c r="E79" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="F79" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H79" t="s">
         <v>109</v>
       </c>
       <c r="I79" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J79" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="K79" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="80" spans="1:11">
       <c r="A80" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B80" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C80" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D80" t="s">
         <v>24</v>
       </c>
+      <c r="E80" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="H80" t="s">
         <v>17</v>
       </c>
       <c r="I80" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J80" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="K80" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="81" spans="1:11">
       <c r="A81" t="s">
+        <v>312</v>
+      </c>
+      <c r="B81" t="s">
+        <v>313</v>
+      </c>
+      <c r="C81" t="s">
         <v>314</v>
-      </c>
-      <c r="B81" t="s">
-        <v>315</v>
-      </c>
-      <c r="C81" t="s">
-        <v>316</v>
       </c>
       <c r="D81" t="s">
         <v>24</v>
       </c>
+      <c r="E81" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="F81" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="G81" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="H81" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I81" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J81" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="K81" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="82" spans="1:11">
       <c r="A82" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B82" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C82" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D82" t="s">
         <v>24</v>
       </c>
-      <c r="E82" t="s">
-        <v>97</v>
+      <c r="E82" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="F82" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="G82" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="H82" t="s">
         <v>109</v>
       </c>
       <c r="I82" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J82" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="K82" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="83" hidden="1" spans="1:11">
       <c r="A83" t="s">
+        <v>321</v>
+      </c>
+      <c r="B83" t="s">
+        <v>322</v>
+      </c>
+      <c r="C83" t="s">
         <v>323</v>
       </c>
-      <c r="B83" t="s">
+      <c r="D83" t="s">
+        <v>14</v>
+      </c>
+      <c r="E83" t="s">
+        <v>15</v>
+      </c>
+      <c r="F83" t="s">
         <v>324</v>
       </c>
-      <c r="C83" t="s">
+      <c r="H83" t="s">
+        <v>27</v>
+      </c>
+      <c r="I83" t="s">
+        <v>40</v>
+      </c>
+      <c r="J83" t="s">
+        <v>309</v>
+      </c>
+      <c r="K83" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="84" hidden="1" spans="1:11">
+      <c r="A84" t="s">
         <v>325</v>
       </c>
-      <c r="D83" t="s">
-        <v>14</v>
-      </c>
-      <c r="E83" t="s">
-        <v>15</v>
-      </c>
-      <c r="F83" t="s">
+      <c r="B84" t="s">
         <v>326</v>
       </c>
-      <c r="H83" t="s">
-        <v>26</v>
-      </c>
-      <c r="I83" t="s">
-        <v>39</v>
-      </c>
-      <c r="J83" t="s">
-        <v>311</v>
-      </c>
-      <c r="K83" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="84" spans="1:11">
-      <c r="A84" t="s">
-        <v>327</v>
-      </c>
-      <c r="B84" t="s">
-        <v>328</v>
-      </c>
       <c r="C84" t="s">
+        <v>142</v>
+      </c>
+      <c r="D84" t="s">
+        <v>14</v>
+      </c>
+      <c r="E84" t="s">
+        <v>15</v>
+      </c>
+      <c r="F84" t="s">
         <v>143</v>
       </c>
-      <c r="D84" t="s">
-        <v>14</v>
-      </c>
-      <c r="E84" t="s">
-        <v>15</v>
-      </c>
-      <c r="F84" t="s">
-        <v>144</v>
-      </c>
       <c r="H84" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I84" t="s">
         <v>18</v>
       </c>
       <c r="J84" t="s">
+        <v>327</v>
+      </c>
+      <c r="K84" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="85" hidden="1" spans="1:11">
+      <c r="A85" t="s">
         <v>329</v>
       </c>
-      <c r="K84" t="s">
+      <c r="B85" t="s">
         <v>330</v>
       </c>
-    </row>
-    <row r="85" spans="1:11">
-      <c r="A85" t="s">
+      <c r="C85" t="s">
         <v>331</v>
       </c>
-      <c r="B85" t="s">
+      <c r="D85" t="s">
+        <v>14</v>
+      </c>
+      <c r="E85" t="s">
+        <v>15</v>
+      </c>
+      <c r="F85" t="s">
         <v>332</v>
-      </c>
-      <c r="C85" t="s">
-        <v>333</v>
-      </c>
-      <c r="D85" t="s">
-        <v>14</v>
-      </c>
-      <c r="E85" t="s">
-        <v>15</v>
-      </c>
-      <c r="F85" t="s">
-        <v>334</v>
       </c>
       <c r="H85" t="s">
         <v>104</v>
@@ -5358,146 +5416,146 @@
         <v>18</v>
       </c>
       <c r="J85" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="K85" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="86" hidden="1" spans="1:11">
       <c r="A86" t="s">
+        <v>333</v>
+      </c>
+      <c r="B86" t="s">
+        <v>334</v>
+      </c>
+      <c r="C86" t="s">
         <v>335</v>
       </c>
-      <c r="B86" t="s">
+      <c r="D86" t="s">
+        <v>14</v>
+      </c>
+      <c r="E86" t="s">
+        <v>15</v>
+      </c>
+      <c r="F86" t="s">
         <v>336</v>
       </c>
-      <c r="C86" t="s">
+      <c r="H86" t="s">
+        <v>27</v>
+      </c>
+      <c r="I86" t="s">
+        <v>55</v>
+      </c>
+      <c r="J86" t="s">
+        <v>328</v>
+      </c>
+      <c r="K86" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="87" hidden="1" spans="1:11">
+      <c r="A87" t="s">
+        <v>325</v>
+      </c>
+      <c r="B87" t="s">
         <v>337</v>
       </c>
-      <c r="D86" t="s">
-        <v>14</v>
-      </c>
-      <c r="E86" t="s">
-        <v>15</v>
-      </c>
-      <c r="F86" t="s">
+      <c r="C87" t="s">
+        <v>142</v>
+      </c>
+      <c r="D87" t="s">
+        <v>14</v>
+      </c>
+      <c r="E87" t="s">
+        <v>15</v>
+      </c>
+      <c r="F87" t="s">
+        <v>143</v>
+      </c>
+      <c r="H87" t="s">
+        <v>27</v>
+      </c>
+      <c r="I87" t="s">
+        <v>28</v>
+      </c>
+      <c r="J87" t="s">
+        <v>327</v>
+      </c>
+      <c r="K87" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="88" hidden="1" spans="1:11">
+      <c r="A88" t="s">
         <v>338</v>
       </c>
-      <c r="H86" t="s">
-        <v>26</v>
-      </c>
-      <c r="I86" t="s">
-        <v>54</v>
-      </c>
-      <c r="J86" t="s">
-        <v>330</v>
-      </c>
-      <c r="K86" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="87" spans="1:11">
-      <c r="A87" t="s">
-        <v>327</v>
-      </c>
-      <c r="B87" t="s">
+      <c r="B88" t="s">
         <v>339</v>
       </c>
-      <c r="C87" t="s">
-        <v>143</v>
-      </c>
-      <c r="D87" t="s">
-        <v>14</v>
-      </c>
-      <c r="E87" t="s">
-        <v>15</v>
-      </c>
-      <c r="F87" t="s">
-        <v>144</v>
-      </c>
-      <c r="H87" t="s">
-        <v>26</v>
-      </c>
-      <c r="I87" t="s">
-        <v>27</v>
-      </c>
-      <c r="J87" t="s">
-        <v>329</v>
-      </c>
-      <c r="K87" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11">
-      <c r="A88" t="s">
+      <c r="C88" t="s">
         <v>340</v>
       </c>
-      <c r="B88" t="s">
+      <c r="D88" t="s">
+        <v>14</v>
+      </c>
+      <c r="E88" t="s">
+        <v>15</v>
+      </c>
+      <c r="F88" t="s">
         <v>341</v>
-      </c>
-      <c r="C88" t="s">
-        <v>342</v>
-      </c>
-      <c r="D88" t="s">
-        <v>14</v>
-      </c>
-      <c r="E88" t="s">
-        <v>15</v>
-      </c>
-      <c r="F88" t="s">
-        <v>343</v>
       </c>
       <c r="H88" t="s">
         <v>109</v>
       </c>
       <c r="I88" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J88" t="s">
+        <v>342</v>
+      </c>
+      <c r="K88" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="89" hidden="1" spans="1:11">
+      <c r="A89" t="s">
+        <v>343</v>
+      </c>
+      <c r="B89" t="s">
         <v>344</v>
       </c>
-      <c r="K88" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="89" spans="1:11">
-      <c r="A89" t="s">
+      <c r="C89" t="s">
+        <v>142</v>
+      </c>
+      <c r="D89" t="s">
+        <v>14</v>
+      </c>
+      <c r="E89" t="s">
+        <v>15</v>
+      </c>
+      <c r="F89" t="s">
+        <v>143</v>
+      </c>
+      <c r="H89" t="s">
+        <v>27</v>
+      </c>
+      <c r="I89" t="s">
+        <v>35</v>
+      </c>
+      <c r="J89" t="s">
+        <v>342</v>
+      </c>
+      <c r="K89" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="90" hidden="1" spans="1:11">
+      <c r="A90" t="s">
         <v>345</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B90" t="s">
         <v>346</v>
-      </c>
-      <c r="C89" t="s">
-        <v>143</v>
-      </c>
-      <c r="D89" t="s">
-        <v>14</v>
-      </c>
-      <c r="E89" t="s">
-        <v>15</v>
-      </c>
-      <c r="F89" t="s">
-        <v>144</v>
-      </c>
-      <c r="H89" t="s">
-        <v>26</v>
-      </c>
-      <c r="I89" t="s">
-        <v>34</v>
-      </c>
-      <c r="J89" t="s">
-        <v>344</v>
-      </c>
-      <c r="K89" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="90" spans="1:11">
-      <c r="A90" t="s">
-        <v>347</v>
-      </c>
-      <c r="B90" t="s">
-        <v>348</v>
       </c>
       <c r="C90" t="s">
         <v>107</v>
@@ -5515,24 +5573,24 @@
         <v>104</v>
       </c>
       <c r="I90" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J90" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="K90" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="91" spans="1:11">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="91" hidden="1" spans="1:11">
       <c r="A91" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B91" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C91" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D91" t="s">
         <v>14</v>
@@ -5541,62 +5599,62 @@
         <v>15</v>
       </c>
       <c r="F91" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="H91" t="s">
         <v>109</v>
       </c>
       <c r="I91" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J91" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="K91" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="92" hidden="1" spans="1:11">
       <c r="A92" t="s">
         <v>100</v>
       </c>
       <c r="B92" t="s">
+        <v>349</v>
+      </c>
+      <c r="C92" t="s">
+        <v>350</v>
+      </c>
+      <c r="D92" t="s">
+        <v>14</v>
+      </c>
+      <c r="E92" t="s">
+        <v>15</v>
+      </c>
+      <c r="F92" t="s">
         <v>351</v>
       </c>
-      <c r="C92" t="s">
+      <c r="H92" t="s">
+        <v>27</v>
+      </c>
+      <c r="I92" t="s">
+        <v>40</v>
+      </c>
+      <c r="J92" t="s">
+        <v>327</v>
+      </c>
+      <c r="K92" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="93" hidden="1" spans="1:11">
+      <c r="A93" t="s">
         <v>352</v>
       </c>
-      <c r="D92" t="s">
-        <v>14</v>
-      </c>
-      <c r="E92" t="s">
-        <v>15</v>
-      </c>
-      <c r="F92" t="s">
+      <c r="B93" t="s">
         <v>353</v>
       </c>
-      <c r="H92" t="s">
-        <v>26</v>
-      </c>
-      <c r="I92" t="s">
-        <v>39</v>
-      </c>
-      <c r="J92" t="s">
-        <v>329</v>
-      </c>
-      <c r="K92" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="93" spans="1:11">
-      <c r="A93" t="s">
-        <v>354</v>
-      </c>
-      <c r="B93" t="s">
-        <v>355</v>
-      </c>
       <c r="C93" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D93" t="s">
         <v>14</v>
@@ -5605,7 +5663,7 @@
         <v>15</v>
       </c>
       <c r="F93" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="H93" t="s">
         <v>17</v>
@@ -5614,30 +5672,30 @@
         <v>18</v>
       </c>
       <c r="J93" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="K93" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="94" spans="1:11">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="94" hidden="1" spans="1:11">
       <c r="A94" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B94" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C94" t="s">
+        <v>159</v>
+      </c>
+      <c r="D94" t="s">
+        <v>14</v>
+      </c>
+      <c r="E94" t="s">
+        <v>160</v>
+      </c>
+      <c r="F94" t="s">
         <v>161</v>
-      </c>
-      <c r="D94" t="s">
-        <v>14</v>
-      </c>
-      <c r="E94" t="s">
-        <v>162</v>
-      </c>
-      <c r="F94" t="s">
-        <v>163</v>
       </c>
       <c r="H94" t="s">
         <v>104</v>
@@ -5646,85 +5704,85 @@
         <v>18</v>
       </c>
       <c r="J94" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="K94" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="95" hidden="1" spans="1:11">
+      <c r="A95" t="s">
         <v>356</v>
       </c>
-    </row>
-    <row r="95" spans="1:11">
-      <c r="A95" t="s">
+      <c r="B95" t="s">
+        <v>357</v>
+      </c>
+      <c r="C95" t="s">
+        <v>180</v>
+      </c>
+      <c r="D95" t="s">
+        <v>14</v>
+      </c>
+      <c r="E95" t="s">
+        <v>32</v>
+      </c>
+      <c r="F95" t="s">
+        <v>181</v>
+      </c>
+      <c r="H95" t="s">
+        <v>27</v>
+      </c>
+      <c r="I95" t="s">
+        <v>55</v>
+      </c>
+      <c r="J95" t="s">
         <v>358</v>
       </c>
-      <c r="B95" t="s">
+      <c r="K95" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="96" hidden="1" spans="1:11">
+      <c r="A96" t="s">
+        <v>170</v>
+      </c>
+      <c r="B96" t="s">
         <v>359</v>
       </c>
-      <c r="C95" t="s">
-        <v>182</v>
-      </c>
-      <c r="D95" t="s">
-        <v>14</v>
-      </c>
-      <c r="E95" t="s">
-        <v>31</v>
-      </c>
-      <c r="F95" t="s">
-        <v>183</v>
-      </c>
-      <c r="H95" t="s">
-        <v>26</v>
-      </c>
-      <c r="I95" t="s">
-        <v>54</v>
-      </c>
-      <c r="J95" t="s">
+      <c r="C96" t="s">
+        <v>172</v>
+      </c>
+      <c r="D96" t="s">
+        <v>14</v>
+      </c>
+      <c r="E96" t="s">
+        <v>32</v>
+      </c>
+      <c r="F96" t="s">
+        <v>173</v>
+      </c>
+      <c r="H96" t="s">
+        <v>27</v>
+      </c>
+      <c r="I96" t="s">
+        <v>28</v>
+      </c>
+      <c r="J96" t="s">
+        <v>162</v>
+      </c>
+      <c r="K96" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="97" hidden="1" spans="1:11">
+      <c r="A97" t="s">
         <v>360</v>
       </c>
-      <c r="K95" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="96" spans="1:11">
-      <c r="A96" t="s">
-        <v>172</v>
-      </c>
-      <c r="B96" t="s">
+      <c r="B97" t="s">
         <v>361</v>
       </c>
-      <c r="C96" t="s">
-        <v>174</v>
-      </c>
-      <c r="D96" t="s">
-        <v>14</v>
-      </c>
-      <c r="E96" t="s">
-        <v>31</v>
-      </c>
-      <c r="F96" t="s">
-        <v>175</v>
-      </c>
-      <c r="H96" t="s">
-        <v>26</v>
-      </c>
-      <c r="I96" t="s">
-        <v>27</v>
-      </c>
-      <c r="J96" t="s">
-        <v>164</v>
-      </c>
-      <c r="K96" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="97" spans="1:11">
-      <c r="A97" t="s">
-        <v>362</v>
-      </c>
-      <c r="B97" t="s">
-        <v>363</v>
-      </c>
       <c r="C97" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D97" t="s">
         <v>14</v>
@@ -5733,62 +5791,62 @@
         <v>15</v>
       </c>
       <c r="F97" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="H97" t="s">
         <v>109</v>
       </c>
       <c r="I97" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J97" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="K97" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="98" spans="1:11">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="98" hidden="1" spans="1:11">
       <c r="A98" t="s">
+        <v>362</v>
+      </c>
+      <c r="B98" t="s">
+        <v>363</v>
+      </c>
+      <c r="C98" t="s">
+        <v>202</v>
+      </c>
+      <c r="D98" t="s">
+        <v>14</v>
+      </c>
+      <c r="E98" t="s">
+        <v>15</v>
+      </c>
+      <c r="F98" t="s">
+        <v>203</v>
+      </c>
+      <c r="G98" t="s">
+        <v>204</v>
+      </c>
+      <c r="H98" t="s">
+        <v>27</v>
+      </c>
+      <c r="I98" t="s">
+        <v>35</v>
+      </c>
+      <c r="J98" t="s">
+        <v>358</v>
+      </c>
+      <c r="K98" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="99" hidden="1" spans="1:11">
+      <c r="A99" t="s">
         <v>364</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B99" t="s">
         <v>365</v>
-      </c>
-      <c r="C98" t="s">
-        <v>204</v>
-      </c>
-      <c r="D98" t="s">
-        <v>14</v>
-      </c>
-      <c r="E98" t="s">
-        <v>15</v>
-      </c>
-      <c r="F98" t="s">
-        <v>205</v>
-      </c>
-      <c r="G98" t="s">
-        <v>206</v>
-      </c>
-      <c r="H98" t="s">
-        <v>26</v>
-      </c>
-      <c r="I98" t="s">
-        <v>34</v>
-      </c>
-      <c r="J98" t="s">
-        <v>360</v>
-      </c>
-      <c r="K98" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="99" spans="1:11">
-      <c r="A99" t="s">
-        <v>366</v>
-      </c>
-      <c r="B99" t="s">
-        <v>367</v>
       </c>
       <c r="C99" t="s">
         <v>13</v>
@@ -5803,36 +5861,36 @@
         <v>16</v>
       </c>
       <c r="H99" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I99" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J99" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="K99" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="100" hidden="1" spans="1:11">
+      <c r="A100" t="s">
         <v>356</v>
       </c>
-    </row>
-    <row r="100" spans="1:11">
-      <c r="A100" t="s">
-        <v>358</v>
-      </c>
       <c r="B100" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C100" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D100" t="s">
         <v>14</v>
       </c>
       <c r="E100" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F100" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H100" t="s">
         <v>109</v>
@@ -5841,21 +5899,21 @@
         <v>18</v>
       </c>
       <c r="J100" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="K100" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="101" spans="1:11">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="101" hidden="1" spans="1:11">
       <c r="A101" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B101" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C101" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D101" t="s">
         <v>14</v>
@@ -5864,7 +5922,7 @@
         <v>15</v>
       </c>
       <c r="F101" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="H101" t="s">
         <v>17</v>
@@ -5873,30 +5931,30 @@
         <v>18</v>
       </c>
       <c r="J101" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="K101" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="102" hidden="1" spans="1:11">
+      <c r="A102" t="s">
+        <v>196</v>
+      </c>
+      <c r="B102" t="s">
         <v>369</v>
       </c>
-    </row>
-    <row r="102" spans="1:11">
-      <c r="A102" t="s">
-        <v>198</v>
-      </c>
-      <c r="B102" t="s">
-        <v>371</v>
-      </c>
       <c r="C102" t="s">
+        <v>159</v>
+      </c>
+      <c r="D102" t="s">
+        <v>14</v>
+      </c>
+      <c r="E102" t="s">
+        <v>160</v>
+      </c>
+      <c r="F102" t="s">
         <v>161</v>
-      </c>
-      <c r="D102" t="s">
-        <v>14</v>
-      </c>
-      <c r="E102" t="s">
-        <v>162</v>
-      </c>
-      <c r="F102" t="s">
-        <v>163</v>
       </c>
       <c r="H102" t="s">
         <v>104</v>
@@ -5905,53 +5963,53 @@
         <v>18</v>
       </c>
       <c r="J102" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="K102" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="103" spans="1:11">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="103" hidden="1" spans="1:11">
       <c r="A103" t="s">
+        <v>370</v>
+      </c>
+      <c r="B103" t="s">
+        <v>371</v>
+      </c>
+      <c r="C103" t="s">
+        <v>172</v>
+      </c>
+      <c r="D103" t="s">
+        <v>14</v>
+      </c>
+      <c r="E103" t="s">
+        <v>32</v>
+      </c>
+      <c r="F103" t="s">
+        <v>173</v>
+      </c>
+      <c r="H103" t="s">
+        <v>27</v>
+      </c>
+      <c r="I103" t="s">
+        <v>28</v>
+      </c>
+      <c r="J103" t="s">
+        <v>162</v>
+      </c>
+      <c r="K103" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="104" hidden="1" spans="1:11">
+      <c r="A104" t="s">
+        <v>360</v>
+      </c>
+      <c r="B104" t="s">
         <v>372</v>
       </c>
-      <c r="B103" t="s">
-        <v>373</v>
-      </c>
-      <c r="C103" t="s">
-        <v>174</v>
-      </c>
-      <c r="D103" t="s">
-        <v>14</v>
-      </c>
-      <c r="E103" t="s">
-        <v>31</v>
-      </c>
-      <c r="F103" t="s">
-        <v>175</v>
-      </c>
-      <c r="H103" t="s">
-        <v>26</v>
-      </c>
-      <c r="I103" t="s">
-        <v>27</v>
-      </c>
-      <c r="J103" t="s">
-        <v>164</v>
-      </c>
-      <c r="K103" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="104" spans="1:11">
-      <c r="A104" t="s">
-        <v>362</v>
-      </c>
-      <c r="B104" t="s">
-        <v>374</v>
-      </c>
       <c r="C104" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D104" t="s">
         <v>14</v>
@@ -5960,62 +6018,62 @@
         <v>15</v>
       </c>
       <c r="F104" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="H104" t="s">
         <v>109</v>
       </c>
       <c r="I104" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J104" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="K104" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="105" spans="1:11">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="105" hidden="1" spans="1:11">
       <c r="A105" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B105" t="s">
+        <v>373</v>
+      </c>
+      <c r="C105" t="s">
+        <v>202</v>
+      </c>
+      <c r="D105" t="s">
+        <v>14</v>
+      </c>
+      <c r="E105" t="s">
+        <v>15</v>
+      </c>
+      <c r="F105" t="s">
+        <v>203</v>
+      </c>
+      <c r="G105" t="s">
+        <v>204</v>
+      </c>
+      <c r="H105" t="s">
+        <v>27</v>
+      </c>
+      <c r="I105" t="s">
+        <v>35</v>
+      </c>
+      <c r="J105" t="s">
+        <v>358</v>
+      </c>
+      <c r="K105" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="106" hidden="1" spans="1:11">
+      <c r="A106" t="s">
+        <v>374</v>
+      </c>
+      <c r="B106" t="s">
         <v>375</v>
-      </c>
-      <c r="C105" t="s">
-        <v>204</v>
-      </c>
-      <c r="D105" t="s">
-        <v>14</v>
-      </c>
-      <c r="E105" t="s">
-        <v>15</v>
-      </c>
-      <c r="F105" t="s">
-        <v>205</v>
-      </c>
-      <c r="G105" t="s">
-        <v>206</v>
-      </c>
-      <c r="H105" t="s">
-        <v>26</v>
-      </c>
-      <c r="I105" t="s">
-        <v>34</v>
-      </c>
-      <c r="J105" t="s">
-        <v>360</v>
-      </c>
-      <c r="K105" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="106" spans="1:11">
-      <c r="A106" t="s">
-        <v>376</v>
-      </c>
-      <c r="B106" t="s">
-        <v>377</v>
       </c>
       <c r="C106" t="s">
         <v>13</v>
@@ -6030,24 +6088,24 @@
         <v>16</v>
       </c>
       <c r="H106" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I106" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J106" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="K106" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="107" spans="1:11">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="107" hidden="1" spans="1:11">
       <c r="A107" t="s">
+        <v>374</v>
+      </c>
+      <c r="B107" t="s">
         <v>376</v>
-      </c>
-      <c r="B107" t="s">
-        <v>378</v>
       </c>
       <c r="C107" t="s">
         <v>13</v>
@@ -6068,56 +6126,56 @@
         <v>18</v>
       </c>
       <c r="J107" t="s">
+        <v>377</v>
+      </c>
+      <c r="K107" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11">
+      <c r="A108" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B108" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="K107" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="108" spans="1:11">
-      <c r="A108" t="s">
-        <v>172</v>
-      </c>
-      <c r="B108" t="s">
-        <v>381</v>
-      </c>
-      <c r="C108" t="s">
+      <c r="C108" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="D108" t="s">
+      <c r="D108" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E108" t="s">
+      <c r="E108" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F108" t="s">
         <v>129</v>
       </c>
-      <c r="F108" t="s">
+      <c r="G108" t="s">
         <v>130</v>
       </c>
-      <c r="G108" t="s">
-        <v>131</v>
-      </c>
       <c r="H108" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I108" t="s">
         <v>18</v>
       </c>
       <c r="J108" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="K108" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="109" hidden="1" spans="1:11">
+      <c r="A109" t="s">
         <v>380</v>
       </c>
-    </row>
-    <row r="109" spans="1:11">
-      <c r="A109" t="s">
-        <v>382</v>
-      </c>
       <c r="B109" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C109" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D109" t="s">
         <v>14</v>
@@ -6126,7 +6184,7 @@
         <v>15</v>
       </c>
       <c r="F109" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H109" t="s">
         <v>104</v>
@@ -6135,18 +6193,18 @@
         <v>18</v>
       </c>
       <c r="J109" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="K109" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="110" spans="1:11">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="110" hidden="1" spans="1:11">
       <c r="A110" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B110" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C110" t="s">
         <v>119</v>
@@ -6164,56 +6222,56 @@
         <v>109</v>
       </c>
       <c r="I110" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J110" t="s">
+        <v>377</v>
+      </c>
+      <c r="K110" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11">
+      <c r="A111" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B111" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="K110" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="111" spans="1:11">
-      <c r="A111" t="s">
-        <v>172</v>
-      </c>
-      <c r="B111" t="s">
-        <v>381</v>
-      </c>
-      <c r="C111" t="s">
+      <c r="C111" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="D111" t="s">
+      <c r="D111" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E111" t="s">
+      <c r="E111" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F111" t="s">
         <v>129</v>
       </c>
-      <c r="F111" t="s">
+      <c r="G111" t="s">
         <v>130</v>
-      </c>
-      <c r="G111" t="s">
-        <v>131</v>
       </c>
       <c r="H111" t="s">
         <v>109</v>
       </c>
       <c r="I111" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J111" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="K111" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="112" spans="1:11">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="112" hidden="1" spans="1:11">
       <c r="A112" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B112" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C112" t="s">
         <v>119</v>
@@ -6228,100 +6286,103 @@
         <v>120</v>
       </c>
       <c r="H112" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I112" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J112" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="K112" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="113" spans="1:11">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="113" hidden="1" spans="1:11">
       <c r="A113" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B113" t="s">
+        <v>386</v>
+      </c>
+      <c r="C113" t="s">
+        <v>387</v>
+      </c>
+      <c r="D113" t="s">
+        <v>14</v>
+      </c>
+      <c r="E113" t="s">
+        <v>160</v>
+      </c>
+      <c r="F113" t="s">
         <v>388</v>
-      </c>
-      <c r="C113" t="s">
-        <v>389</v>
-      </c>
-      <c r="D113" t="s">
-        <v>14</v>
-      </c>
-      <c r="E113" t="s">
-        <v>162</v>
-      </c>
-      <c r="F113" t="s">
-        <v>390</v>
       </c>
       <c r="H113" t="s">
         <v>109</v>
       </c>
       <c r="I113" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J113" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="K113" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="114" spans="1:11">
       <c r="A114" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B114" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C114" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D114" t="s">
         <v>24</v>
       </c>
+      <c r="E114" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="F114" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="G114" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="H114" t="s">
         <v>104</v>
       </c>
       <c r="I114" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J114" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="K114" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="115" spans="1:11">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="115" hidden="1" spans="1:11">
       <c r="A115" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B115" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C115" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D115" t="s">
         <v>14</v>
       </c>
       <c r="E115" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F115" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H115" t="s">
         <v>109</v>
@@ -6330,21 +6391,21 @@
         <v>18</v>
       </c>
       <c r="J115" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="K115" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="116" spans="1:11">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="116" hidden="1" spans="1:11">
       <c r="A116" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B116" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C116" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D116" t="s">
         <v>14</v>
@@ -6353,7 +6414,7 @@
         <v>15</v>
       </c>
       <c r="F116" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="H116" t="s">
         <v>17</v>
@@ -6362,225 +6423,225 @@
         <v>18</v>
       </c>
       <c r="J116" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="K116" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="117" hidden="1" spans="1:11">
+      <c r="A117" t="s">
+        <v>196</v>
+      </c>
+      <c r="B117" t="s">
         <v>392</v>
       </c>
-    </row>
-    <row r="117" spans="1:11">
-      <c r="A117" t="s">
-        <v>198</v>
-      </c>
-      <c r="B117" t="s">
-        <v>394</v>
-      </c>
       <c r="C117" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D117" t="s">
         <v>14</v>
       </c>
       <c r="E117" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F117" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="H117" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I117" t="s">
         <v>18</v>
       </c>
       <c r="J117" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="K117" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="118" spans="1:11">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="118" hidden="1" spans="1:11">
       <c r="A118" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B118" t="s">
+        <v>393</v>
+      </c>
+      <c r="C118" t="s">
+        <v>394</v>
+      </c>
+      <c r="D118" t="s">
+        <v>14</v>
+      </c>
+      <c r="E118" t="s">
+        <v>15</v>
+      </c>
+      <c r="F118" t="s">
         <v>395</v>
-      </c>
-      <c r="C118" t="s">
-        <v>396</v>
-      </c>
-      <c r="D118" t="s">
-        <v>14</v>
-      </c>
-      <c r="E118" t="s">
-        <v>15</v>
-      </c>
-      <c r="F118" t="s">
-        <v>397</v>
       </c>
       <c r="H118" t="s">
         <v>109</v>
       </c>
       <c r="I118" t="s">
+        <v>28</v>
+      </c>
+      <c r="J118" t="s">
+        <v>396</v>
+      </c>
+      <c r="K118" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="119" hidden="1" spans="1:11">
+      <c r="A119" t="s">
+        <v>362</v>
+      </c>
+      <c r="B119" t="s">
+        <v>397</v>
+      </c>
+      <c r="C119" t="s">
+        <v>202</v>
+      </c>
+      <c r="D119" t="s">
+        <v>14</v>
+      </c>
+      <c r="E119" t="s">
+        <v>15</v>
+      </c>
+      <c r="F119" t="s">
+        <v>203</v>
+      </c>
+      <c r="G119" t="s">
+        <v>204</v>
+      </c>
+      <c r="H119" t="s">
         <v>27</v>
       </c>
-      <c r="J118" t="s">
+      <c r="I119" t="s">
+        <v>35</v>
+      </c>
+      <c r="J119" t="s">
+        <v>358</v>
+      </c>
+      <c r="K119" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="120" hidden="1" spans="1:11">
+      <c r="A120" t="s">
+        <v>170</v>
+      </c>
+      <c r="B120" t="s">
         <v>398</v>
       </c>
-      <c r="K118" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="119" spans="1:11">
-      <c r="A119" t="s">
-        <v>364</v>
-      </c>
-      <c r="B119" t="s">
-        <v>399</v>
-      </c>
-      <c r="C119" t="s">
-        <v>204</v>
-      </c>
-      <c r="D119" t="s">
-        <v>14</v>
-      </c>
-      <c r="E119" t="s">
-        <v>15</v>
-      </c>
-      <c r="F119" t="s">
-        <v>205</v>
-      </c>
-      <c r="G119" t="s">
-        <v>206</v>
-      </c>
-      <c r="H119" t="s">
-        <v>26</v>
-      </c>
-      <c r="I119" t="s">
-        <v>34</v>
-      </c>
-      <c r="J119" t="s">
-        <v>360</v>
-      </c>
-      <c r="K119" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="120" spans="1:11">
-      <c r="A120" t="s">
+      <c r="C120" t="s">
         <v>172</v>
       </c>
-      <c r="B120" t="s">
-        <v>400</v>
-      </c>
-      <c r="C120" t="s">
-        <v>174</v>
-      </c>
       <c r="D120" t="s">
         <v>14</v>
       </c>
       <c r="E120" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F120" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H120" t="s">
         <v>109</v>
       </c>
       <c r="I120" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J120" t="s">
+        <v>358</v>
+      </c>
+      <c r="K120" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="121" hidden="1" spans="1:11">
+      <c r="A121" t="s">
         <v>360</v>
       </c>
-      <c r="K120" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="121" spans="1:11">
-      <c r="A121" t="s">
-        <v>362</v>
-      </c>
       <c r="B121" t="s">
+        <v>399</v>
+      </c>
+      <c r="C121" t="s">
+        <v>400</v>
+      </c>
+      <c r="D121" t="s">
+        <v>14</v>
+      </c>
+      <c r="E121" t="s">
+        <v>15</v>
+      </c>
+      <c r="F121" t="s">
         <v>401</v>
       </c>
-      <c r="C121" t="s">
+      <c r="H121" t="s">
+        <v>27</v>
+      </c>
+      <c r="I121" t="s">
+        <v>40</v>
+      </c>
+      <c r="J121" t="s">
+        <v>358</v>
+      </c>
+      <c r="K121" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="122" hidden="1" spans="1:11">
+      <c r="A122" t="s">
         <v>402</v>
       </c>
-      <c r="D121" t="s">
-        <v>14</v>
-      </c>
-      <c r="E121" t="s">
-        <v>15</v>
-      </c>
-      <c r="F121" t="s">
+      <c r="B122" t="s">
         <v>403</v>
       </c>
-      <c r="H121" t="s">
-        <v>26</v>
-      </c>
-      <c r="I121" t="s">
-        <v>39</v>
-      </c>
-      <c r="J121" t="s">
-        <v>360</v>
-      </c>
-      <c r="K121" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="122" spans="1:11">
-      <c r="A122" t="s">
-        <v>404</v>
-      </c>
-      <c r="B122" t="s">
-        <v>405</v>
-      </c>
       <c r="C122" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D122" t="s">
         <v>14</v>
       </c>
       <c r="E122" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F122" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="H122" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I122" t="s">
         <v>18</v>
       </c>
       <c r="J122" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="K122" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="123" hidden="1" spans="1:11">
+      <c r="A123" t="s">
+        <v>405</v>
+      </c>
+      <c r="B123" t="s">
         <v>406</v>
       </c>
-    </row>
-    <row r="123" spans="1:11">
-      <c r="A123" t="s">
-        <v>407</v>
-      </c>
-      <c r="B123" t="s">
-        <v>408</v>
-      </c>
       <c r="C123" t="s">
+        <v>142</v>
+      </c>
+      <c r="D123" t="s">
+        <v>14</v>
+      </c>
+      <c r="E123" t="s">
+        <v>15</v>
+      </c>
+      <c r="F123" t="s">
         <v>143</v>
-      </c>
-      <c r="D123" t="s">
-        <v>14</v>
-      </c>
-      <c r="E123" t="s">
-        <v>15</v>
-      </c>
-      <c r="F123" t="s">
-        <v>144</v>
       </c>
       <c r="H123" t="s">
         <v>104</v>
@@ -6592,50 +6653,50 @@
         <v>19</v>
       </c>
       <c r="K123" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="124" spans="1:11">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="124" hidden="1" spans="1:11">
       <c r="A124" t="s">
+        <v>407</v>
+      </c>
+      <c r="B124" t="s">
+        <v>408</v>
+      </c>
+      <c r="C124" t="s">
+        <v>180</v>
+      </c>
+      <c r="D124" t="s">
+        <v>14</v>
+      </c>
+      <c r="E124" t="s">
+        <v>32</v>
+      </c>
+      <c r="F124" t="s">
+        <v>181</v>
+      </c>
+      <c r="H124" t="s">
+        <v>27</v>
+      </c>
+      <c r="I124" t="s">
+        <v>55</v>
+      </c>
+      <c r="J124" t="s">
+        <v>358</v>
+      </c>
+      <c r="K124" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="125" hidden="1" spans="1:11">
+      <c r="A125" t="s">
+        <v>374</v>
+      </c>
+      <c r="B125" t="s">
         <v>409</v>
       </c>
-      <c r="B124" t="s">
-        <v>410</v>
-      </c>
-      <c r="C124" t="s">
-        <v>182</v>
-      </c>
-      <c r="D124" t="s">
-        <v>14</v>
-      </c>
-      <c r="E124" t="s">
-        <v>31</v>
-      </c>
-      <c r="F124" t="s">
-        <v>183</v>
-      </c>
-      <c r="H124" t="s">
-        <v>26</v>
-      </c>
-      <c r="I124" t="s">
-        <v>54</v>
-      </c>
-      <c r="J124" t="s">
-        <v>360</v>
-      </c>
-      <c r="K124" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="125" spans="1:11">
-      <c r="A125" t="s">
-        <v>376</v>
-      </c>
-      <c r="B125" t="s">
-        <v>411</v>
-      </c>
       <c r="C125" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D125" t="s">
         <v>14</v>
@@ -6644,138 +6705,138 @@
         <v>15</v>
       </c>
       <c r="F125" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H125" t="s">
         <v>109</v>
       </c>
       <c r="I125" t="s">
+        <v>28</v>
+      </c>
+      <c r="J125" t="s">
+        <v>358</v>
+      </c>
+      <c r="K125" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="126" hidden="1" spans="1:11">
+      <c r="A126" t="s">
+        <v>362</v>
+      </c>
+      <c r="B126" t="s">
+        <v>410</v>
+      </c>
+      <c r="C126" t="s">
+        <v>202</v>
+      </c>
+      <c r="D126" t="s">
+        <v>14</v>
+      </c>
+      <c r="E126" t="s">
+        <v>15</v>
+      </c>
+      <c r="F126" t="s">
+        <v>203</v>
+      </c>
+      <c r="G126" t="s">
+        <v>204</v>
+      </c>
+      <c r="H126" t="s">
         <v>27</v>
       </c>
-      <c r="J125" t="s">
-        <v>360</v>
-      </c>
-      <c r="K125" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="126" spans="1:11">
-      <c r="A126" t="s">
-        <v>364</v>
-      </c>
-      <c r="B126" t="s">
-        <v>412</v>
-      </c>
-      <c r="C126" t="s">
-        <v>204</v>
-      </c>
-      <c r="D126" t="s">
-        <v>14</v>
-      </c>
-      <c r="E126" t="s">
-        <v>15</v>
-      </c>
-      <c r="F126" t="s">
-        <v>205</v>
-      </c>
-      <c r="G126" t="s">
-        <v>206</v>
-      </c>
-      <c r="H126" t="s">
-        <v>26</v>
-      </c>
       <c r="I126" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J126" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="K126" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="127" spans="1:11">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="127" hidden="1" spans="1:11">
       <c r="A127" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B127" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C127" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D127" t="s">
         <v>14</v>
       </c>
       <c r="E127" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F127" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="H127" t="s">
         <v>104</v>
       </c>
       <c r="I127" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J127" t="s">
+        <v>358</v>
+      </c>
+      <c r="K127" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="128" hidden="1" spans="1:11">
+      <c r="A128" t="s">
         <v>360</v>
       </c>
-      <c r="K127" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="128" spans="1:11">
-      <c r="A128" t="s">
-        <v>362</v>
-      </c>
       <c r="B128" t="s">
+        <v>411</v>
+      </c>
+      <c r="C128" t="s">
+        <v>400</v>
+      </c>
+      <c r="D128" t="s">
+        <v>14</v>
+      </c>
+      <c r="E128" t="s">
+        <v>15</v>
+      </c>
+      <c r="F128" t="s">
+        <v>401</v>
+      </c>
+      <c r="H128" t="s">
+        <v>27</v>
+      </c>
+      <c r="I128" t="s">
+        <v>40</v>
+      </c>
+      <c r="J128" t="s">
+        <v>358</v>
+      </c>
+      <c r="K128" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="129" hidden="1" spans="1:11">
+      <c r="A129" t="s">
+        <v>412</v>
+      </c>
+      <c r="B129" t="s">
         <v>413</v>
       </c>
-      <c r="C128" t="s">
-        <v>402</v>
-      </c>
-      <c r="D128" t="s">
-        <v>14</v>
-      </c>
-      <c r="E128" t="s">
-        <v>15</v>
-      </c>
-      <c r="F128" t="s">
-        <v>403</v>
-      </c>
-      <c r="H128" t="s">
-        <v>26</v>
-      </c>
-      <c r="I128" t="s">
-        <v>39</v>
-      </c>
-      <c r="J128" t="s">
-        <v>360</v>
-      </c>
-      <c r="K128" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="129" spans="1:11">
-      <c r="A129" t="s">
+      <c r="C129" t="s">
         <v>414</v>
       </c>
-      <c r="B129" t="s">
+      <c r="D129" t="s">
+        <v>14</v>
+      </c>
+      <c r="E129" t="s">
+        <v>32</v>
+      </c>
+      <c r="F129" t="s">
         <v>415</v>
-      </c>
-      <c r="C129" t="s">
-        <v>416</v>
-      </c>
-      <c r="D129" t="s">
-        <v>14</v>
-      </c>
-      <c r="E129" t="s">
-        <v>31</v>
-      </c>
-      <c r="F129" t="s">
-        <v>417</v>
       </c>
       <c r="H129" t="s">
         <v>109</v>
@@ -6784,315 +6845,318 @@
         <v>18</v>
       </c>
       <c r="J129" t="s">
+        <v>416</v>
+      </c>
+      <c r="K129" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="130" hidden="1" spans="1:11">
+      <c r="A130" t="s">
         <v>418</v>
       </c>
-      <c r="K129" t="s">
+      <c r="B130" t="s">
         <v>419</v>
       </c>
-    </row>
-    <row r="130" spans="1:11">
-      <c r="A130" t="s">
+      <c r="C130" t="s">
         <v>420</v>
       </c>
-      <c r="B130" t="s">
+      <c r="D130" t="s">
+        <v>14</v>
+      </c>
+      <c r="E130" t="s">
+        <v>15</v>
+      </c>
+      <c r="F130" t="s">
         <v>421</v>
       </c>
-      <c r="C130" t="s">
-        <v>422</v>
-      </c>
-      <c r="D130" t="s">
-        <v>14</v>
-      </c>
-      <c r="E130" t="s">
-        <v>15</v>
-      </c>
-      <c r="F130" t="s">
-        <v>423</v>
-      </c>
       <c r="H130" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I130" t="s">
         <v>18</v>
       </c>
       <c r="J130" t="s">
+        <v>422</v>
+      </c>
+      <c r="K130" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="131" hidden="1" spans="1:11">
+      <c r="A131" t="s">
+        <v>423</v>
+      </c>
+      <c r="B131" t="s">
         <v>424</v>
       </c>
-      <c r="K130" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="131" spans="1:11">
-      <c r="A131" t="s">
+      <c r="C131" t="s">
         <v>425</v>
       </c>
-      <c r="B131" t="s">
+      <c r="D131" t="s">
+        <v>14</v>
+      </c>
+      <c r="E131" t="s">
+        <v>15</v>
+      </c>
+      <c r="F131" t="s">
         <v>426</v>
-      </c>
-      <c r="C131" t="s">
-        <v>427</v>
-      </c>
-      <c r="D131" t="s">
-        <v>14</v>
-      </c>
-      <c r="E131" t="s">
-        <v>15</v>
-      </c>
-      <c r="F131" t="s">
-        <v>428</v>
       </c>
       <c r="H131" t="s">
         <v>104</v>
       </c>
       <c r="I131" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J131" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K131" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="132" spans="1:11">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="132" hidden="1" spans="1:11">
       <c r="A132" t="s">
+        <v>427</v>
+      </c>
+      <c r="B132" t="s">
+        <v>428</v>
+      </c>
+      <c r="C132" t="s">
+        <v>146</v>
+      </c>
+      <c r="D132" t="s">
+        <v>14</v>
+      </c>
+      <c r="E132" t="s">
+        <v>15</v>
+      </c>
+      <c r="F132" t="s">
+        <v>147</v>
+      </c>
+      <c r="H132" t="s">
+        <v>27</v>
+      </c>
+      <c r="I132" t="s">
+        <v>28</v>
+      </c>
+      <c r="J132" t="s">
+        <v>422</v>
+      </c>
+      <c r="K132" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="133" hidden="1" spans="1:11">
+      <c r="A133" t="s">
         <v>429</v>
       </c>
-      <c r="B132" t="s">
+      <c r="B133" t="s">
         <v>430</v>
       </c>
-      <c r="C132" t="s">
-        <v>147</v>
-      </c>
-      <c r="D132" t="s">
-        <v>14</v>
-      </c>
-      <c r="E132" t="s">
-        <v>15</v>
-      </c>
-      <c r="F132" t="s">
-        <v>148</v>
-      </c>
-      <c r="H132" t="s">
-        <v>26</v>
-      </c>
-      <c r="I132" t="s">
-        <v>27</v>
-      </c>
-      <c r="J132" t="s">
-        <v>424</v>
-      </c>
-      <c r="K132" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="133" spans="1:11">
-      <c r="A133" t="s">
-        <v>431</v>
-      </c>
-      <c r="B133" t="s">
-        <v>432</v>
-      </c>
       <c r="C133" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D133" t="s">
         <v>14</v>
       </c>
       <c r="E133" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F133" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="H133" t="s">
         <v>109</v>
       </c>
       <c r="I133" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J133" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="K133" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="134" spans="1:11">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="134" hidden="1" spans="1:11">
       <c r="A134" t="s">
+        <v>431</v>
+      </c>
+      <c r="B134" t="s">
+        <v>432</v>
+      </c>
+      <c r="C134" t="s">
         <v>433</v>
       </c>
-      <c r="B134" t="s">
+      <c r="D134" t="s">
+        <v>14</v>
+      </c>
+      <c r="E134" t="s">
+        <v>32</v>
+      </c>
+      <c r="F134" t="s">
         <v>434</v>
-      </c>
-      <c r="C134" t="s">
-        <v>435</v>
-      </c>
-      <c r="D134" t="s">
-        <v>14</v>
-      </c>
-      <c r="E134" t="s">
-        <v>31</v>
-      </c>
-      <c r="F134" t="s">
-        <v>436</v>
       </c>
       <c r="H134" t="s">
         <v>17</v>
       </c>
       <c r="I134" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J134" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="K134" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="135" hidden="1" spans="1:11">
+      <c r="A135" t="s">
+        <v>418</v>
+      </c>
+      <c r="B135" t="s">
         <v>419</v>
       </c>
-    </row>
-    <row r="135" spans="1:11">
-      <c r="A135" t="s">
+      <c r="C135" t="s">
         <v>420</v>
       </c>
-      <c r="B135" t="s">
+      <c r="D135" t="s">
+        <v>14</v>
+      </c>
+      <c r="E135" t="s">
+        <v>15</v>
+      </c>
+      <c r="F135" t="s">
         <v>421</v>
       </c>
-      <c r="C135" t="s">
+      <c r="H135" t="s">
+        <v>27</v>
+      </c>
+      <c r="I135" t="s">
+        <v>35</v>
+      </c>
+      <c r="J135" t="s">
         <v>422</v>
       </c>
-      <c r="D135" t="s">
-        <v>14</v>
-      </c>
-      <c r="E135" t="s">
-        <v>15</v>
-      </c>
-      <c r="F135" t="s">
-        <v>423</v>
-      </c>
-      <c r="H135" t="s">
-        <v>26</v>
-      </c>
-      <c r="I135" t="s">
-        <v>34</v>
-      </c>
-      <c r="J135" t="s">
-        <v>424</v>
-      </c>
       <c r="K135" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="136" spans="1:11">
       <c r="A136" t="s">
+        <v>435</v>
+      </c>
+      <c r="B136" t="s">
+        <v>436</v>
+      </c>
+      <c r="C136" t="s">
         <v>437</v>
-      </c>
-      <c r="B136" t="s">
-        <v>438</v>
-      </c>
-      <c r="C136" t="s">
-        <v>439</v>
       </c>
       <c r="D136" t="s">
         <v>24</v>
       </c>
+      <c r="E136" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="F136" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="H136" t="s">
         <v>17</v>
       </c>
       <c r="I136" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J136" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="K136" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="137" spans="1:11">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="137" hidden="1" spans="1:11">
       <c r="A137" t="s">
+        <v>439</v>
+      </c>
+      <c r="B137" t="s">
+        <v>440</v>
+      </c>
+      <c r="C137" t="s">
+        <v>184</v>
+      </c>
+      <c r="D137" t="s">
+        <v>14</v>
+      </c>
+      <c r="E137" t="s">
+        <v>32</v>
+      </c>
+      <c r="F137" t="s">
+        <v>185</v>
+      </c>
+      <c r="H137" t="s">
+        <v>27</v>
+      </c>
+      <c r="I137" t="s">
+        <v>40</v>
+      </c>
+      <c r="J137" t="s">
+        <v>422</v>
+      </c>
+      <c r="K137" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="138" hidden="1" spans="1:11">
+      <c r="A138" t="s">
         <v>441</v>
       </c>
-      <c r="B137" t="s">
+      <c r="B138" t="s">
         <v>442</v>
       </c>
-      <c r="C137" t="s">
-        <v>186</v>
-      </c>
-      <c r="D137" t="s">
-        <v>14</v>
-      </c>
-      <c r="E137" t="s">
-        <v>31</v>
-      </c>
-      <c r="F137" t="s">
-        <v>187</v>
-      </c>
-      <c r="H137" t="s">
-        <v>26</v>
-      </c>
-      <c r="I137" t="s">
-        <v>39</v>
-      </c>
-      <c r="J137" t="s">
-        <v>424</v>
-      </c>
-      <c r="K137" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="138" spans="1:11">
-      <c r="A138" t="s">
-        <v>443</v>
-      </c>
-      <c r="B138" t="s">
-        <v>444</v>
-      </c>
       <c r="C138" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D138" t="s">
         <v>14</v>
       </c>
       <c r="E138" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F138" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H138" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I138" t="s">
         <v>18</v>
       </c>
       <c r="J138" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="K138" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="139" hidden="1" spans="1:11">
+      <c r="A139" t="s">
+        <v>444</v>
+      </c>
+      <c r="B139" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="139" spans="1:11">
-      <c r="A139" t="s">
-        <v>446</v>
-      </c>
-      <c r="B139" t="s">
-        <v>447</v>
-      </c>
       <c r="C139" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D139" t="s">
         <v>14</v>
       </c>
       <c r="E139" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F139" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="H139" t="s">
         <v>104</v>
@@ -7101,22 +7165,22 @@
         <v>18</v>
       </c>
       <c r="J139" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="K139" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="140" spans="1:11">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="140" hidden="1" spans="1:11">
       <c r="A140" t="s">
+        <v>423</v>
+      </c>
+      <c r="B140" t="s">
+        <v>446</v>
+      </c>
+      <c r="C140" t="s">
         <v>425</v>
       </c>
-      <c r="B140" t="s">
-        <v>448</v>
-      </c>
-      <c r="C140" t="s">
-        <v>427</v>
-      </c>
       <c r="D140" t="s">
         <v>14</v>
       </c>
@@ -7124,62 +7188,62 @@
         <v>15</v>
       </c>
       <c r="F140" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="H140" t="s">
         <v>104</v>
       </c>
       <c r="I140" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J140" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K140" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="141" spans="1:11">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="141" hidden="1" spans="1:11">
       <c r="A141" t="s">
+        <v>447</v>
+      </c>
+      <c r="B141" t="s">
+        <v>448</v>
+      </c>
+      <c r="C141" t="s">
+        <v>246</v>
+      </c>
+      <c r="D141" t="s">
+        <v>14</v>
+      </c>
+      <c r="E141" t="s">
+        <v>15</v>
+      </c>
+      <c r="F141" t="s">
+        <v>247</v>
+      </c>
+      <c r="H141" t="s">
+        <v>27</v>
+      </c>
+      <c r="I141" t="s">
+        <v>28</v>
+      </c>
+      <c r="J141" t="s">
+        <v>228</v>
+      </c>
+      <c r="K141" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="142" hidden="1" spans="1:11">
+      <c r="A142" t="s">
+        <v>248</v>
+      </c>
+      <c r="B142" t="s">
         <v>449</v>
       </c>
-      <c r="B141" t="s">
-        <v>450</v>
-      </c>
-      <c r="C141" t="s">
-        <v>248</v>
-      </c>
-      <c r="D141" t="s">
-        <v>14</v>
-      </c>
-      <c r="E141" t="s">
-        <v>15</v>
-      </c>
-      <c r="F141" t="s">
-        <v>249</v>
-      </c>
-      <c r="H141" t="s">
-        <v>26</v>
-      </c>
-      <c r="I141" t="s">
-        <v>27</v>
-      </c>
-      <c r="J141" t="s">
-        <v>230</v>
-      </c>
-      <c r="K141" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="142" spans="1:11">
-      <c r="A142" t="s">
-        <v>250</v>
-      </c>
-      <c r="B142" t="s">
-        <v>451</v>
-      </c>
       <c r="C142" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D142" t="s">
         <v>14</v>
@@ -7188,158 +7252,161 @@
         <v>15</v>
       </c>
       <c r="F142" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H142" t="s">
         <v>104</v>
       </c>
       <c r="I142" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J142" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="K142" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="143" spans="1:11">
       <c r="A143" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B143" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C143" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D143" t="s">
         <v>24</v>
       </c>
+      <c r="E143" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="F143" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="H143" t="s">
         <v>109</v>
       </c>
       <c r="I143" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J143" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="K143" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="144" spans="1:11">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="144" hidden="1" spans="1:11">
       <c r="A144" t="s">
+        <v>452</v>
+      </c>
+      <c r="B144" t="s">
+        <v>453</v>
+      </c>
+      <c r="C144" t="s">
         <v>454</v>
       </c>
-      <c r="B144" t="s">
+      <c r="D144" t="s">
+        <v>14</v>
+      </c>
+      <c r="E144" t="s">
+        <v>15</v>
+      </c>
+      <c r="F144" t="s">
         <v>455</v>
       </c>
-      <c r="C144" t="s">
+      <c r="H144" t="s">
+        <v>27</v>
+      </c>
+      <c r="I144" t="s">
+        <v>35</v>
+      </c>
+      <c r="J144" t="s">
+        <v>416</v>
+      </c>
+      <c r="K144" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="145" hidden="1" spans="1:11">
+      <c r="A145" t="s">
         <v>456</v>
       </c>
-      <c r="D144" t="s">
-        <v>14</v>
-      </c>
-      <c r="E144" t="s">
-        <v>15</v>
-      </c>
-      <c r="F144" t="s">
+      <c r="B145" t="s">
         <v>457</v>
       </c>
-      <c r="H144" t="s">
-        <v>26</v>
-      </c>
-      <c r="I144" t="s">
-        <v>34</v>
-      </c>
-      <c r="J144" t="s">
-        <v>418</v>
-      </c>
-      <c r="K144" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="145" spans="1:11">
-      <c r="A145" t="s">
+      <c r="C145" t="s">
+        <v>414</v>
+      </c>
+      <c r="D145" t="s">
+        <v>14</v>
+      </c>
+      <c r="E145" t="s">
+        <v>32</v>
+      </c>
+      <c r="F145" t="s">
+        <v>415</v>
+      </c>
+      <c r="H145" t="s">
+        <v>27</v>
+      </c>
+      <c r="I145" t="s">
+        <v>40</v>
+      </c>
+      <c r="J145" t="s">
+        <v>228</v>
+      </c>
+      <c r="K145" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="146" hidden="1" spans="1:11">
+      <c r="A146" t="s">
         <v>458</v>
       </c>
-      <c r="B145" t="s">
+      <c r="B146" t="s">
         <v>459</v>
       </c>
-      <c r="C145" t="s">
-        <v>416</v>
-      </c>
-      <c r="D145" t="s">
-        <v>14</v>
-      </c>
-      <c r="E145" t="s">
-        <v>31</v>
-      </c>
-      <c r="F145" t="s">
-        <v>417</v>
-      </c>
-      <c r="H145" t="s">
-        <v>26</v>
-      </c>
-      <c r="I145" t="s">
-        <v>39</v>
-      </c>
-      <c r="J145" t="s">
-        <v>230</v>
-      </c>
-      <c r="K145" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="146" spans="1:11">
-      <c r="A146" t="s">
-        <v>460</v>
-      </c>
-      <c r="B146" t="s">
-        <v>461</v>
-      </c>
       <c r="C146" t="s">
+        <v>202</v>
+      </c>
+      <c r="D146" t="s">
+        <v>14</v>
+      </c>
+      <c r="E146" t="s">
+        <v>15</v>
+      </c>
+      <c r="F146" t="s">
+        <v>203</v>
+      </c>
+      <c r="G146" t="s">
         <v>204</v>
-      </c>
-      <c r="D146" t="s">
-        <v>14</v>
-      </c>
-      <c r="E146" t="s">
-        <v>15</v>
-      </c>
-      <c r="F146" t="s">
-        <v>205</v>
-      </c>
-      <c r="G146" t="s">
-        <v>206</v>
       </c>
       <c r="H146" t="s">
         <v>104</v>
       </c>
       <c r="I146" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J146" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="K146" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="147" spans="1:11">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="147" hidden="1" spans="1:11">
       <c r="A147" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B147" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C147" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D147" t="s">
         <v>14</v>
@@ -7348,7 +7415,7 @@
         <v>15</v>
       </c>
       <c r="F147" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H147" t="s">
         <v>109</v>
@@ -7357,21 +7424,21 @@
         <v>18</v>
       </c>
       <c r="J147" t="s">
+        <v>461</v>
+      </c>
+      <c r="K147" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="148" hidden="1" spans="1:11">
+      <c r="A148" t="s">
         <v>463</v>
       </c>
-      <c r="K147" t="s">
+      <c r="B148" t="s">
         <v>464</v>
       </c>
-    </row>
-    <row r="148" spans="1:11">
-      <c r="A148" t="s">
-        <v>465</v>
-      </c>
-      <c r="B148" t="s">
-        <v>466</v>
-      </c>
       <c r="C148" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D148" t="s">
         <v>14</v>
@@ -7380,7 +7447,7 @@
         <v>15</v>
       </c>
       <c r="F148" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H148" t="s">
         <v>17</v>
@@ -7389,30 +7456,30 @@
         <v>18</v>
       </c>
       <c r="J148" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="K148" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="149" spans="1:11">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="149" hidden="1" spans="1:11">
       <c r="A149" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B149" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C149" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D149" t="s">
         <v>14</v>
       </c>
       <c r="E149" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F149" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H149" t="s">
         <v>104</v>
@@ -7421,22 +7488,22 @@
         <v>18</v>
       </c>
       <c r="J149" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="K149" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="150" spans="1:11">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="150" hidden="1" spans="1:11">
       <c r="A150" t="s">
+        <v>423</v>
+      </c>
+      <c r="B150" t="s">
+        <v>467</v>
+      </c>
+      <c r="C150" t="s">
         <v>425</v>
       </c>
-      <c r="B150" t="s">
-        <v>469</v>
-      </c>
-      <c r="C150" t="s">
-        <v>427</v>
-      </c>
       <c r="D150" t="s">
         <v>14</v>
       </c>
@@ -7444,30 +7511,30 @@
         <v>15</v>
       </c>
       <c r="F150" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="H150" t="s">
         <v>104</v>
       </c>
       <c r="I150" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J150" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K150" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="151" spans="1:11">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="151" hidden="1" spans="1:11">
       <c r="A151" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B151" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C151" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D151" t="s">
         <v>14</v>
@@ -7476,62 +7543,62 @@
         <v>15</v>
       </c>
       <c r="F151" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="H151" t="s">
         <v>17</v>
       </c>
       <c r="I151" t="s">
+        <v>28</v>
+      </c>
+      <c r="J151" t="s">
+        <v>461</v>
+      </c>
+      <c r="K151" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="152" hidden="1" spans="1:11">
+      <c r="A152" t="s">
+        <v>412</v>
+      </c>
+      <c r="B152" t="s">
+        <v>470</v>
+      </c>
+      <c r="C152" t="s">
+        <v>414</v>
+      </c>
+      <c r="D152" t="s">
+        <v>14</v>
+      </c>
+      <c r="E152" t="s">
+        <v>32</v>
+      </c>
+      <c r="F152" t="s">
+        <v>415</v>
+      </c>
+      <c r="H152" t="s">
         <v>27</v>
       </c>
-      <c r="J151" t="s">
-        <v>463</v>
-      </c>
-      <c r="K151" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="152" spans="1:11">
-      <c r="A152" t="s">
-        <v>414</v>
-      </c>
-      <c r="B152" t="s">
+      <c r="I152" t="s">
+        <v>28</v>
+      </c>
+      <c r="J152" t="s">
+        <v>461</v>
+      </c>
+      <c r="K152" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="153" hidden="1" spans="1:11">
+      <c r="A153" t="s">
+        <v>471</v>
+      </c>
+      <c r="B153" t="s">
         <v>472</v>
       </c>
-      <c r="C152" t="s">
-        <v>416</v>
-      </c>
-      <c r="D152" t="s">
-        <v>14</v>
-      </c>
-      <c r="E152" t="s">
-        <v>31</v>
-      </c>
-      <c r="F152" t="s">
-        <v>417</v>
-      </c>
-      <c r="H152" t="s">
-        <v>26</v>
-      </c>
-      <c r="I152" t="s">
-        <v>27</v>
-      </c>
-      <c r="J152" t="s">
-        <v>463</v>
-      </c>
-      <c r="K152" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="153" spans="1:11">
-      <c r="A153" t="s">
-        <v>473</v>
-      </c>
-      <c r="B153" t="s">
-        <v>474</v>
-      </c>
       <c r="C153" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D153" t="s">
         <v>14</v>
@@ -7540,30 +7607,30 @@
         <v>15</v>
       </c>
       <c r="F153" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="H153" t="s">
         <v>104</v>
       </c>
       <c r="I153" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J153" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="K153" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="154" spans="1:11">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="154" hidden="1" spans="1:11">
       <c r="A154" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B154" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C154" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D154" t="s">
         <v>14</v>
@@ -7572,30 +7639,30 @@
         <v>15</v>
       </c>
       <c r="F154" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H154" t="s">
         <v>17</v>
       </c>
       <c r="I154" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J154" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="K154" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="155" spans="1:11">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="155" hidden="1" spans="1:11">
       <c r="A155" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B155" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C155" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D155" t="s">
         <v>14</v>
@@ -7604,39 +7671,39 @@
         <v>15</v>
       </c>
       <c r="F155" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="H155" t="s">
         <v>104</v>
       </c>
       <c r="I155" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J155" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="K155" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="156" spans="1:11">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="156" hidden="1" spans="1:11">
       <c r="A156" t="s">
+        <v>477</v>
+      </c>
+      <c r="B156" t="s">
+        <v>478</v>
+      </c>
+      <c r="C156" t="s">
         <v>479</v>
       </c>
-      <c r="B156" t="s">
+      <c r="D156" t="s">
+        <v>14</v>
+      </c>
+      <c r="E156" t="s">
+        <v>15</v>
+      </c>
+      <c r="F156" t="s">
         <v>480</v>
-      </c>
-      <c r="C156" t="s">
-        <v>481</v>
-      </c>
-      <c r="D156" t="s">
-        <v>14</v>
-      </c>
-      <c r="E156" t="s">
-        <v>15</v>
-      </c>
-      <c r="F156" t="s">
-        <v>482</v>
       </c>
       <c r="H156" t="s">
         <v>109</v>
@@ -7645,21 +7712,21 @@
         <v>18</v>
       </c>
       <c r="J156" t="s">
+        <v>481</v>
+      </c>
+      <c r="K156" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="157" hidden="1" spans="1:11">
+      <c r="A157" t="s">
         <v>483</v>
       </c>
-      <c r="K156" t="s">
+      <c r="B157" t="s">
         <v>484</v>
       </c>
-    </row>
-    <row r="157" spans="1:11">
-      <c r="A157" t="s">
-        <v>485</v>
-      </c>
-      <c r="B157" t="s">
-        <v>486</v>
-      </c>
       <c r="C157" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D157" t="s">
         <v>14</v>
@@ -7668,30 +7735,30 @@
         <v>15</v>
       </c>
       <c r="F157" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="H157" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I157" t="s">
         <v>18</v>
       </c>
       <c r="J157" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="K157" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="158" spans="1:11">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="158" hidden="1" spans="1:11">
       <c r="A158" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B158" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C158" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D158" t="s">
         <v>14</v>
@@ -7700,190 +7767,193 @@
         <v>15</v>
       </c>
       <c r="F158" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="H158" t="s">
         <v>104</v>
       </c>
       <c r="I158" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J158" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="K158" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="159" spans="1:11">
       <c r="A159" t="s">
+        <v>487</v>
+      </c>
+      <c r="B159" t="s">
+        <v>488</v>
+      </c>
+      <c r="C159" t="s">
         <v>489</v>
-      </c>
-      <c r="B159" t="s">
-        <v>490</v>
-      </c>
-      <c r="C159" t="s">
-        <v>491</v>
       </c>
       <c r="D159" t="s">
         <v>24</v>
       </c>
+      <c r="E159" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="F159" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="G159" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="H159" t="s">
         <v>17</v>
       </c>
       <c r="I159" t="s">
+        <v>28</v>
+      </c>
+      <c r="J159" t="s">
+        <v>481</v>
+      </c>
+      <c r="K159" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="160" hidden="1" spans="1:11">
+      <c r="A160" t="s">
+        <v>492</v>
+      </c>
+      <c r="B160" t="s">
+        <v>493</v>
+      </c>
+      <c r="C160" t="s">
+        <v>400</v>
+      </c>
+      <c r="D160" t="s">
+        <v>14</v>
+      </c>
+      <c r="E160" t="s">
+        <v>15</v>
+      </c>
+      <c r="F160" t="s">
+        <v>401</v>
+      </c>
+      <c r="H160" t="s">
         <v>27</v>
       </c>
-      <c r="J159" t="s">
-        <v>483</v>
-      </c>
-      <c r="K159" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="160" spans="1:11">
-      <c r="A160" t="s">
+      <c r="I160" t="s">
+        <v>28</v>
+      </c>
+      <c r="J160" t="s">
+        <v>481</v>
+      </c>
+      <c r="K160" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="161" hidden="1" spans="1:11">
+      <c r="A161" t="s">
         <v>494</v>
       </c>
-      <c r="B160" t="s">
+      <c r="B161" t="s">
         <v>495</v>
       </c>
-      <c r="C160" t="s">
-        <v>402</v>
-      </c>
-      <c r="D160" t="s">
-        <v>14</v>
-      </c>
-      <c r="E160" t="s">
-        <v>15</v>
-      </c>
-      <c r="F160" t="s">
-        <v>403</v>
-      </c>
-      <c r="H160" t="s">
-        <v>26</v>
-      </c>
-      <c r="I160" t="s">
-        <v>27</v>
-      </c>
-      <c r="J160" t="s">
-        <v>483</v>
-      </c>
-      <c r="K160" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="161" spans="1:11">
-      <c r="A161" t="s">
-        <v>496</v>
-      </c>
-      <c r="B161" t="s">
-        <v>497</v>
-      </c>
       <c r="C161" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D161" t="s">
         <v>14</v>
       </c>
       <c r="E161" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F161" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="H161" t="s">
         <v>109</v>
       </c>
       <c r="I161" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J161" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="K161" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="162" spans="1:11">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="162" hidden="1" spans="1:11">
       <c r="A162" t="s">
+        <v>496</v>
+      </c>
+      <c r="B162" t="s">
+        <v>497</v>
+      </c>
+      <c r="C162" t="s">
         <v>498</v>
       </c>
-      <c r="B162" t="s">
+      <c r="D162" t="s">
+        <v>14</v>
+      </c>
+      <c r="E162" t="s">
+        <v>15</v>
+      </c>
+      <c r="F162" t="s">
         <v>499</v>
       </c>
-      <c r="C162" t="s">
+      <c r="H162" t="s">
+        <v>27</v>
+      </c>
+      <c r="I162" t="s">
+        <v>35</v>
+      </c>
+      <c r="J162" t="s">
+        <v>481</v>
+      </c>
+      <c r="K162" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="163" hidden="1" spans="1:11">
+      <c r="A163" t="s">
+        <v>412</v>
+      </c>
+      <c r="B163" t="s">
         <v>500</v>
       </c>
-      <c r="D162" t="s">
-        <v>14</v>
-      </c>
-      <c r="E162" t="s">
-        <v>15</v>
-      </c>
-      <c r="F162" t="s">
+      <c r="C163" t="s">
+        <v>414</v>
+      </c>
+      <c r="D163" t="s">
+        <v>14</v>
+      </c>
+      <c r="E163" t="s">
+        <v>32</v>
+      </c>
+      <c r="F163" t="s">
+        <v>415</v>
+      </c>
+      <c r="H163" t="s">
+        <v>27</v>
+      </c>
+      <c r="I163" t="s">
+        <v>40</v>
+      </c>
+      <c r="J163" t="s">
+        <v>228</v>
+      </c>
+      <c r="K163" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="164" hidden="1" spans="1:11">
+      <c r="A164" t="s">
         <v>501</v>
       </c>
-      <c r="H162" t="s">
-        <v>26</v>
-      </c>
-      <c r="I162" t="s">
-        <v>34</v>
-      </c>
-      <c r="J162" t="s">
-        <v>483</v>
-      </c>
-      <c r="K162" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="163" spans="1:11">
-      <c r="A163" t="s">
-        <v>414</v>
-      </c>
-      <c r="B163" t="s">
+      <c r="B164" t="s">
         <v>502</v>
       </c>
-      <c r="C163" t="s">
-        <v>416</v>
-      </c>
-      <c r="D163" t="s">
-        <v>14</v>
-      </c>
-      <c r="E163" t="s">
-        <v>31</v>
-      </c>
-      <c r="F163" t="s">
-        <v>417</v>
-      </c>
-      <c r="H163" t="s">
-        <v>26</v>
-      </c>
-      <c r="I163" t="s">
-        <v>39</v>
-      </c>
-      <c r="J163" t="s">
-        <v>230</v>
-      </c>
-      <c r="K163" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="164" spans="1:11">
-      <c r="A164" t="s">
-        <v>503</v>
-      </c>
-      <c r="B164" t="s">
-        <v>504</v>
-      </c>
       <c r="C164" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D164" t="s">
         <v>14</v>
@@ -7892,39 +7962,39 @@
         <v>15</v>
       </c>
       <c r="F164" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H164" t="s">
         <v>104</v>
       </c>
       <c r="I164" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J164" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="K164" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="165" spans="1:11">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="165" hidden="1" spans="1:11">
       <c r="A165" t="s">
+        <v>412</v>
+      </c>
+      <c r="B165" t="s">
+        <v>503</v>
+      </c>
+      <c r="C165" t="s">
         <v>414</v>
       </c>
-      <c r="B165" t="s">
-        <v>505</v>
-      </c>
-      <c r="C165" t="s">
-        <v>416</v>
-      </c>
       <c r="D165" t="s">
         <v>14</v>
       </c>
       <c r="E165" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F165" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="H165" t="s">
         <v>109</v>
@@ -7933,21 +8003,21 @@
         <v>18</v>
       </c>
       <c r="J165" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="K165" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="166" spans="1:11">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="166" hidden="1" spans="1:11">
       <c r="A166" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B166" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C166" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D166" t="s">
         <v>14</v>
@@ -7956,31 +8026,31 @@
         <v>15</v>
       </c>
       <c r="F166" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H166" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I166" t="s">
         <v>18</v>
       </c>
       <c r="J166" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="K166" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="167" hidden="1" spans="1:11">
+      <c r="A167" t="s">
+        <v>423</v>
+      </c>
+      <c r="B167" t="s">
         <v>506</v>
       </c>
-    </row>
-    <row r="167" spans="1:11">
-      <c r="A167" t="s">
+      <c r="C167" t="s">
         <v>425</v>
       </c>
-      <c r="B167" t="s">
-        <v>508</v>
-      </c>
-      <c r="C167" t="s">
-        <v>427</v>
-      </c>
       <c r="D167" t="s">
         <v>14</v>
       </c>
@@ -7988,30 +8058,30 @@
         <v>15</v>
       </c>
       <c r="F167" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="H167" t="s">
         <v>104</v>
       </c>
       <c r="I167" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J167" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K167" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="168" spans="1:11">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="168" hidden="1" spans="1:11">
       <c r="A168" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B168" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C168" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D168" t="s">
         <v>14</v>
@@ -8020,30 +8090,30 @@
         <v>15</v>
       </c>
       <c r="F168" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="H168" t="s">
         <v>109</v>
       </c>
       <c r="I168" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J168" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="K168" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="169" spans="1:11">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="169" hidden="1" spans="1:11">
       <c r="A169" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B169" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C169" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D169" t="s">
         <v>14</v>
@@ -8052,30 +8122,30 @@
         <v>15</v>
       </c>
       <c r="F169" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="H169" t="s">
         <v>17</v>
       </c>
       <c r="I169" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J169" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="K169" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="170" spans="1:11">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="170" hidden="1" spans="1:11">
       <c r="A170" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B170" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C170" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D170" t="s">
         <v>14</v>
@@ -8084,30 +8154,30 @@
         <v>15</v>
       </c>
       <c r="F170" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="H170" t="s">
         <v>17</v>
       </c>
       <c r="I170" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J170" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="K170" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="171" spans="1:11">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="171" hidden="1" spans="1:11">
       <c r="A171" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="B171" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C171" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D171" t="s">
         <v>14</v>
@@ -8116,27 +8186,27 @@
         <v>15</v>
       </c>
       <c r="F171" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="H171" t="s">
         <v>104</v>
       </c>
       <c r="I171" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J171" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="K171" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="172" spans="1:11">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="172" hidden="1" spans="1:11">
       <c r="A172" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B172" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="C172" t="s">
         <v>102</v>
@@ -8145,7 +8215,7 @@
         <v>14</v>
       </c>
       <c r="E172" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F172" t="s">
         <v>103</v>
@@ -8154,24 +8224,24 @@
         <v>109</v>
       </c>
       <c r="I172" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J172" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="K172" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="173" spans="1:11">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="173" hidden="1" spans="1:11">
       <c r="A173" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="B173" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C173" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D173" t="s">
         <v>14</v>
@@ -8180,34 +8250,37 @@
         <v>15</v>
       </c>
       <c r="F173" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="H173" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I173" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J173" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="K173" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="174" spans="1:11">
       <c r="A174" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="B174" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C174" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D174" t="s">
         <v>24</v>
       </c>
+      <c r="E174" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="H174" t="s">
         <v>109</v>
       </c>
@@ -8215,53 +8288,53 @@
         <v>18</v>
       </c>
       <c r="J174" t="s">
+        <v>519</v>
+      </c>
+      <c r="K174" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="175" hidden="1" spans="1:11">
+      <c r="A175" t="s">
+        <v>62</v>
+      </c>
+      <c r="B175" t="s">
         <v>521</v>
       </c>
-      <c r="K174" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="175" spans="1:11">
-      <c r="A175" t="s">
-        <v>61</v>
-      </c>
-      <c r="B175" t="s">
-        <v>523</v>
-      </c>
       <c r="C175" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D175" t="s">
         <v>14</v>
       </c>
       <c r="E175" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F175" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H175" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I175" t="s">
         <v>18</v>
       </c>
       <c r="J175" t="s">
+        <v>522</v>
+      </c>
+      <c r="K175" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="176" hidden="1" spans="1:11">
+      <c r="A176" t="s">
+        <v>523</v>
+      </c>
+      <c r="B176" t="s">
         <v>524</v>
       </c>
-      <c r="K175" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="176" spans="1:11">
-      <c r="A176" t="s">
-        <v>525</v>
-      </c>
-      <c r="B176" t="s">
-        <v>526</v>
-      </c>
       <c r="C176" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D176" t="s">
         <v>14</v>
@@ -8270,161 +8343,164 @@
         <v>15</v>
       </c>
       <c r="F176" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="H176" t="s">
         <v>109</v>
       </c>
       <c r="I176" t="s">
+        <v>28</v>
+      </c>
+      <c r="J176" t="s">
+        <v>525</v>
+      </c>
+      <c r="K176" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="177" hidden="1" spans="1:11">
+      <c r="A177" t="s">
+        <v>69</v>
+      </c>
+      <c r="B177" t="s">
+        <v>526</v>
+      </c>
+      <c r="C177" t="s">
+        <v>198</v>
+      </c>
+      <c r="D177" t="s">
+        <v>14</v>
+      </c>
+      <c r="E177" t="s">
+        <v>15</v>
+      </c>
+      <c r="F177" t="s">
+        <v>199</v>
+      </c>
+      <c r="H177" t="s">
         <v>27</v>
       </c>
-      <c r="J176" t="s">
-        <v>527</v>
-      </c>
-      <c r="K176" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="177" spans="1:11">
-      <c r="A177" t="s">
-        <v>68</v>
-      </c>
-      <c r="B177" t="s">
-        <v>528</v>
-      </c>
-      <c r="C177" t="s">
-        <v>200</v>
-      </c>
-      <c r="D177" t="s">
-        <v>14</v>
-      </c>
-      <c r="E177" t="s">
-        <v>15</v>
-      </c>
-      <c r="F177" t="s">
-        <v>201</v>
-      </c>
-      <c r="H177" t="s">
-        <v>26</v>
-      </c>
       <c r="I177" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J177" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="K177" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="178" spans="1:11">
       <c r="A178" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="B178" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C178" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D178" t="s">
         <v>24</v>
       </c>
+      <c r="E178" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="F178" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="G178" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="H178" t="s">
         <v>109</v>
       </c>
       <c r="I178" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J178" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="K178" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="179" spans="1:11">
       <c r="A179" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B179" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C179" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="D179" t="s">
         <v>24</v>
       </c>
-      <c r="E179" t="s">
-        <v>153</v>
+      <c r="E179" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="F179" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="H179" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I179" t="s">
+        <v>35</v>
+      </c>
+      <c r="J179" t="s">
+        <v>519</v>
+      </c>
+      <c r="K179" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="180" hidden="1" spans="1:11">
+      <c r="A180" t="s">
+        <v>46</v>
+      </c>
+      <c r="B180" t="s">
+        <v>532</v>
+      </c>
+      <c r="C180" t="s">
+        <v>31</v>
+      </c>
+      <c r="D180" t="s">
+        <v>14</v>
+      </c>
+      <c r="E180" t="s">
+        <v>32</v>
+      </c>
+      <c r="F180" t="s">
+        <v>33</v>
+      </c>
+      <c r="G180" t="s">
         <v>34</v>
-      </c>
-      <c r="J179" t="s">
-        <v>521</v>
-      </c>
-      <c r="K179" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="180" spans="1:11">
-      <c r="A180" t="s">
-        <v>45</v>
-      </c>
-      <c r="B180" t="s">
-        <v>534</v>
-      </c>
-      <c r="C180" t="s">
-        <v>30</v>
-      </c>
-      <c r="D180" t="s">
-        <v>14</v>
-      </c>
-      <c r="E180" t="s">
-        <v>31</v>
-      </c>
-      <c r="F180" t="s">
-        <v>32</v>
-      </c>
-      <c r="G180" t="s">
-        <v>33</v>
       </c>
       <c r="H180" t="s">
         <v>104</v>
       </c>
       <c r="I180" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J180" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="K180" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="181" spans="1:11">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="181" hidden="1" spans="1:11">
       <c r="A181" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B181" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="C181" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D181" t="s">
         <v>14</v>
@@ -8433,39 +8509,42 @@
         <v>15</v>
       </c>
       <c r="F181" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="H181" t="s">
         <v>104</v>
       </c>
       <c r="I181" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J181" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="K181" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="182" spans="1:11">
       <c r="A182" t="s">
+        <v>535</v>
+      </c>
+      <c r="B182" t="s">
+        <v>536</v>
+      </c>
+      <c r="C182" t="s">
         <v>537</v>
-      </c>
-      <c r="B182" t="s">
-        <v>538</v>
-      </c>
-      <c r="C182" t="s">
-        <v>539</v>
       </c>
       <c r="D182" t="s">
         <v>24</v>
       </c>
+      <c r="E182" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="F182" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="G182" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="H182" t="s">
         <v>109</v>
@@ -8477,30 +8556,30 @@
         <v>110</v>
       </c>
       <c r="K182" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
     <row r="183" spans="1:11">
       <c r="A183" t="s">
+        <v>541</v>
+      </c>
+      <c r="B183" t="s">
+        <v>542</v>
+      </c>
+      <c r="C183" t="s">
         <v>543</v>
-      </c>
-      <c r="B183" t="s">
-        <v>544</v>
-      </c>
-      <c r="C183" t="s">
-        <v>545</v>
       </c>
       <c r="D183" t="s">
         <v>24</v>
       </c>
-      <c r="E183" t="s">
-        <v>97</v>
+      <c r="E183" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="F183" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="G183" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="H183" t="s">
         <v>17</v>
@@ -8509,18 +8588,18 @@
         <v>18</v>
       </c>
       <c r="J183" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="K183" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="184" spans="1:11">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="184" hidden="1" spans="1:11">
       <c r="A184" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B184" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="C184" t="s">
         <v>113</v>
@@ -8535,7 +8614,7 @@
         <v>114</v>
       </c>
       <c r="H184" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I184" t="s">
         <v>18</v>
@@ -8544,18 +8623,18 @@
         <v>110</v>
       </c>
       <c r="K184" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="185" spans="1:11">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="185" hidden="1" spans="1:11">
       <c r="A185" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B185" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C185" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D185" t="s">
         <v>14</v>
@@ -8564,27 +8643,27 @@
         <v>15</v>
       </c>
       <c r="F185" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="H185" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I185" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J185" t="s">
         <v>110</v>
       </c>
       <c r="K185" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="186" spans="1:11">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="186" hidden="1" spans="1:11">
       <c r="A186" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B186" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="C186" t="s">
         <v>107</v>
@@ -8602,53 +8681,53 @@
         <v>109</v>
       </c>
       <c r="I186" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J186" t="s">
         <v>110</v>
       </c>
       <c r="K186" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="187" spans="1:11">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="187" hidden="1" spans="1:11">
       <c r="A187" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B187" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="C187" t="s">
+        <v>142</v>
+      </c>
+      <c r="D187" t="s">
+        <v>14</v>
+      </c>
+      <c r="E187" t="s">
+        <v>15</v>
+      </c>
+      <c r="F187" t="s">
         <v>143</v>
       </c>
-      <c r="D187" t="s">
-        <v>14</v>
-      </c>
-      <c r="E187" t="s">
-        <v>15</v>
-      </c>
-      <c r="F187" t="s">
-        <v>144</v>
-      </c>
       <c r="H187" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I187" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J187" t="s">
         <v>110</v>
       </c>
       <c r="K187" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="188" spans="1:11">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="188" hidden="1" spans="1:11">
       <c r="A188" t="s">
         <v>100</v>
       </c>
       <c r="B188" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="C188" t="s">
         <v>102</v>
@@ -8657,7 +8736,7 @@
         <v>14</v>
       </c>
       <c r="E188" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F188" t="s">
         <v>103</v>
@@ -8666,24 +8745,24 @@
         <v>104</v>
       </c>
       <c r="I188" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J188" t="s">
         <v>110</v>
       </c>
       <c r="K188" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="189" spans="1:11">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="189" hidden="1" spans="1:11">
       <c r="A189" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="B189" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="C189" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D189" t="s">
         <v>14</v>
@@ -8692,30 +8771,30 @@
         <v>15</v>
       </c>
       <c r="F189" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H189" t="s">
         <v>104</v>
       </c>
       <c r="I189" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J189" t="s">
         <v>110</v>
       </c>
       <c r="K189" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="190" spans="1:11">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="190" hidden="1" spans="1:11">
       <c r="A190" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="B190" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="C190" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D190" t="s">
         <v>14</v>
@@ -8724,23 +8803,28 @@
         <v>15</v>
       </c>
       <c r="F190" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H190" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I190" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J190" t="s">
         <v>110</v>
       </c>
       <c r="K190" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:K190" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="Vacataire"/>
+      </filters>
+    </filterColumn>
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
